--- a/sheets/AAYNA_Product_Scout_Lite.xlsx
+++ b/sheets/AAYNA_Product_Scout_Lite.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Product Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dropdown Lists" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Instructions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Claude Scoring Prompt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dropdown Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="USD_BDT">Settings!$B$5</definedName>
@@ -19,17 +21,23 @@
     <definedName name="MISC_FEE">Settings!$B$8</definedName>
     <definedName name="MARKUP_PCT">Settings!$B$9</definedName>
     <definedName name="MAX_PRICE">Settings!$B$10</definedName>
-    <definedName name="W_TREND">Settings!$B$11</definedName>
-    <definedName name="W_BRAND">Settings!$B$12</definedName>
-    <definedName name="W_DEMAND">Settings!$B$13</definedName>
-    <definedName name="W_COMPETITION">Settings!$B$14</definedName>
-    <definedName name="W_PRICEFIT">Settings!$B$15</definedName>
-    <definedName name="BUY_THRESHOLD">Settings!$B$16</definedName>
-    <definedName name="MAYBE_THRESHOLD">Settings!$B$17</definedName>
+    <definedName name="HARD_REJECT_PRICE">Settings!$B$11</definedName>
+    <definedName name="W_FEMININE">Settings!$B$12</definedName>
+    <definedName name="W_TREND">Settings!$B$13</definedName>
+    <definedName name="W_AESTHETIC">Settings!$B$14</definedName>
+    <definedName name="W_STYLE">Settings!$B$15</definedName>
+    <definedName name="W_LIGHT">Settings!$B$16</definedName>
+    <definedName name="W_REELS">Settings!$B$17</definedName>
+    <definedName name="W_GIFT">Settings!$B$18</definedName>
+    <definedName name="W_PRICEFIT">Settings!$B$19</definedName>
+    <definedName name="W_DEMAND">Settings!$B$20</definedName>
+    <definedName name="W_QUALITY">Settings!$B$21</definedName>
+    <definedName name="BUY_THRESHOLD">Settings!$B$22</definedName>
+    <definedName name="MAYBE_THRESHOLD">Settings!$B$23</definedName>
     <definedName name="LIST_PLATFORM">'Dropdown Lists'!$A$2:$A$7</definedName>
     <definedName name="LIST_CATEGORY">'Dropdown Lists'!$B$2:$B$13</definedName>
     <definedName name="LIST_CURRENCY">'Dropdown Lists'!$C$2:$C$4</definedName>
-    <definedName name="LIST_DECISION">'Dropdown Lists'!$D$2:$D$4</definedName>
+    <definedName name="LIST_DECISION">'Dropdown Lists'!$D$2:$D$5</definedName>
     <definedName name="LIST_APPROVAL">'Dropdown Lists'!$E$2:$E$5</definedName>
     <definedName name="LIST_SCORE">'Dropdown Lists'!$F$2:$F$6</definedName>
   </definedNames>
@@ -43,7 +51,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0 &quot;BDT&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +88,23 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003B2F2A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="003B2F2A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -115,11 +138,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FBF7F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFD9DC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -141,11 +174,25 @@
         <color rgb="00D9CDC3"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B89B5E"/>
+      </left>
+      <right style="medium">
+        <color rgb="00B89B5E"/>
+      </right>
+      <top style="medium">
+        <color rgb="00B89B5E"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B89B5E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,6 +211,9 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -179,24 +229,48 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -207,7 +281,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
     <dxf>
       <font>
         <b val="1"/>
@@ -233,6 +307,17 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="00B2650A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color rgb="00B23A32"/>
       </font>
       <fill>
@@ -245,6 +330,12 @@
       <font>
         <b val="1"/>
         <color rgb="00B23A32"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00B2650A"/>
       </font>
     </dxf>
     <dxf>
@@ -631,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD42"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,18 +743,28 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="10" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="10" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="10" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="10" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,7 +779,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>SKU</t>
@@ -771,2437 +872,3691 @@
       </c>
       <c r="S2" s="6" t="inlineStr">
         <is>
+          <t>Feminine Score (1-5)</t>
+        </is>
+      </c>
+      <c r="T2" s="6" t="inlineStr">
+        <is>
           <t>Trend Score (1-5)</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
-        <is>
-          <t>Brand Fit Score (1-5)</t>
-        </is>
-      </c>
       <c r="U2" s="6" t="inlineStr">
         <is>
+          <t>AAYNA Aesthetic Fit Score (1-5)</t>
+        </is>
+      </c>
+      <c r="V2" s="6" t="inlineStr">
+        <is>
+          <t>Easy to Style Score (1-5)</t>
+        </is>
+      </c>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>Lightweight Score (1-5)</t>
+        </is>
+      </c>
+      <c r="X2" s="6" t="inlineStr">
+        <is>
+          <t>Reels/Photo Potential Score (1-5)</t>
+        </is>
+      </c>
+      <c r="Y2" s="6" t="inlineStr">
+        <is>
+          <t>Giftability Score (1-5)</t>
+        </is>
+      </c>
+      <c r="Z2" s="6" t="inlineStr">
+        <is>
+          <t>Price Fit Score (1-5)</t>
+        </is>
+      </c>
+      <c r="AA2" s="6" t="inlineStr">
+        <is>
           <t>Demand Score (1-5)</t>
         </is>
       </c>
-      <c r="V2" s="6" t="inlineStr">
-        <is>
-          <t>Competition Score (1-5)</t>
-        </is>
-      </c>
-      <c r="W2" s="6" t="inlineStr">
-        <is>
-          <t>Price Fit Score (1-5)</t>
-        </is>
-      </c>
-      <c r="X2" s="6" t="inlineStr">
+      <c r="AB2" s="6" t="inlineStr">
+        <is>
+          <t>Quality/Risk Score (1-5)</t>
+        </is>
+      </c>
+      <c r="AC2" s="6" t="inlineStr">
         <is>
           <t>Total Product Score (/100)</t>
         </is>
       </c>
-      <c r="Y2" s="6" t="inlineStr">
+      <c r="AD2" s="6" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="Z2" s="6" t="inlineStr">
+      <c r="AE2" s="6" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>SKU/Content/Reel Idea</t>
-        </is>
-      </c>
-      <c r="AB2" s="7" t="inlineStr">
+      <c r="AF2" s="7" t="inlineStr">
+        <is>
+          <t>Content/Reel Idea</t>
+        </is>
+      </c>
+      <c r="AG2" s="7" t="inlineStr">
         <is>
           <t>Approval Status</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AH2" s="7" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AI2" s="7" t="inlineStr">
         <is>
           <t>Date Decided</t>
         </is>
       </c>
+      <c r="AJ2" s="8" t="inlineStr">
+        <is>
+          <t>Rank Key: Overall (hidden)</t>
+        </is>
+      </c>
+      <c r="AK2" s="8" t="inlineStr">
+        <is>
+          <t>Rank Key: Under 700 BDT (hidden)</t>
+        </is>
+      </c>
+      <c r="AL2" s="8" t="inlineStr">
+        <is>
+          <t>Rank Key: Reels/Photo (hidden)</t>
+        </is>
+      </c>
+      <c r="AM2" s="8" t="inlineStr">
+        <is>
+          <t>Rank Key: Giftability (hidden)</t>
+        </is>
+      </c>
+      <c r="AN2" s="8" t="inlineStr">
+        <is>
+          <t>Rank Key: Needs Review (hidden)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <f>IF(C3="","","AYN-"&amp;UPPER(LEFT(E3,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Antique Gold Hoop Earrings</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>drive.google.com/sample1</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Earrings</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>aliexpress.com/item/sample1</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Lin Wei Trading</t>
         </is>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="11">
         <f>IF(I3="","",IF(J3="BDT",I3,IF(J3="USD",I3*USD_BDT,IF(J3="RMB",I3*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L3" s="10" t="n">
+      <c r="L3" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="10" t="n">
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="11">
         <f>IF(K3="","",K3+IFERROR(L3,0)+(K3*IF(M3="",CUSTOMS_PCT,M3))+IF(N3="",MISC_FEE,N3))</f>
         <v/>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="11">
         <f>IF(O3="","",ROUND(O3*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="11">
         <f>IF(P3="","",P3-O3)</f>
         <v/>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="12">
         <f>IF(OR(P3="",P3=0),"",Q3/P3)</f>
         <v/>
       </c>
-      <c r="S3" s="8" t="n">
+      <c r="S3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="T3" s="8" t="n">
+      <c r="W3" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="U3" s="8" t="n">
+      <c r="X3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="V3" s="8" t="n">
+      <c r="Z3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="13">
+        <f>IF(COUNT(S3:AB3)&lt;10,"",(S3*W_FEMININE+T3*W_TREND+U3*W_AESTHETIC+V3*W_STYLE+W3*W_LIGHT+X3*W_REELS+Y3*W_GIFT+Z3*W_PRICEFIT+AA3*W_DEMAND+AB3*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD3" s="9">
+        <f>IF(P3="","",IF(P3&gt;HARD_REJECT_PRICE,"Reject",IF(P3&gt;MAX_PRICE,"Price Review",IF(AC3="","",IF(AND(AC3&gt;=BUY_THRESHOLD,OR(AB3&lt;=2,U3&lt;=2)),"Maybe",IF(AC3&gt;=BUY_THRESHOLD,"Buy",IF(AC3&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="9" t="inlineStr">
+        <is>
+          <t>Strong rose-gold match, trending on TikTok, lightweight and giftable.</t>
+        </is>
+      </c>
+      <c r="AF3" s="9" t="inlineStr">
+        <is>
+          <t>Reel: 'Get Ready With Me' earring swap, 3 looks in 15 sec.</t>
+        </is>
+      </c>
+      <c r="AG3" s="9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AH3" s="9" t="inlineStr">
+        <is>
+          <t>Nadia</t>
+        </is>
+      </c>
+      <c r="AI3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <f>IF(AC3="",-9999-ROW()*0.0000001,AC3-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK3">
+        <f>IF(OR(AC3="",P3="",P3&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC3-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL3">
+        <f>IF(AC3="",-9999-ROW()*0.0000001,X3*1000+AC3-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM3">
+        <f>IF(AC3="",-9999-ROW()*0.0000001,Y3*1000+AC3-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN3">
+        <f>IF(AND(OR(AD3="Maybe",AD3="Price Review"),AG3&lt;&gt;"Approved",AG3&lt;&gt;"Rejected"),IF(AC3="",0,AC3)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(C4="","","AYN-"&amp;UPPER(LEFT(E4,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Beaded Choker Necklace</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>drive.google.com/sample2</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Necklace</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>SkyBuyBD</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>skybuybd.com/item/sample2</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Skybuy Supplier 14</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="K4" s="16">
+        <f>IF(I4="","",IF(J4="BDT",I4,IF(J4="USD",I4*USD_BDT,IF(J4="RMB",I4*RMB_BDT,""))))</f>
+        <v/>
+      </c>
+      <c r="L4" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="17" t="n"/>
+      <c r="N4" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="O4" s="16">
+        <f>IF(K4="","",K4+IFERROR(L4,0)+(K4*IF(M4="",CUSTOMS_PCT,M4))+IF(N4="",MISC_FEE,N4))</f>
+        <v/>
+      </c>
+      <c r="P4" s="16">
+        <f>IF(O4="","",ROUND(O4*(1+MARKUP_PCT),-1)-1)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="16">
+        <f>IF(P4="","",P4-O4)</f>
+        <v/>
+      </c>
+      <c r="R4" s="17">
+        <f>IF(OR(P4="",P4=0),"",Q4/P4)</f>
+        <v/>
+      </c>
+      <c r="S4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="18">
+        <f>IF(COUNT(S4:AB4)&lt;10,"",(S4*W_FEMININE+T4*W_TREND+U4*W_AESTHETIC+V4*W_STYLE+W4*W_LIGHT+X4*W_REELS+Y4*W_GIFT+Z4*W_PRICEFIT+AA4*W_DEMAND+AB4*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD4" s="14">
+        <f>IF(P4="","",IF(P4&gt;HARD_REJECT_PRICE,"Reject",IF(P4&gt;MAX_PRICE,"Price Review",IF(AC4="","",IF(AND(AC4&gt;=BUY_THRESHOLD,OR(AB4&lt;=2,U4&lt;=2)),"Maybe",IF(AC4&gt;=BUY_THRESHOLD,"Buy",IF(AC4&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="14" t="inlineStr">
+        <is>
+          <t>Gorgeous and on-trend, but beads chip easily in transit — quality/return risk caps this at Maybe.</t>
+        </is>
+      </c>
+      <c r="AF4" s="14" t="inlineStr">
+        <is>
+          <t>Try-on reel layering 3 chokers.</t>
+        </is>
+      </c>
+      <c r="AG4" s="14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="AH4" s="14" t="n"/>
+      <c r="AI4" s="15" t="n"/>
+      <c r="AJ4">
+        <f>IF(AC4="",-9999-ROW()*0.0000001,AC4-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK4">
+        <f>IF(OR(AC4="",P4="",P4&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC4-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL4">
+        <f>IF(AC4="",-9999-ROW()*0.0000001,X4*1000+AC4-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM4">
+        <f>IF(AC4="",-9999-ROW()*0.0000001,Y4*1000+AC4-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN4">
+        <f>IF(AND(OR(AD4="Maybe",AD4="Price Review"),AG4&lt;&gt;"Approved",AG4&lt;&gt;"Rejected"),IF(AC4="",0,AC4)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9">
+        <f>IF(C5="","","AYN-"&amp;UPPER(LEFT(E5,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Plain Plastic Hair Clip</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>drive.google.com/sample3</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Hair Accessory</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>1688.com/item/sample3</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Generic Factory 8</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="K5" s="11">
+        <f>IF(I5="","",IF(J5="BDT",I5,IF(J5="USD",I5*USD_BDT,IF(J5="RMB",I5*RMB_BDT,""))))</f>
+        <v/>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" s="11">
+        <f>IF(K5="","",K5+IFERROR(L5,0)+(K5*IF(M5="",CUSTOMS_PCT,M5))+IF(N5="",MISC_FEE,N5))</f>
+        <v/>
+      </c>
+      <c r="P5" s="11">
+        <f>IF(O5="","",ROUND(O5*(1+MARKUP_PCT),-1)-1)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="11">
+        <f>IF(P5="","",P5-O5)</f>
+        <v/>
+      </c>
+      <c r="R5" s="12">
+        <f>IF(OR(P5="",P5=0),"",Q5/P5)</f>
+        <v/>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W3" s="8" t="n">
+      <c r="W5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="X3" s="12">
-        <f>IF(COUNT(S3:W3)&lt;5,"",(S3*W_TREND+T3*W_BRAND+U3*W_DEMAND+V3*W_COMPETITION+W3*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y3" s="8">
-        <f>IF(X3="","",IF(X3&gt;=BUY_THRESHOLD,"Buy",IF(X3&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z3" s="8" t="n"/>
-      <c r="AA3" s="8" t="inlineStr">
-        <is>
-          <t>Strong match for AAYNA's gold/feminine aesthetic; trending on TikTok.</t>
-        </is>
-      </c>
-      <c r="AB3" s="8" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="AC3" s="8" t="inlineStr">
-        <is>
-          <t>Reel: 'Get Ready With Me' earring swap, 3 looks in 15 sec.</t>
-        </is>
-      </c>
-      <c r="AD3" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13">
-        <f>IF(C4="","","AYN-"&amp;UPPER(LEFT(E4,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
-        <v/>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Dusty Rose Pearl Hair Clip Set</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>drive.google.com/sample2</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Hair Accessory</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>SkyBuyBD</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>skybuybd.com/item/sample2</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Skybuy Supplier 22</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="AA5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC5" s="13">
+        <f>IF(COUNT(S5:AB5)&lt;10,"",(S5*W_FEMININE+T5*W_TREND+U5*W_AESTHETIC+V5*W_STYLE+W5*W_LIGHT+X5*W_REELS+Y5*W_GIFT+Z5*W_PRICEFIT+AA5*W_DEMAND+AB5*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD5" s="9">
+        <f>IF(P5="","",IF(P5&gt;HARD_REJECT_PRICE,"Reject",IF(P5&gt;MAX_PRICE,"Price Review",IF(AC5="","",IF(AND(AC5&gt;=BUY_THRESHOLD,OR(AB5&lt;=2,U5&lt;=2)),"Maybe",IF(AC5&gt;=BUY_THRESHOLD,"Buy",IF(AC5&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="9" t="inlineStr">
+        <is>
+          <t>Generic look, low trend/demand/aesthetic fit — total score too low to justify stocking.</t>
+        </is>
+      </c>
+      <c r="AF5" s="9" t="inlineStr"/>
+      <c r="AG5" s="9" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="10" t="n"/>
+      <c r="AJ5">
+        <f>IF(AC5="",-9999-ROW()*0.0000001,AC5-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK5">
+        <f>IF(OR(AC5="",P5="",P5&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC5-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL5">
+        <f>IF(AC5="",-9999-ROW()*0.0000001,X5*1000+AC5-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM5">
+        <f>IF(AC5="",-9999-ROW()*0.0000001,Y5*1000+AC5-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN5">
+        <f>IF(AND(OR(AD5="Maybe",AD5="Price Review"),AG5&lt;&gt;"Approved",AG5&lt;&gt;"Rejected"),IF(AC5="",0,AC5)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(C6="","","AYN-"&amp;UPPER(LEFT(E6,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Embroidered Tote Bag</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>drive.google.com/sample4</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>aliexpress.com/item/sample4</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Lin Wei Trading</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>BDT</t>
         </is>
       </c>
-      <c r="K4" s="15">
-        <f>IF(I4="","",IF(J4="BDT",I4,IF(J4="USD",I4*USD_BDT,IF(J4="RMB",I4*RMB_BDT,""))))</f>
-        <v/>
-      </c>
-      <c r="L4" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N4" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="O4" s="15">
-        <f>IF(K4="","",K4+IFERROR(L4,0)+(K4*IF(M4="",CUSTOMS_PCT,M4))+IF(N4="",MISC_FEE,N4))</f>
-        <v/>
-      </c>
-      <c r="P4" s="15">
-        <f>IF(O4="","",ROUND(O4*(1+MARKUP_PCT),-1)-1)</f>
-        <v/>
-      </c>
-      <c r="Q4" s="15">
-        <f>IF(P4="","",P4-O4)</f>
-        <v/>
-      </c>
-      <c r="R4" s="16">
-        <f>IF(OR(P4="",P4=0),"",Q4/P4)</f>
-        <v/>
-      </c>
-      <c r="S4" s="13" t="n">
+      <c r="K6" s="16">
+        <f>IF(I6="","",IF(J6="BDT",I6,IF(J6="USD",I6*USD_BDT,IF(J6="RMB",I6*RMB_BDT,""))))</f>
+        <v/>
+      </c>
+      <c r="L6" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="16">
+        <f>IF(K6="","",K6+IFERROR(L6,0)+(K6*IF(M6="",CUSTOMS_PCT,M6))+IF(N6="",MISC_FEE,N6))</f>
+        <v/>
+      </c>
+      <c r="P6" s="16">
+        <f>IF(O6="","",ROUND(O6*(1+MARKUP_PCT),-1)-1)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="16">
+        <f>IF(P6="","",P6-O6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="17">
+        <f>IF(OR(P6="",P6=0),"",Q6/P6)</f>
+        <v/>
+      </c>
+      <c r="S6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="13" t="n">
+      <c r="W6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="U4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="13" t="n">
+      <c r="Z6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="X4" s="17">
-        <f>IF(COUNT(S4:W4)&lt;5,"",(S4*W_TREND+T4*W_BRAND+U4*W_DEMAND+V4*W_COMPETITION+W4*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y4" s="13">
-        <f>IF(X4="","",IF(X4&gt;=BUY_THRESHOLD,"Buy",IF(X4&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z4" s="13" t="n"/>
-      <c r="AA4" s="13" t="inlineStr">
-        <is>
-          <t>Good margin but lots of similar clips already in market; watch competition.</t>
-        </is>
-      </c>
-      <c r="AB4" s="13" t="inlineStr">
+      <c r="AA6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" s="18">
+        <f>IF(COUNT(S6:AB6)&lt;10,"",(S6*W_FEMININE+T6*W_TREND+U6*W_AESTHETIC+V6*W_STYLE+W6*W_LIGHT+X6*W_REELS+Y6*W_GIFT+Z6*W_PRICEFIT+AA6*W_DEMAND+AB6*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="14">
+        <f>IF(P6="","",IF(P6&gt;HARD_REJECT_PRICE,"Reject",IF(P6&gt;MAX_PRICE,"Price Review",IF(AC6="","",IF(AND(AC6&gt;=BUY_THRESHOLD,OR(AB6&lt;=2,U6&lt;=2)),"Maybe",IF(AC6&gt;=BUY_THRESHOLD,"Buy",IF(AC6&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="14" t="inlineStr">
+        <is>
+          <t>Lovely design, but landed cost pushes selling price over 700 — needs supplier price negotiation.</t>
+        </is>
+      </c>
+      <c r="AF6" s="14" t="inlineStr">
+        <is>
+          <t>Flatlay reel with 3 outfit pairings.</t>
+        </is>
+      </c>
+      <c r="AG6" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AC4" s="13" t="inlineStr">
-        <is>
-          <t>Carousel post: 5 hairstyles using one clip set.</t>
-        </is>
-      </c>
-      <c r="AD4" s="14" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8">
-        <f>IF(C5="","","AYN-"&amp;UPPER(LEFT(E5,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
-        <v/>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="10">
-        <f>IF(I5="","",IF(J5="BDT",I5,IF(J5="USD",I5*USD_BDT,IF(J5="RMB",I5*RMB_BDT,""))))</f>
-        <v/>
-      </c>
-      <c r="L5" s="10" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10">
-        <f>IF(K5="","",K5+IFERROR(L5,0)+(K5*IF(M5="",CUSTOMS_PCT,M5))+IF(N5="",MISC_FEE,N5))</f>
-        <v/>
-      </c>
-      <c r="P5" s="10">
-        <f>IF(O5="","",ROUND(O5*(1+MARKUP_PCT),-1)-1)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="10">
-        <f>IF(P5="","",P5-O5)</f>
-        <v/>
-      </c>
-      <c r="R5" s="11">
-        <f>IF(OR(P5="",P5=0),"",Q5/P5)</f>
-        <v/>
-      </c>
-      <c r="S5" s="8" t="n"/>
-      <c r="T5" s="8" t="n"/>
-      <c r="U5" s="8" t="n"/>
-      <c r="V5" s="8" t="n"/>
-      <c r="W5" s="8" t="n"/>
-      <c r="X5" s="12">
-        <f>IF(COUNT(S5:W5)&lt;5,"",(S5*W_TREND+T5*W_BRAND+U5*W_DEMAND+V5*W_COMPETITION+W5*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y5" s="8">
-        <f>IF(X5="","",IF(X5&gt;=BUY_THRESHOLD,"Buy",IF(X5&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z5" s="8" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="8" t="n"/>
-      <c r="AC5" s="8" t="n"/>
-      <c r="AD5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13">
-        <f>IF(C6="","","AYN-"&amp;UPPER(LEFT(E6,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="15">
-        <f>IF(I6="","",IF(J6="BDT",I6,IF(J6="USD",I6*USD_BDT,IF(J6="RMB",I6*RMB_BDT,""))))</f>
-        <v/>
-      </c>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15">
-        <f>IF(K6="","",K6+IFERROR(L6,0)+(K6*IF(M6="",CUSTOMS_PCT,M6))+IF(N6="",MISC_FEE,N6))</f>
-        <v/>
-      </c>
-      <c r="P6" s="15">
-        <f>IF(O6="","",ROUND(O6*(1+MARKUP_PCT),-1)-1)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="15">
-        <f>IF(P6="","",P6-O6)</f>
-        <v/>
-      </c>
-      <c r="R6" s="16">
-        <f>IF(OR(P6="",P6=0),"",Q6/P6)</f>
-        <v/>
-      </c>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
-      <c r="X6" s="17">
-        <f>IF(COUNT(S6:W6)&lt;5,"",(S6*W_TREND+T6*W_BRAND+U6*W_DEMAND+V6*W_COMPETITION+W6*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="13">
-        <f>IF(X6="","",IF(X6&gt;=BUY_THRESHOLD,"Buy",IF(X6&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="13" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n"/>
-      <c r="AC6" s="13" t="n"/>
-      <c r="AD6" s="14" t="n"/>
+      <c r="AH6" s="14" t="n"/>
+      <c r="AI6" s="15" t="n"/>
+      <c r="AJ6">
+        <f>IF(AC6="",-9999-ROW()*0.0000001,AC6-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK6">
+        <f>IF(OR(AC6="",P6="",P6&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC6-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL6">
+        <f>IF(AC6="",-9999-ROW()*0.0000001,X6*1000+AC6-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM6">
+        <f>IF(AC6="",-9999-ROW()*0.0000001,Y6*1000+AC6-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN6">
+        <f>IF(AND(OR(AD6="Maybe",AD6="Price Review"),AG6&lt;&gt;"Approved",AG6&lt;&gt;"Rejected"),IF(AC6="",0,AC6)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <f>IF(C7="","","AYN-"&amp;UPPER(LEFT(E7,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="10">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Designer-Inspired Sunglasses</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>drive.google.com/sample5</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Sunglasses</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>aliexpress.com/item/sample5</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Guangzhou Eyewear Co</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K7" s="11">
         <f>IF(I7="","",IF(J7="BDT",I7,IF(J7="USD",I7*USD_BDT,IF(J7="RMB",I7*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L7" s="10" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="10">
+      <c r="L7" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" s="11">
         <f>IF(K7="","",K7+IFERROR(L7,0)+(K7*IF(M7="",CUSTOMS_PCT,M7))+IF(N7="",MISC_FEE,N7))</f>
         <v/>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="11">
         <f>IF(O7="","",ROUND(O7*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="11">
         <f>IF(P7="","",P7-O7)</f>
         <v/>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="12">
         <f>IF(OR(P7="",P7=0),"",Q7/P7)</f>
         <v/>
       </c>
-      <c r="S7" s="8" t="n"/>
-      <c r="T7" s="8" t="n"/>
-      <c r="U7" s="8" t="n"/>
-      <c r="V7" s="8" t="n"/>
-      <c r="W7" s="8" t="n"/>
-      <c r="X7" s="12">
-        <f>IF(COUNT(S7:W7)&lt;5,"",(S7*W_TREND+T7*W_BRAND+U7*W_DEMAND+V7*W_COMPETITION+W7*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="8">
-        <f>IF(X7="","",IF(X7&gt;=BUY_THRESHOLD,"Buy",IF(X7&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z7" s="8" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="8" t="n"/>
-      <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="9" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="9" t="n"/>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="13">
+        <f>IF(COUNT(S7:AB7)&lt;10,"",(S7*W_FEMININE+T7*W_TREND+U7*W_AESTHETIC+V7*W_STYLE+W7*W_LIGHT+X7*W_REELS+Y7*W_GIFT+Z7*W_PRICEFIT+AA7*W_DEMAND+AB7*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9">
+        <f>IF(P7="","",IF(P7&gt;HARD_REJECT_PRICE,"Reject",IF(P7&gt;MAX_PRICE,"Price Review",IF(AC7="","",IF(AND(AC7&gt;=BUY_THRESHOLD,OR(AB7&lt;=2,U7&lt;=2)),"Maybe",IF(AC7&gt;=BUY_THRESHOLD,"Buy",IF(AC7&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="9" t="inlineStr">
+        <is>
+          <t>Cost alone puts this far above our price ceiling even before scoring — auto-rejected.</t>
+        </is>
+      </c>
+      <c r="AF7" s="9" t="inlineStr"/>
+      <c r="AG7" s="9" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="10" t="n"/>
+      <c r="AJ7">
+        <f>IF(AC7="",-9999-ROW()*0.0000001,AC7-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK7">
+        <f>IF(OR(AC7="",P7="",P7&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC7-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL7">
+        <f>IF(AC7="",-9999-ROW()*0.0000001,X7*1000+AC7-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM7">
+        <f>IF(AC7="",-9999-ROW()*0.0000001,Y7*1000+AC7-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN7">
+        <f>IF(AND(OR(AD7="Maybe",AD7="Price Review"),AG7&lt;&gt;"Approved",AG7&lt;&gt;"Rejected"),IF(AC7="",0,AC7)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <f>IF(C8="","","AYN-"&amp;UPPER(LEFT(E8,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="15">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="16">
         <f>IF(I8="","",IF(J8="BDT",I8,IF(J8="USD",I8*USD_BDT,IF(J8="RMB",I8*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15">
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16">
         <f>IF(K8="","",K8+IFERROR(L8,0)+(K8*IF(M8="",CUSTOMS_PCT,M8))+IF(N8="",MISC_FEE,N8))</f>
         <v/>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="16">
         <f>IF(O8="","",ROUND(O8*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="16">
         <f>IF(P8="","",P8-O8)</f>
         <v/>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="17">
         <f>IF(OR(P8="",P8=0),"",Q8/P8)</f>
         <v/>
       </c>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="17">
-        <f>IF(COUNT(S8:W8)&lt;5,"",(S8*W_TREND+T8*W_BRAND+U8*W_DEMAND+V8*W_COMPETITION+W8*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="13">
-        <f>IF(X8="","",IF(X8&gt;=BUY_THRESHOLD,"Buy",IF(X8&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z8" s="13" t="n"/>
-      <c r="AA8" s="13" t="n"/>
-      <c r="AB8" s="13" t="n"/>
-      <c r="AC8" s="13" t="n"/>
-      <c r="AD8" s="14" t="n"/>
+      <c r="S8" s="14" t="n"/>
+      <c r="T8" s="14" t="n"/>
+      <c r="U8" s="14" t="n"/>
+      <c r="V8" s="14" t="n"/>
+      <c r="W8" s="14" t="n"/>
+      <c r="X8" s="14" t="n"/>
+      <c r="Y8" s="14" t="n"/>
+      <c r="Z8" s="14" t="n"/>
+      <c r="AA8" s="14" t="n"/>
+      <c r="AB8" s="14" t="n"/>
+      <c r="AC8" s="18">
+        <f>IF(COUNT(S8:AB8)&lt;10,"",(S8*W_FEMININE+T8*W_TREND+U8*W_AESTHETIC+V8*W_STYLE+W8*W_LIGHT+X8*W_REELS+Y8*W_GIFT+Z8*W_PRICEFIT+AA8*W_DEMAND+AB8*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="14">
+        <f>IF(P8="","",IF(P8&gt;HARD_REJECT_PRICE,"Reject",IF(P8&gt;MAX_PRICE,"Price Review",IF(AC8="","",IF(AND(AC8&gt;=BUY_THRESHOLD,OR(AB8&lt;=2,U8&lt;=2)),"Maybe",IF(AC8&gt;=BUY_THRESHOLD,"Buy",IF(AC8&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="14" t="n"/>
+      <c r="AF8" s="14" t="n"/>
+      <c r="AG8" s="14" t="n"/>
+      <c r="AH8" s="14" t="n"/>
+      <c r="AI8" s="15" t="n"/>
+      <c r="AJ8">
+        <f>IF(AC8="",-9999-ROW()*0.0000001,AC8-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK8">
+        <f>IF(OR(AC8="",P8="",P8&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC8-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL8">
+        <f>IF(AC8="",-9999-ROW()*0.0000001,X8*1000+AC8-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM8">
+        <f>IF(AC8="",-9999-ROW()*0.0000001,Y8*1000+AC8-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN8">
+        <f>IF(AND(OR(AD8="Maybe",AD8="Price Review"),AG8&lt;&gt;"Approved",AG8&lt;&gt;"Rejected"),IF(AC8="",0,AC8)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <f>IF(C9="","","AYN-"&amp;UPPER(LEFT(E9,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="10">
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="11">
         <f>IF(I9="","",IF(J9="BDT",I9,IF(J9="USD",I9*USD_BDT,IF(J9="RMB",I9*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L9" s="10" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="10" t="n"/>
-      <c r="O9" s="10">
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11">
         <f>IF(K9="","",K9+IFERROR(L9,0)+(K9*IF(M9="",CUSTOMS_PCT,M9))+IF(N9="",MISC_FEE,N9))</f>
         <v/>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="11">
         <f>IF(O9="","",ROUND(O9*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="11">
         <f>IF(P9="","",P9-O9)</f>
         <v/>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="12">
         <f>IF(OR(P9="",P9=0),"",Q9/P9)</f>
         <v/>
       </c>
-      <c r="S9" s="8" t="n"/>
-      <c r="T9" s="8" t="n"/>
-      <c r="U9" s="8" t="n"/>
-      <c r="V9" s="8" t="n"/>
-      <c r="W9" s="8" t="n"/>
-      <c r="X9" s="12">
-        <f>IF(COUNT(S9:W9)&lt;5,"",(S9*W_TREND+T9*W_BRAND+U9*W_DEMAND+V9*W_COMPETITION+W9*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="8">
-        <f>IF(X9="","",IF(X9&gt;=BUY_THRESHOLD,"Buy",IF(X9&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z9" s="8" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="8" t="n"/>
-      <c r="AC9" s="8" t="n"/>
-      <c r="AD9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="9" t="n"/>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="13">
+        <f>IF(COUNT(S9:AB9)&lt;10,"",(S9*W_FEMININE+T9*W_TREND+U9*W_AESTHETIC+V9*W_STYLE+W9*W_LIGHT+X9*W_REELS+Y9*W_GIFT+Z9*W_PRICEFIT+AA9*W_DEMAND+AB9*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9">
+        <f>IF(P9="","",IF(P9&gt;HARD_REJECT_PRICE,"Reject",IF(P9&gt;MAX_PRICE,"Price Review",IF(AC9="","",IF(AND(AC9&gt;=BUY_THRESHOLD,OR(AB9&lt;=2,U9&lt;=2)),"Maybe",IF(AC9&gt;=BUY_THRESHOLD,"Buy",IF(AC9&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="9" t="n"/>
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="10" t="n"/>
+      <c r="AJ9">
+        <f>IF(AC9="",-9999-ROW()*0.0000001,AC9-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK9">
+        <f>IF(OR(AC9="",P9="",P9&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC9-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL9">
+        <f>IF(AC9="",-9999-ROW()*0.0000001,X9*1000+AC9-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM9">
+        <f>IF(AC9="",-9999-ROW()*0.0000001,Y9*1000+AC9-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN9">
+        <f>IF(AND(OR(AD9="Maybe",AD9="Price Review"),AG9&lt;&gt;"Approved",AG9&lt;&gt;"Rejected"),IF(AC9="",0,AC9)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <f>IF(C10="","","AYN-"&amp;UPPER(LEFT(E10,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="15">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="16">
         <f>IF(I10="","",IF(J10="BDT",I10,IF(J10="USD",I10*USD_BDT,IF(J10="RMB",I10*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15">
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16">
         <f>IF(K10="","",K10+IFERROR(L10,0)+(K10*IF(M10="",CUSTOMS_PCT,M10))+IF(N10="",MISC_FEE,N10))</f>
         <v/>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="16">
         <f>IF(O10="","",ROUND(O10*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="16">
         <f>IF(P10="","",P10-O10)</f>
         <v/>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="17">
         <f>IF(OR(P10="",P10=0),"",Q10/P10)</f>
         <v/>
       </c>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
-      <c r="X10" s="17">
-        <f>IF(COUNT(S10:W10)&lt;5,"",(S10*W_TREND+T10*W_BRAND+U10*W_DEMAND+V10*W_COMPETITION+W10*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="13">
-        <f>IF(X10="","",IF(X10&gt;=BUY_THRESHOLD,"Buy",IF(X10&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z10" s="13" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="13" t="n"/>
-      <c r="AC10" s="13" t="n"/>
-      <c r="AD10" s="14" t="n"/>
+      <c r="S10" s="14" t="n"/>
+      <c r="T10" s="14" t="n"/>
+      <c r="U10" s="14" t="n"/>
+      <c r="V10" s="14" t="n"/>
+      <c r="W10" s="14" t="n"/>
+      <c r="X10" s="14" t="n"/>
+      <c r="Y10" s="14" t="n"/>
+      <c r="Z10" s="14" t="n"/>
+      <c r="AA10" s="14" t="n"/>
+      <c r="AB10" s="14" t="n"/>
+      <c r="AC10" s="18">
+        <f>IF(COUNT(S10:AB10)&lt;10,"",(S10*W_FEMININE+T10*W_TREND+U10*W_AESTHETIC+V10*W_STYLE+W10*W_LIGHT+X10*W_REELS+Y10*W_GIFT+Z10*W_PRICEFIT+AA10*W_DEMAND+AB10*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="14">
+        <f>IF(P10="","",IF(P10&gt;HARD_REJECT_PRICE,"Reject",IF(P10&gt;MAX_PRICE,"Price Review",IF(AC10="","",IF(AND(AC10&gt;=BUY_THRESHOLD,OR(AB10&lt;=2,U10&lt;=2)),"Maybe",IF(AC10&gt;=BUY_THRESHOLD,"Buy",IF(AC10&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="14" t="n"/>
+      <c r="AF10" s="14" t="n"/>
+      <c r="AG10" s="14" t="n"/>
+      <c r="AH10" s="14" t="n"/>
+      <c r="AI10" s="15" t="n"/>
+      <c r="AJ10">
+        <f>IF(AC10="",-9999-ROW()*0.0000001,AC10-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK10">
+        <f>IF(OR(AC10="",P10="",P10&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC10-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL10">
+        <f>IF(AC10="",-9999-ROW()*0.0000001,X10*1000+AC10-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM10">
+        <f>IF(AC10="",-9999-ROW()*0.0000001,Y10*1000+AC10-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN10">
+        <f>IF(AND(OR(AD10="Maybe",AD10="Price Review"),AG10&lt;&gt;"Approved",AG10&lt;&gt;"Rejected"),IF(AC10="",0,AC10)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <f>IF(C11="","","AYN-"&amp;UPPER(LEFT(E11,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="10">
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="11">
         <f>IF(I11="","",IF(J11="BDT",I11,IF(J11="USD",I11*USD_BDT,IF(J11="RMB",I11*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L11" s="10" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="10" t="n"/>
-      <c r="O11" s="10">
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11">
         <f>IF(K11="","",K11+IFERROR(L11,0)+(K11*IF(M11="",CUSTOMS_PCT,M11))+IF(N11="",MISC_FEE,N11))</f>
         <v/>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="11">
         <f>IF(O11="","",ROUND(O11*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="11">
         <f>IF(P11="","",P11-O11)</f>
         <v/>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="12">
         <f>IF(OR(P11="",P11=0),"",Q11/P11)</f>
         <v/>
       </c>
-      <c r="S11" s="8" t="n"/>
-      <c r="T11" s="8" t="n"/>
-      <c r="U11" s="8" t="n"/>
-      <c r="V11" s="8" t="n"/>
-      <c r="W11" s="8" t="n"/>
-      <c r="X11" s="12">
-        <f>IF(COUNT(S11:W11)&lt;5,"",(S11*W_TREND+T11*W_BRAND+U11*W_DEMAND+V11*W_COMPETITION+W11*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="8">
-        <f>IF(X11="","",IF(X11&gt;=BUY_THRESHOLD,"Buy",IF(X11&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z11" s="8" t="n"/>
-      <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="8" t="n"/>
-      <c r="AC11" s="8" t="n"/>
-      <c r="AD11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="13">
+        <f>IF(COUNT(S11:AB11)&lt;10,"",(S11*W_FEMININE+T11*W_TREND+U11*W_AESTHETIC+V11*W_STYLE+W11*W_LIGHT+X11*W_REELS+Y11*W_GIFT+Z11*W_PRICEFIT+AA11*W_DEMAND+AB11*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9">
+        <f>IF(P11="","",IF(P11&gt;HARD_REJECT_PRICE,"Reject",IF(P11&gt;MAX_PRICE,"Price Review",IF(AC11="","",IF(AND(AC11&gt;=BUY_THRESHOLD,OR(AB11&lt;=2,U11&lt;=2)),"Maybe",IF(AC11&gt;=BUY_THRESHOLD,"Buy",IF(AC11&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="9" t="n"/>
+      <c r="AF11" s="9" t="n"/>
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="10" t="n"/>
+      <c r="AJ11">
+        <f>IF(AC11="",-9999-ROW()*0.0000001,AC11-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK11">
+        <f>IF(OR(AC11="",P11="",P11&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC11-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL11">
+        <f>IF(AC11="",-9999-ROW()*0.0000001,X11*1000+AC11-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM11">
+        <f>IF(AC11="",-9999-ROW()*0.0000001,Y11*1000+AC11-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN11">
+        <f>IF(AND(OR(AD11="Maybe",AD11="Price Review"),AG11&lt;&gt;"Approved",AG11&lt;&gt;"Rejected"),IF(AC11="",0,AC11)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <f>IF(C12="","","AYN-"&amp;UPPER(LEFT(E12,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="15">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="16">
         <f>IF(I12="","",IF(J12="BDT",I12,IF(J12="USD",I12*USD_BDT,IF(J12="RMB",I12*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="16" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15">
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16">
         <f>IF(K12="","",K12+IFERROR(L12,0)+(K12*IF(M12="",CUSTOMS_PCT,M12))+IF(N12="",MISC_FEE,N12))</f>
         <v/>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="16">
         <f>IF(O12="","",ROUND(O12*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="16">
         <f>IF(P12="","",P12-O12)</f>
         <v/>
       </c>
-      <c r="R12" s="16">
+      <c r="R12" s="17">
         <f>IF(OR(P12="",P12=0),"",Q12/P12)</f>
         <v/>
       </c>
-      <c r="S12" s="13" t="n"/>
-      <c r="T12" s="13" t="n"/>
-      <c r="U12" s="13" t="n"/>
-      <c r="V12" s="13" t="n"/>
-      <c r="W12" s="13" t="n"/>
-      <c r="X12" s="17">
-        <f>IF(COUNT(S12:W12)&lt;5,"",(S12*W_TREND+T12*W_BRAND+U12*W_DEMAND+V12*W_COMPETITION+W12*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="13">
-        <f>IF(X12="","",IF(X12&gt;=BUY_THRESHOLD,"Buy",IF(X12&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z12" s="13" t="n"/>
-      <c r="AA12" s="13" t="n"/>
-      <c r="AB12" s="13" t="n"/>
-      <c r="AC12" s="13" t="n"/>
-      <c r="AD12" s="14" t="n"/>
+      <c r="S12" s="14" t="n"/>
+      <c r="T12" s="14" t="n"/>
+      <c r="U12" s="14" t="n"/>
+      <c r="V12" s="14" t="n"/>
+      <c r="W12" s="14" t="n"/>
+      <c r="X12" s="14" t="n"/>
+      <c r="Y12" s="14" t="n"/>
+      <c r="Z12" s="14" t="n"/>
+      <c r="AA12" s="14" t="n"/>
+      <c r="AB12" s="14" t="n"/>
+      <c r="AC12" s="18">
+        <f>IF(COUNT(S12:AB12)&lt;10,"",(S12*W_FEMININE+T12*W_TREND+U12*W_AESTHETIC+V12*W_STYLE+W12*W_LIGHT+X12*W_REELS+Y12*W_GIFT+Z12*W_PRICEFIT+AA12*W_DEMAND+AB12*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="14">
+        <f>IF(P12="","",IF(P12&gt;HARD_REJECT_PRICE,"Reject",IF(P12&gt;MAX_PRICE,"Price Review",IF(AC12="","",IF(AND(AC12&gt;=BUY_THRESHOLD,OR(AB12&lt;=2,U12&lt;=2)),"Maybe",IF(AC12&gt;=BUY_THRESHOLD,"Buy",IF(AC12&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="14" t="n"/>
+      <c r="AF12" s="14" t="n"/>
+      <c r="AG12" s="14" t="n"/>
+      <c r="AH12" s="14" t="n"/>
+      <c r="AI12" s="15" t="n"/>
+      <c r="AJ12">
+        <f>IF(AC12="",-9999-ROW()*0.0000001,AC12-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK12">
+        <f>IF(OR(AC12="",P12="",P12&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC12-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL12">
+        <f>IF(AC12="",-9999-ROW()*0.0000001,X12*1000+AC12-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM12">
+        <f>IF(AC12="",-9999-ROW()*0.0000001,Y12*1000+AC12-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN12">
+        <f>IF(AND(OR(AD12="Maybe",AD12="Price Review"),AG12&lt;&gt;"Approved",AG12&lt;&gt;"Rejected"),IF(AC12="",0,AC12)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <f>IF(C13="","","AYN-"&amp;UPPER(LEFT(E13,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="10">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="11">
         <f>IF(I13="","",IF(J13="BDT",I13,IF(J13="USD",I13*USD_BDT,IF(J13="RMB",I13*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10">
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11">
         <f>IF(K13="","",K13+IFERROR(L13,0)+(K13*IF(M13="",CUSTOMS_PCT,M13))+IF(N13="",MISC_FEE,N13))</f>
         <v/>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="11">
         <f>IF(O13="","",ROUND(O13*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="11">
         <f>IF(P13="","",P13-O13)</f>
         <v/>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="12">
         <f>IF(OR(P13="",P13=0),"",Q13/P13)</f>
         <v/>
       </c>
-      <c r="S13" s="8" t="n"/>
-      <c r="T13" s="8" t="n"/>
-      <c r="U13" s="8" t="n"/>
-      <c r="V13" s="8" t="n"/>
-      <c r="W13" s="8" t="n"/>
-      <c r="X13" s="12">
-        <f>IF(COUNT(S13:W13)&lt;5,"",(S13*W_TREND+T13*W_BRAND+U13*W_DEMAND+V13*W_COMPETITION+W13*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="8">
-        <f>IF(X13="","",IF(X13&gt;=BUY_THRESHOLD,"Buy",IF(X13&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z13" s="8" t="n"/>
-      <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="8" t="n"/>
-      <c r="AC13" s="8" t="n"/>
-      <c r="AD13" s="9" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="9" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="9" t="n"/>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="13">
+        <f>IF(COUNT(S13:AB13)&lt;10,"",(S13*W_FEMININE+T13*W_TREND+U13*W_AESTHETIC+V13*W_STYLE+W13*W_LIGHT+X13*W_REELS+Y13*W_GIFT+Z13*W_PRICEFIT+AA13*W_DEMAND+AB13*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9">
+        <f>IF(P13="","",IF(P13&gt;HARD_REJECT_PRICE,"Reject",IF(P13&gt;MAX_PRICE,"Price Review",IF(AC13="","",IF(AND(AC13&gt;=BUY_THRESHOLD,OR(AB13&lt;=2,U13&lt;=2)),"Maybe",IF(AC13&gt;=BUY_THRESHOLD,"Buy",IF(AC13&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="9" t="n"/>
+      <c r="AF13" s="9" t="n"/>
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13">
+        <f>IF(AC13="",-9999-ROW()*0.0000001,AC13-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK13">
+        <f>IF(OR(AC13="",P13="",P13&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC13-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL13">
+        <f>IF(AC13="",-9999-ROW()*0.0000001,X13*1000+AC13-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM13">
+        <f>IF(AC13="",-9999-ROW()*0.0000001,Y13*1000+AC13-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN13">
+        <f>IF(AND(OR(AD13="Maybe",AD13="Price Review"),AG13&lt;&gt;"Approved",AG13&lt;&gt;"Rejected"),IF(AC13="",0,AC13)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <f>IF(C14="","","AYN-"&amp;UPPER(LEFT(E14,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="15">
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="16">
         <f>IF(I14="","",IF(J14="BDT",I14,IF(J14="USD",I14*USD_BDT,IF(J14="RMB",I14*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15">
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16">
         <f>IF(K14="","",K14+IFERROR(L14,0)+(K14*IF(M14="",CUSTOMS_PCT,M14))+IF(N14="",MISC_FEE,N14))</f>
         <v/>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="16">
         <f>IF(O14="","",ROUND(O14*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="16">
         <f>IF(P14="","",P14-O14)</f>
         <v/>
       </c>
-      <c r="R14" s="16">
+      <c r="R14" s="17">
         <f>IF(OR(P14="",P14=0),"",Q14/P14)</f>
         <v/>
       </c>
-      <c r="S14" s="13" t="n"/>
-      <c r="T14" s="13" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="13" t="n"/>
-      <c r="X14" s="17">
-        <f>IF(COUNT(S14:W14)&lt;5,"",(S14*W_TREND+T14*W_BRAND+U14*W_DEMAND+V14*W_COMPETITION+W14*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="13">
-        <f>IF(X14="","",IF(X14&gt;=BUY_THRESHOLD,"Buy",IF(X14&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z14" s="13" t="n"/>
-      <c r="AA14" s="13" t="n"/>
-      <c r="AB14" s="13" t="n"/>
-      <c r="AC14" s="13" t="n"/>
-      <c r="AD14" s="14" t="n"/>
+      <c r="S14" s="14" t="n"/>
+      <c r="T14" s="14" t="n"/>
+      <c r="U14" s="14" t="n"/>
+      <c r="V14" s="14" t="n"/>
+      <c r="W14" s="14" t="n"/>
+      <c r="X14" s="14" t="n"/>
+      <c r="Y14" s="14" t="n"/>
+      <c r="Z14" s="14" t="n"/>
+      <c r="AA14" s="14" t="n"/>
+      <c r="AB14" s="14" t="n"/>
+      <c r="AC14" s="18">
+        <f>IF(COUNT(S14:AB14)&lt;10,"",(S14*W_FEMININE+T14*W_TREND+U14*W_AESTHETIC+V14*W_STYLE+W14*W_LIGHT+X14*W_REELS+Y14*W_GIFT+Z14*W_PRICEFIT+AA14*W_DEMAND+AB14*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="14">
+        <f>IF(P14="","",IF(P14&gt;HARD_REJECT_PRICE,"Reject",IF(P14&gt;MAX_PRICE,"Price Review",IF(AC14="","",IF(AND(AC14&gt;=BUY_THRESHOLD,OR(AB14&lt;=2,U14&lt;=2)),"Maybe",IF(AC14&gt;=BUY_THRESHOLD,"Buy",IF(AC14&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="14" t="n"/>
+      <c r="AF14" s="14" t="n"/>
+      <c r="AG14" s="14" t="n"/>
+      <c r="AH14" s="14" t="n"/>
+      <c r="AI14" s="15" t="n"/>
+      <c r="AJ14">
+        <f>IF(AC14="",-9999-ROW()*0.0000001,AC14-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK14">
+        <f>IF(OR(AC14="",P14="",P14&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC14-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL14">
+        <f>IF(AC14="",-9999-ROW()*0.0000001,X14*1000+AC14-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM14">
+        <f>IF(AC14="",-9999-ROW()*0.0000001,Y14*1000+AC14-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN14">
+        <f>IF(AND(OR(AD14="Maybe",AD14="Price Review"),AG14&lt;&gt;"Approved",AG14&lt;&gt;"Rejected"),IF(AC14="",0,AC14)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8">
+      <c r="A15" s="9">
         <f>IF(C15="","","AYN-"&amp;UPPER(LEFT(E15,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="10">
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="11">
         <f>IF(I15="","",IF(J15="BDT",I15,IF(J15="USD",I15*USD_BDT,IF(J15="RMB",I15*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L15" s="10" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="10" t="n"/>
-      <c r="O15" s="10">
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11">
         <f>IF(K15="","",K15+IFERROR(L15,0)+(K15*IF(M15="",CUSTOMS_PCT,M15))+IF(N15="",MISC_FEE,N15))</f>
         <v/>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="11">
         <f>IF(O15="","",ROUND(O15*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q15" s="10">
+      <c r="Q15" s="11">
         <f>IF(P15="","",P15-O15)</f>
         <v/>
       </c>
-      <c r="R15" s="11">
+      <c r="R15" s="12">
         <f>IF(OR(P15="",P15=0),"",Q15/P15)</f>
         <v/>
       </c>
-      <c r="S15" s="8" t="n"/>
-      <c r="T15" s="8" t="n"/>
-      <c r="U15" s="8" t="n"/>
-      <c r="V15" s="8" t="n"/>
-      <c r="W15" s="8" t="n"/>
-      <c r="X15" s="12">
-        <f>IF(COUNT(S15:W15)&lt;5,"",(S15*W_TREND+T15*W_BRAND+U15*W_DEMAND+V15*W_COMPETITION+W15*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="8">
-        <f>IF(X15="","",IF(X15&gt;=BUY_THRESHOLD,"Buy",IF(X15&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z15" s="8" t="n"/>
-      <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="8" t="n"/>
-      <c r="AC15" s="8" t="n"/>
-      <c r="AD15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="9" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="13">
+        <f>IF(COUNT(S15:AB15)&lt;10,"",(S15*W_FEMININE+T15*W_TREND+U15*W_AESTHETIC+V15*W_STYLE+W15*W_LIGHT+X15*W_REELS+Y15*W_GIFT+Z15*W_PRICEFIT+AA15*W_DEMAND+AB15*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="9">
+        <f>IF(P15="","",IF(P15&gt;HARD_REJECT_PRICE,"Reject",IF(P15&gt;MAX_PRICE,"Price Review",IF(AC15="","",IF(AND(AC15&gt;=BUY_THRESHOLD,OR(AB15&lt;=2,U15&lt;=2)),"Maybe",IF(AC15&gt;=BUY_THRESHOLD,"Buy",IF(AC15&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="9" t="n"/>
+      <c r="AF15" s="9" t="n"/>
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+      <c r="AI15" s="10" t="n"/>
+      <c r="AJ15">
+        <f>IF(AC15="",-9999-ROW()*0.0000001,AC15-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK15">
+        <f>IF(OR(AC15="",P15="",P15&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC15-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL15">
+        <f>IF(AC15="",-9999-ROW()*0.0000001,X15*1000+AC15-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM15">
+        <f>IF(AC15="",-9999-ROW()*0.0000001,Y15*1000+AC15-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN15">
+        <f>IF(AND(OR(AD15="Maybe",AD15="Price Review"),AG15&lt;&gt;"Approved",AG15&lt;&gt;"Rejected"),IF(AC15="",0,AC15)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <f>IF(C16="","","AYN-"&amp;UPPER(LEFT(E16,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="15">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="16">
         <f>IF(I16="","",IF(J16="BDT",I16,IF(J16="USD",I16*USD_BDT,IF(J16="RMB",I16*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15">
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16">
         <f>IF(K16="","",K16+IFERROR(L16,0)+(K16*IF(M16="",CUSTOMS_PCT,M16))+IF(N16="",MISC_FEE,N16))</f>
         <v/>
       </c>
-      <c r="P16" s="15">
+      <c r="P16" s="16">
         <f>IF(O16="","",ROUND(O16*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="16">
         <f>IF(P16="","",P16-O16)</f>
         <v/>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="17">
         <f>IF(OR(P16="",P16=0),"",Q16/P16)</f>
         <v/>
       </c>
-      <c r="S16" s="13" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="13" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="13" t="n"/>
-      <c r="X16" s="17">
-        <f>IF(COUNT(S16:W16)&lt;5,"",(S16*W_TREND+T16*W_BRAND+U16*W_DEMAND+V16*W_COMPETITION+W16*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="13">
-        <f>IF(X16="","",IF(X16&gt;=BUY_THRESHOLD,"Buy",IF(X16&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z16" s="13" t="n"/>
-      <c r="AA16" s="13" t="n"/>
-      <c r="AB16" s="13" t="n"/>
-      <c r="AC16" s="13" t="n"/>
-      <c r="AD16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
+      <c r="T16" s="14" t="n"/>
+      <c r="U16" s="14" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="14" t="n"/>
+      <c r="X16" s="14" t="n"/>
+      <c r="Y16" s="14" t="n"/>
+      <c r="Z16" s="14" t="n"/>
+      <c r="AA16" s="14" t="n"/>
+      <c r="AB16" s="14" t="n"/>
+      <c r="AC16" s="18">
+        <f>IF(COUNT(S16:AB16)&lt;10,"",(S16*W_FEMININE+T16*W_TREND+U16*W_AESTHETIC+V16*W_STYLE+W16*W_LIGHT+X16*W_REELS+Y16*W_GIFT+Z16*W_PRICEFIT+AA16*W_DEMAND+AB16*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="14">
+        <f>IF(P16="","",IF(P16&gt;HARD_REJECT_PRICE,"Reject",IF(P16&gt;MAX_PRICE,"Price Review",IF(AC16="","",IF(AND(AC16&gt;=BUY_THRESHOLD,OR(AB16&lt;=2,U16&lt;=2)),"Maybe",IF(AC16&gt;=BUY_THRESHOLD,"Buy",IF(AC16&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="14" t="n"/>
+      <c r="AF16" s="14" t="n"/>
+      <c r="AG16" s="14" t="n"/>
+      <c r="AH16" s="14" t="n"/>
+      <c r="AI16" s="15" t="n"/>
+      <c r="AJ16">
+        <f>IF(AC16="",-9999-ROW()*0.0000001,AC16-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK16">
+        <f>IF(OR(AC16="",P16="",P16&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC16-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL16">
+        <f>IF(AC16="",-9999-ROW()*0.0000001,X16*1000+AC16-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM16">
+        <f>IF(AC16="",-9999-ROW()*0.0000001,Y16*1000+AC16-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN16">
+        <f>IF(AND(OR(AD16="Maybe",AD16="Price Review"),AG16&lt;&gt;"Approved",AG16&lt;&gt;"Rejected"),IF(AC16="",0,AC16)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <f>IF(C17="","","AYN-"&amp;UPPER(LEFT(E17,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="10">
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="11">
         <f>IF(I17="","",IF(J17="BDT",I17,IF(J17="USD",I17*USD_BDT,IF(J17="RMB",I17*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="10">
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="11">
         <f>IF(K17="","",K17+IFERROR(L17,0)+(K17*IF(M17="",CUSTOMS_PCT,M17))+IF(N17="",MISC_FEE,N17))</f>
         <v/>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="11">
         <f>IF(O17="","",ROUND(O17*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="11">
         <f>IF(P17="","",P17-O17)</f>
         <v/>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="12">
         <f>IF(OR(P17="",P17=0),"",Q17/P17)</f>
         <v/>
       </c>
-      <c r="S17" s="8" t="n"/>
-      <c r="T17" s="8" t="n"/>
-      <c r="U17" s="8" t="n"/>
-      <c r="V17" s="8" t="n"/>
-      <c r="W17" s="8" t="n"/>
-      <c r="X17" s="12">
-        <f>IF(COUNT(S17:W17)&lt;5,"",(S17*W_TREND+T17*W_BRAND+U17*W_DEMAND+V17*W_COMPETITION+W17*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="8">
-        <f>IF(X17="","",IF(X17&gt;=BUY_THRESHOLD,"Buy",IF(X17&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z17" s="8" t="n"/>
-      <c r="AA17" s="8" t="n"/>
-      <c r="AB17" s="8" t="n"/>
-      <c r="AC17" s="8" t="n"/>
-      <c r="AD17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="9" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="13">
+        <f>IF(COUNT(S17:AB17)&lt;10,"",(S17*W_FEMININE+T17*W_TREND+U17*W_AESTHETIC+V17*W_STYLE+W17*W_LIGHT+X17*W_REELS+Y17*W_GIFT+Z17*W_PRICEFIT+AA17*W_DEMAND+AB17*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="9">
+        <f>IF(P17="","",IF(P17&gt;HARD_REJECT_PRICE,"Reject",IF(P17&gt;MAX_PRICE,"Price Review",IF(AC17="","",IF(AND(AC17&gt;=BUY_THRESHOLD,OR(AB17&lt;=2,U17&lt;=2)),"Maybe",IF(AC17&gt;=BUY_THRESHOLD,"Buy",IF(AC17&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="9" t="n"/>
+      <c r="AF17" s="9" t="n"/>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+      <c r="AI17" s="10" t="n"/>
+      <c r="AJ17">
+        <f>IF(AC17="",-9999-ROW()*0.0000001,AC17-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK17">
+        <f>IF(OR(AC17="",P17="",P17&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC17-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL17">
+        <f>IF(AC17="",-9999-ROW()*0.0000001,X17*1000+AC17-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM17">
+        <f>IF(AC17="",-9999-ROW()*0.0000001,Y17*1000+AC17-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN17">
+        <f>IF(AND(OR(AD17="Maybe",AD17="Price Review"),AG17&lt;&gt;"Approved",AG17&lt;&gt;"Rejected"),IF(AC17="",0,AC17)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <f>IF(C18="","","AYN-"&amp;UPPER(LEFT(E18,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="15">
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="16">
         <f>IF(I18="","",IF(J18="BDT",I18,IF(J18="USD",I18*USD_BDT,IF(J18="RMB",I18*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15">
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16">
         <f>IF(K18="","",K18+IFERROR(L18,0)+(K18*IF(M18="",CUSTOMS_PCT,M18))+IF(N18="",MISC_FEE,N18))</f>
         <v/>
       </c>
-      <c r="P18" s="15">
+      <c r="P18" s="16">
         <f>IF(O18="","",ROUND(O18*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="16">
         <f>IF(P18="","",P18-O18)</f>
         <v/>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="17">
         <f>IF(OR(P18="",P18=0),"",Q18/P18)</f>
         <v/>
       </c>
-      <c r="S18" s="13" t="n"/>
-      <c r="T18" s="13" t="n"/>
-      <c r="U18" s="13" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="13" t="n"/>
-      <c r="X18" s="17">
-        <f>IF(COUNT(S18:W18)&lt;5,"",(S18*W_TREND+T18*W_BRAND+U18*W_DEMAND+V18*W_COMPETITION+W18*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y18" s="13">
-        <f>IF(X18="","",IF(X18&gt;=BUY_THRESHOLD,"Buy",IF(X18&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z18" s="13" t="n"/>
-      <c r="AA18" s="13" t="n"/>
-      <c r="AB18" s="13" t="n"/>
-      <c r="AC18" s="13" t="n"/>
-      <c r="AD18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="14" t="n"/>
+      <c r="U18" s="14" t="n"/>
+      <c r="V18" s="14" t="n"/>
+      <c r="W18" s="14" t="n"/>
+      <c r="X18" s="14" t="n"/>
+      <c r="Y18" s="14" t="n"/>
+      <c r="Z18" s="14" t="n"/>
+      <c r="AA18" s="14" t="n"/>
+      <c r="AB18" s="14" t="n"/>
+      <c r="AC18" s="18">
+        <f>IF(COUNT(S18:AB18)&lt;10,"",(S18*W_FEMININE+T18*W_TREND+U18*W_AESTHETIC+V18*W_STYLE+W18*W_LIGHT+X18*W_REELS+Y18*W_GIFT+Z18*W_PRICEFIT+AA18*W_DEMAND+AB18*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="14">
+        <f>IF(P18="","",IF(P18&gt;HARD_REJECT_PRICE,"Reject",IF(P18&gt;MAX_PRICE,"Price Review",IF(AC18="","",IF(AND(AC18&gt;=BUY_THRESHOLD,OR(AB18&lt;=2,U18&lt;=2)),"Maybe",IF(AC18&gt;=BUY_THRESHOLD,"Buy",IF(AC18&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="14" t="n"/>
+      <c r="AF18" s="14" t="n"/>
+      <c r="AG18" s="14" t="n"/>
+      <c r="AH18" s="14" t="n"/>
+      <c r="AI18" s="15" t="n"/>
+      <c r="AJ18">
+        <f>IF(AC18="",-9999-ROW()*0.0000001,AC18-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK18">
+        <f>IF(OR(AC18="",P18="",P18&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC18-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL18">
+        <f>IF(AC18="",-9999-ROW()*0.0000001,X18*1000+AC18-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM18">
+        <f>IF(AC18="",-9999-ROW()*0.0000001,Y18*1000+AC18-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN18">
+        <f>IF(AND(OR(AD18="Maybe",AD18="Price Review"),AG18&lt;&gt;"Approved",AG18&lt;&gt;"Rejected"),IF(AC18="",0,AC18)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8">
+      <c r="A19" s="9">
         <f>IF(C19="","","AYN-"&amp;UPPER(LEFT(E19,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="10">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="11">
         <f>IF(I19="","",IF(J19="BDT",I19,IF(J19="USD",I19*USD_BDT,IF(J19="RMB",I19*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10">
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11">
         <f>IF(K19="","",K19+IFERROR(L19,0)+(K19*IF(M19="",CUSTOMS_PCT,M19))+IF(N19="",MISC_FEE,N19))</f>
         <v/>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="11">
         <f>IF(O19="","",ROUND(O19*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q19" s="11">
         <f>IF(P19="","",P19-O19)</f>
         <v/>
       </c>
-      <c r="R19" s="11">
+      <c r="R19" s="12">
         <f>IF(OR(P19="",P19=0),"",Q19/P19)</f>
         <v/>
       </c>
-      <c r="S19" s="8" t="n"/>
-      <c r="T19" s="8" t="n"/>
-      <c r="U19" s="8" t="n"/>
-      <c r="V19" s="8" t="n"/>
-      <c r="W19" s="8" t="n"/>
-      <c r="X19" s="12">
-        <f>IF(COUNT(S19:W19)&lt;5,"",(S19*W_TREND+T19*W_BRAND+U19*W_DEMAND+V19*W_COMPETITION+W19*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="8">
-        <f>IF(X19="","",IF(X19&gt;=BUY_THRESHOLD,"Buy",IF(X19&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z19" s="8" t="n"/>
-      <c r="AA19" s="8" t="n"/>
-      <c r="AB19" s="8" t="n"/>
-      <c r="AC19" s="8" t="n"/>
-      <c r="AD19" s="9" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="9" t="n"/>
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="9" t="n"/>
+      <c r="AA19" s="9" t="n"/>
+      <c r="AB19" s="9" t="n"/>
+      <c r="AC19" s="13">
+        <f>IF(COUNT(S19:AB19)&lt;10,"",(S19*W_FEMININE+T19*W_TREND+U19*W_AESTHETIC+V19*W_STYLE+W19*W_LIGHT+X19*W_REELS+Y19*W_GIFT+Z19*W_PRICEFIT+AA19*W_DEMAND+AB19*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="9">
+        <f>IF(P19="","",IF(P19&gt;HARD_REJECT_PRICE,"Reject",IF(P19&gt;MAX_PRICE,"Price Review",IF(AC19="","",IF(AND(AC19&gt;=BUY_THRESHOLD,OR(AB19&lt;=2,U19&lt;=2)),"Maybe",IF(AC19&gt;=BUY_THRESHOLD,"Buy",IF(AC19&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="9" t="n"/>
+      <c r="AF19" s="9" t="n"/>
+      <c r="AG19" s="9" t="n"/>
+      <c r="AH19" s="9" t="n"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19">
+        <f>IF(AC19="",-9999-ROW()*0.0000001,AC19-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK19">
+        <f>IF(OR(AC19="",P19="",P19&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC19-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL19">
+        <f>IF(AC19="",-9999-ROW()*0.0000001,X19*1000+AC19-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM19">
+        <f>IF(AC19="",-9999-ROW()*0.0000001,Y19*1000+AC19-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN19">
+        <f>IF(AND(OR(AD19="Maybe",AD19="Price Review"),AG19&lt;&gt;"Approved",AG19&lt;&gt;"Rejected"),IF(AC19="",0,AC19)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <f>IF(C20="","","AYN-"&amp;UPPER(LEFT(E20,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="15">
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="16">
         <f>IF(I20="","",IF(J20="BDT",I20,IF(J20="USD",I20*USD_BDT,IF(J20="RMB",I20*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15">
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16">
         <f>IF(K20="","",K20+IFERROR(L20,0)+(K20*IF(M20="",CUSTOMS_PCT,M20))+IF(N20="",MISC_FEE,N20))</f>
         <v/>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="16">
         <f>IF(O20="","",ROUND(O20*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q20" s="15">
+      <c r="Q20" s="16">
         <f>IF(P20="","",P20-O20)</f>
         <v/>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="17">
         <f>IF(OR(P20="",P20=0),"",Q20/P20)</f>
         <v/>
       </c>
-      <c r="S20" s="13" t="n"/>
-      <c r="T20" s="13" t="n"/>
-      <c r="U20" s="13" t="n"/>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="13" t="n"/>
-      <c r="X20" s="17">
-        <f>IF(COUNT(S20:W20)&lt;5,"",(S20*W_TREND+T20*W_BRAND+U20*W_DEMAND+V20*W_COMPETITION+W20*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="13">
-        <f>IF(X20="","",IF(X20&gt;=BUY_THRESHOLD,"Buy",IF(X20&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z20" s="13" t="n"/>
-      <c r="AA20" s="13" t="n"/>
-      <c r="AB20" s="13" t="n"/>
-      <c r="AC20" s="13" t="n"/>
-      <c r="AD20" s="14" t="n"/>
+      <c r="S20" s="14" t="n"/>
+      <c r="T20" s="14" t="n"/>
+      <c r="U20" s="14" t="n"/>
+      <c r="V20" s="14" t="n"/>
+      <c r="W20" s="14" t="n"/>
+      <c r="X20" s="14" t="n"/>
+      <c r="Y20" s="14" t="n"/>
+      <c r="Z20" s="14" t="n"/>
+      <c r="AA20" s="14" t="n"/>
+      <c r="AB20" s="14" t="n"/>
+      <c r="AC20" s="18">
+        <f>IF(COUNT(S20:AB20)&lt;10,"",(S20*W_FEMININE+T20*W_TREND+U20*W_AESTHETIC+V20*W_STYLE+W20*W_LIGHT+X20*W_REELS+Y20*W_GIFT+Z20*W_PRICEFIT+AA20*W_DEMAND+AB20*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="14">
+        <f>IF(P20="","",IF(P20&gt;HARD_REJECT_PRICE,"Reject",IF(P20&gt;MAX_PRICE,"Price Review",IF(AC20="","",IF(AND(AC20&gt;=BUY_THRESHOLD,OR(AB20&lt;=2,U20&lt;=2)),"Maybe",IF(AC20&gt;=BUY_THRESHOLD,"Buy",IF(AC20&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="14" t="n"/>
+      <c r="AF20" s="14" t="n"/>
+      <c r="AG20" s="14" t="n"/>
+      <c r="AH20" s="14" t="n"/>
+      <c r="AI20" s="15" t="n"/>
+      <c r="AJ20">
+        <f>IF(AC20="",-9999-ROW()*0.0000001,AC20-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK20">
+        <f>IF(OR(AC20="",P20="",P20&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC20-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL20">
+        <f>IF(AC20="",-9999-ROW()*0.0000001,X20*1000+AC20-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM20">
+        <f>IF(AC20="",-9999-ROW()*0.0000001,Y20*1000+AC20-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN20">
+        <f>IF(AND(OR(AD20="Maybe",AD20="Price Review"),AG20&lt;&gt;"Approved",AG20&lt;&gt;"Rejected"),IF(AC20="",0,AC20)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8">
+      <c r="A21" s="9">
         <f>IF(C21="","","AYN-"&amp;UPPER(LEFT(E21,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="10">
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="11">
         <f>IF(I21="","",IF(J21="BDT",I21,IF(J21="USD",I21*USD_BDT,IF(J21="RMB",I21*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10">
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11">
         <f>IF(K21="","",K21+IFERROR(L21,0)+(K21*IF(M21="",CUSTOMS_PCT,M21))+IF(N21="",MISC_FEE,N21))</f>
         <v/>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="11">
         <f>IF(O21="","",ROUND(O21*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q21" s="10">
+      <c r="Q21" s="11">
         <f>IF(P21="","",P21-O21)</f>
         <v/>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="12">
         <f>IF(OR(P21="",P21=0),"",Q21/P21)</f>
         <v/>
       </c>
-      <c r="S21" s="8" t="n"/>
-      <c r="T21" s="8" t="n"/>
-      <c r="U21" s="8" t="n"/>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="8" t="n"/>
-      <c r="X21" s="12">
-        <f>IF(COUNT(S21:W21)&lt;5,"",(S21*W_TREND+T21*W_BRAND+U21*W_DEMAND+V21*W_COMPETITION+W21*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="8">
-        <f>IF(X21="","",IF(X21&gt;=BUY_THRESHOLD,"Buy",IF(X21&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z21" s="8" t="n"/>
-      <c r="AA21" s="8" t="n"/>
-      <c r="AB21" s="8" t="n"/>
-      <c r="AC21" s="8" t="n"/>
-      <c r="AD21" s="9" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="9" t="n"/>
+      <c r="AA21" s="9" t="n"/>
+      <c r="AB21" s="9" t="n"/>
+      <c r="AC21" s="13">
+        <f>IF(COUNT(S21:AB21)&lt;10,"",(S21*W_FEMININE+T21*W_TREND+U21*W_AESTHETIC+V21*W_STYLE+W21*W_LIGHT+X21*W_REELS+Y21*W_GIFT+Z21*W_PRICEFIT+AA21*W_DEMAND+AB21*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="9">
+        <f>IF(P21="","",IF(P21&gt;HARD_REJECT_PRICE,"Reject",IF(P21&gt;MAX_PRICE,"Price Review",IF(AC21="","",IF(AND(AC21&gt;=BUY_THRESHOLD,OR(AB21&lt;=2,U21&lt;=2)),"Maybe",IF(AC21&gt;=BUY_THRESHOLD,"Buy",IF(AC21&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="9" t="n"/>
+      <c r="AF21" s="9" t="n"/>
+      <c r="AG21" s="9" t="n"/>
+      <c r="AH21" s="9" t="n"/>
+      <c r="AI21" s="10" t="n"/>
+      <c r="AJ21">
+        <f>IF(AC21="",-9999-ROW()*0.0000001,AC21-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK21">
+        <f>IF(OR(AC21="",P21="",P21&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC21-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL21">
+        <f>IF(AC21="",-9999-ROW()*0.0000001,X21*1000+AC21-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM21">
+        <f>IF(AC21="",-9999-ROW()*0.0000001,Y21*1000+AC21-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN21">
+        <f>IF(AND(OR(AD21="Maybe",AD21="Price Review"),AG21&lt;&gt;"Approved",AG21&lt;&gt;"Rejected"),IF(AC21="",0,AC21)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <f>IF(C22="","","AYN-"&amp;UPPER(LEFT(E22,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="15">
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="16">
         <f>IF(I22="","",IF(J22="BDT",I22,IF(J22="USD",I22*USD_BDT,IF(J22="RMB",I22*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="16" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15">
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="17" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16">
         <f>IF(K22="","",K22+IFERROR(L22,0)+(K22*IF(M22="",CUSTOMS_PCT,M22))+IF(N22="",MISC_FEE,N22))</f>
         <v/>
       </c>
-      <c r="P22" s="15">
+      <c r="P22" s="16">
         <f>IF(O22="","",ROUND(O22*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q22" s="15">
+      <c r="Q22" s="16">
         <f>IF(P22="","",P22-O22)</f>
         <v/>
       </c>
-      <c r="R22" s="16">
+      <c r="R22" s="17">
         <f>IF(OR(P22="",P22=0),"",Q22/P22)</f>
         <v/>
       </c>
-      <c r="S22" s="13" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="13" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="13" t="n"/>
-      <c r="X22" s="17">
-        <f>IF(COUNT(S22:W22)&lt;5,"",(S22*W_TREND+T22*W_BRAND+U22*W_DEMAND+V22*W_COMPETITION+W22*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="13">
-        <f>IF(X22="","",IF(X22&gt;=BUY_THRESHOLD,"Buy",IF(X22&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z22" s="13" t="n"/>
-      <c r="AA22" s="13" t="n"/>
-      <c r="AB22" s="13" t="n"/>
-      <c r="AC22" s="13" t="n"/>
-      <c r="AD22" s="14" t="n"/>
+      <c r="S22" s="14" t="n"/>
+      <c r="T22" s="14" t="n"/>
+      <c r="U22" s="14" t="n"/>
+      <c r="V22" s="14" t="n"/>
+      <c r="W22" s="14" t="n"/>
+      <c r="X22" s="14" t="n"/>
+      <c r="Y22" s="14" t="n"/>
+      <c r="Z22" s="14" t="n"/>
+      <c r="AA22" s="14" t="n"/>
+      <c r="AB22" s="14" t="n"/>
+      <c r="AC22" s="18">
+        <f>IF(COUNT(S22:AB22)&lt;10,"",(S22*W_FEMININE+T22*W_TREND+U22*W_AESTHETIC+V22*W_STYLE+W22*W_LIGHT+X22*W_REELS+Y22*W_GIFT+Z22*W_PRICEFIT+AA22*W_DEMAND+AB22*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="14">
+        <f>IF(P22="","",IF(P22&gt;HARD_REJECT_PRICE,"Reject",IF(P22&gt;MAX_PRICE,"Price Review",IF(AC22="","",IF(AND(AC22&gt;=BUY_THRESHOLD,OR(AB22&lt;=2,U22&lt;=2)),"Maybe",IF(AC22&gt;=BUY_THRESHOLD,"Buy",IF(AC22&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="14" t="n"/>
+      <c r="AF22" s="14" t="n"/>
+      <c r="AG22" s="14" t="n"/>
+      <c r="AH22" s="14" t="n"/>
+      <c r="AI22" s="15" t="n"/>
+      <c r="AJ22">
+        <f>IF(AC22="",-9999-ROW()*0.0000001,AC22-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK22">
+        <f>IF(OR(AC22="",P22="",P22&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC22-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL22">
+        <f>IF(AC22="",-9999-ROW()*0.0000001,X22*1000+AC22-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM22">
+        <f>IF(AC22="",-9999-ROW()*0.0000001,Y22*1000+AC22-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN22">
+        <f>IF(AND(OR(AD22="Maybe",AD22="Price Review"),AG22&lt;&gt;"Approved",AG22&lt;&gt;"Rejected"),IF(AC22="",0,AC22)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8">
+      <c r="A23" s="9">
         <f>IF(C23="","","AYN-"&amp;UPPER(LEFT(E23,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="10">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="11">
         <f>IF(I23="","",IF(J23="BDT",I23,IF(J23="USD",I23*USD_BDT,IF(J23="RMB",I23*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="10" t="n"/>
-      <c r="O23" s="10">
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="11">
         <f>IF(K23="","",K23+IFERROR(L23,0)+(K23*IF(M23="",CUSTOMS_PCT,M23))+IF(N23="",MISC_FEE,N23))</f>
         <v/>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="11">
         <f>IF(O23="","",ROUND(O23*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="11">
         <f>IF(P23="","",P23-O23)</f>
         <v/>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="12">
         <f>IF(OR(P23="",P23=0),"",Q23/P23)</f>
         <v/>
       </c>
-      <c r="S23" s="8" t="n"/>
-      <c r="T23" s="8" t="n"/>
-      <c r="U23" s="8" t="n"/>
-      <c r="V23" s="8" t="n"/>
-      <c r="W23" s="8" t="n"/>
-      <c r="X23" s="12">
-        <f>IF(COUNT(S23:W23)&lt;5,"",(S23*W_TREND+T23*W_BRAND+U23*W_DEMAND+V23*W_COMPETITION+W23*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="8">
-        <f>IF(X23="","",IF(X23&gt;=BUY_THRESHOLD,"Buy",IF(X23&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z23" s="8" t="n"/>
-      <c r="AA23" s="8" t="n"/>
-      <c r="AB23" s="8" t="n"/>
-      <c r="AC23" s="8" t="n"/>
-      <c r="AD23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="9" t="n"/>
+      <c r="AC23" s="13">
+        <f>IF(COUNT(S23:AB23)&lt;10,"",(S23*W_FEMININE+T23*W_TREND+U23*W_AESTHETIC+V23*W_STYLE+W23*W_LIGHT+X23*W_REELS+Y23*W_GIFT+Z23*W_PRICEFIT+AA23*W_DEMAND+AB23*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="9">
+        <f>IF(P23="","",IF(P23&gt;HARD_REJECT_PRICE,"Reject",IF(P23&gt;MAX_PRICE,"Price Review",IF(AC23="","",IF(AND(AC23&gt;=BUY_THRESHOLD,OR(AB23&lt;=2,U23&lt;=2)),"Maybe",IF(AC23&gt;=BUY_THRESHOLD,"Buy",IF(AC23&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="9" t="n"/>
+      <c r="AF23" s="9" t="n"/>
+      <c r="AG23" s="9" t="n"/>
+      <c r="AH23" s="9" t="n"/>
+      <c r="AI23" s="10" t="n"/>
+      <c r="AJ23">
+        <f>IF(AC23="",-9999-ROW()*0.0000001,AC23-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK23">
+        <f>IF(OR(AC23="",P23="",P23&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC23-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL23">
+        <f>IF(AC23="",-9999-ROW()*0.0000001,X23*1000+AC23-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM23">
+        <f>IF(AC23="",-9999-ROW()*0.0000001,Y23*1000+AC23-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN23">
+        <f>IF(AND(OR(AD23="Maybe",AD23="Price Review"),AG23&lt;&gt;"Approved",AG23&lt;&gt;"Rejected"),IF(AC23="",0,AC23)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <f>IF(C24="","","AYN-"&amp;UPPER(LEFT(E24,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="15">
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="16">
         <f>IF(I24="","",IF(J24="BDT",I24,IF(J24="USD",I24*USD_BDT,IF(J24="RMB",I24*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="16" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15">
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16">
         <f>IF(K24="","",K24+IFERROR(L24,0)+(K24*IF(M24="",CUSTOMS_PCT,M24))+IF(N24="",MISC_FEE,N24))</f>
         <v/>
       </c>
-      <c r="P24" s="15">
+      <c r="P24" s="16">
         <f>IF(O24="","",ROUND(O24*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q24" s="15">
+      <c r="Q24" s="16">
         <f>IF(P24="","",P24-O24)</f>
         <v/>
       </c>
-      <c r="R24" s="16">
+      <c r="R24" s="17">
         <f>IF(OR(P24="",P24=0),"",Q24/P24)</f>
         <v/>
       </c>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="13" t="n"/>
-      <c r="U24" s="13" t="n"/>
-      <c r="V24" s="13" t="n"/>
-      <c r="W24" s="13" t="n"/>
-      <c r="X24" s="17">
-        <f>IF(COUNT(S24:W24)&lt;5,"",(S24*W_TREND+T24*W_BRAND+U24*W_DEMAND+V24*W_COMPETITION+W24*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y24" s="13">
-        <f>IF(X24="","",IF(X24&gt;=BUY_THRESHOLD,"Buy",IF(X24&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z24" s="13" t="n"/>
-      <c r="AA24" s="13" t="n"/>
-      <c r="AB24" s="13" t="n"/>
-      <c r="AC24" s="13" t="n"/>
-      <c r="AD24" s="14" t="n"/>
+      <c r="S24" s="14" t="n"/>
+      <c r="T24" s="14" t="n"/>
+      <c r="U24" s="14" t="n"/>
+      <c r="V24" s="14" t="n"/>
+      <c r="W24" s="14" t="n"/>
+      <c r="X24" s="14" t="n"/>
+      <c r="Y24" s="14" t="n"/>
+      <c r="Z24" s="14" t="n"/>
+      <c r="AA24" s="14" t="n"/>
+      <c r="AB24" s="14" t="n"/>
+      <c r="AC24" s="18">
+        <f>IF(COUNT(S24:AB24)&lt;10,"",(S24*W_FEMININE+T24*W_TREND+U24*W_AESTHETIC+V24*W_STYLE+W24*W_LIGHT+X24*W_REELS+Y24*W_GIFT+Z24*W_PRICEFIT+AA24*W_DEMAND+AB24*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="14">
+        <f>IF(P24="","",IF(P24&gt;HARD_REJECT_PRICE,"Reject",IF(P24&gt;MAX_PRICE,"Price Review",IF(AC24="","",IF(AND(AC24&gt;=BUY_THRESHOLD,OR(AB24&lt;=2,U24&lt;=2)),"Maybe",IF(AC24&gt;=BUY_THRESHOLD,"Buy",IF(AC24&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="14" t="n"/>
+      <c r="AF24" s="14" t="n"/>
+      <c r="AG24" s="14" t="n"/>
+      <c r="AH24" s="14" t="n"/>
+      <c r="AI24" s="15" t="n"/>
+      <c r="AJ24">
+        <f>IF(AC24="",-9999-ROW()*0.0000001,AC24-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK24">
+        <f>IF(OR(AC24="",P24="",P24&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC24-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL24">
+        <f>IF(AC24="",-9999-ROW()*0.0000001,X24*1000+AC24-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM24">
+        <f>IF(AC24="",-9999-ROW()*0.0000001,Y24*1000+AC24-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN24">
+        <f>IF(AND(OR(AD24="Maybe",AD24="Price Review"),AG24&lt;&gt;"Approved",AG24&lt;&gt;"Rejected"),IF(AC24="",0,AC24)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8">
+      <c r="A25" s="9">
         <f>IF(C25="","","AYN-"&amp;UPPER(LEFT(E25,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="10">
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="11">
         <f>IF(I25="","",IF(J25="BDT",I25,IF(J25="USD",I25*USD_BDT,IF(J25="RMB",I25*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L25" s="10" t="n"/>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="10" t="n"/>
-      <c r="O25" s="10">
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="11">
         <f>IF(K25="","",K25+IFERROR(L25,0)+(K25*IF(M25="",CUSTOMS_PCT,M25))+IF(N25="",MISC_FEE,N25))</f>
         <v/>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="11">
         <f>IF(O25="","",ROUND(O25*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q25" s="10">
+      <c r="Q25" s="11">
         <f>IF(P25="","",P25-O25)</f>
         <v/>
       </c>
-      <c r="R25" s="11">
+      <c r="R25" s="12">
         <f>IF(OR(P25="",P25=0),"",Q25/P25)</f>
         <v/>
       </c>
-      <c r="S25" s="8" t="n"/>
-      <c r="T25" s="8" t="n"/>
-      <c r="U25" s="8" t="n"/>
-      <c r="V25" s="8" t="n"/>
-      <c r="W25" s="8" t="n"/>
-      <c r="X25" s="12">
-        <f>IF(COUNT(S25:W25)&lt;5,"",(S25*W_TREND+T25*W_BRAND+U25*W_DEMAND+V25*W_COMPETITION+W25*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y25" s="8">
-        <f>IF(X25="","",IF(X25&gt;=BUY_THRESHOLD,"Buy",IF(X25&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z25" s="8" t="n"/>
-      <c r="AA25" s="8" t="n"/>
-      <c r="AB25" s="8" t="n"/>
-      <c r="AC25" s="8" t="n"/>
-      <c r="AD25" s="9" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="9" t="n"/>
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="9" t="n"/>
+      <c r="AA25" s="9" t="n"/>
+      <c r="AB25" s="9" t="n"/>
+      <c r="AC25" s="13">
+        <f>IF(COUNT(S25:AB25)&lt;10,"",(S25*W_FEMININE+T25*W_TREND+U25*W_AESTHETIC+V25*W_STYLE+W25*W_LIGHT+X25*W_REELS+Y25*W_GIFT+Z25*W_PRICEFIT+AA25*W_DEMAND+AB25*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="9">
+        <f>IF(P25="","",IF(P25&gt;HARD_REJECT_PRICE,"Reject",IF(P25&gt;MAX_PRICE,"Price Review",IF(AC25="","",IF(AND(AC25&gt;=BUY_THRESHOLD,OR(AB25&lt;=2,U25&lt;=2)),"Maybe",IF(AC25&gt;=BUY_THRESHOLD,"Buy",IF(AC25&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="9" t="n"/>
+      <c r="AF25" s="9" t="n"/>
+      <c r="AG25" s="9" t="n"/>
+      <c r="AH25" s="9" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25">
+        <f>IF(AC25="",-9999-ROW()*0.0000001,AC25-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK25">
+        <f>IF(OR(AC25="",P25="",P25&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC25-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL25">
+        <f>IF(AC25="",-9999-ROW()*0.0000001,X25*1000+AC25-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM25">
+        <f>IF(AC25="",-9999-ROW()*0.0000001,Y25*1000+AC25-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN25">
+        <f>IF(AND(OR(AD25="Maybe",AD25="Price Review"),AG25&lt;&gt;"Approved",AG25&lt;&gt;"Rejected"),IF(AC25="",0,AC25)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <f>IF(C26="","","AYN-"&amp;UPPER(LEFT(E26,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="15">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="16">
         <f>IF(I26="","",IF(J26="BDT",I26,IF(J26="USD",I26*USD_BDT,IF(J26="RMB",I26*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="16" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15">
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="17" t="n"/>
+      <c r="N26" s="16" t="n"/>
+      <c r="O26" s="16">
         <f>IF(K26="","",K26+IFERROR(L26,0)+(K26*IF(M26="",CUSTOMS_PCT,M26))+IF(N26="",MISC_FEE,N26))</f>
         <v/>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="16">
         <f>IF(O26="","",ROUND(O26*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q26" s="15">
+      <c r="Q26" s="16">
         <f>IF(P26="","",P26-O26)</f>
         <v/>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="17">
         <f>IF(OR(P26="",P26=0),"",Q26/P26)</f>
         <v/>
       </c>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="13" t="n"/>
-      <c r="U26" s="13" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="13" t="n"/>
-      <c r="X26" s="17">
-        <f>IF(COUNT(S26:W26)&lt;5,"",(S26*W_TREND+T26*W_BRAND+U26*W_DEMAND+V26*W_COMPETITION+W26*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y26" s="13">
-        <f>IF(X26="","",IF(X26&gt;=BUY_THRESHOLD,"Buy",IF(X26&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z26" s="13" t="n"/>
-      <c r="AA26" s="13" t="n"/>
-      <c r="AB26" s="13" t="n"/>
-      <c r="AC26" s="13" t="n"/>
-      <c r="AD26" s="14" t="n"/>
+      <c r="S26" s="14" t="n"/>
+      <c r="T26" s="14" t="n"/>
+      <c r="U26" s="14" t="n"/>
+      <c r="V26" s="14" t="n"/>
+      <c r="W26" s="14" t="n"/>
+      <c r="X26" s="14" t="n"/>
+      <c r="Y26" s="14" t="n"/>
+      <c r="Z26" s="14" t="n"/>
+      <c r="AA26" s="14" t="n"/>
+      <c r="AB26" s="14" t="n"/>
+      <c r="AC26" s="18">
+        <f>IF(COUNT(S26:AB26)&lt;10,"",(S26*W_FEMININE+T26*W_TREND+U26*W_AESTHETIC+V26*W_STYLE+W26*W_LIGHT+X26*W_REELS+Y26*W_GIFT+Z26*W_PRICEFIT+AA26*W_DEMAND+AB26*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="14">
+        <f>IF(P26="","",IF(P26&gt;HARD_REJECT_PRICE,"Reject",IF(P26&gt;MAX_PRICE,"Price Review",IF(AC26="","",IF(AND(AC26&gt;=BUY_THRESHOLD,OR(AB26&lt;=2,U26&lt;=2)),"Maybe",IF(AC26&gt;=BUY_THRESHOLD,"Buy",IF(AC26&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="14" t="n"/>
+      <c r="AF26" s="14" t="n"/>
+      <c r="AG26" s="14" t="n"/>
+      <c r="AH26" s="14" t="n"/>
+      <c r="AI26" s="15" t="n"/>
+      <c r="AJ26">
+        <f>IF(AC26="",-9999-ROW()*0.0000001,AC26-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK26">
+        <f>IF(OR(AC26="",P26="",P26&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC26-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL26">
+        <f>IF(AC26="",-9999-ROW()*0.0000001,X26*1000+AC26-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM26">
+        <f>IF(AC26="",-9999-ROW()*0.0000001,Y26*1000+AC26-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN26">
+        <f>IF(AND(OR(AD26="Maybe",AD26="Price Review"),AG26&lt;&gt;"Approved",AG26&lt;&gt;"Rejected"),IF(AC26="",0,AC26)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="8">
+      <c r="A27" s="9">
         <f>IF(C27="","","AYN-"&amp;UPPER(LEFT(E27,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="10">
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="11">
         <f>IF(I27="","",IF(J27="BDT",I27,IF(J27="USD",I27*USD_BDT,IF(J27="RMB",I27*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10">
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11">
         <f>IF(K27="","",K27+IFERROR(L27,0)+(K27*IF(M27="",CUSTOMS_PCT,M27))+IF(N27="",MISC_FEE,N27))</f>
         <v/>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="11">
         <f>IF(O27="","",ROUND(O27*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="11">
         <f>IF(P27="","",P27-O27)</f>
         <v/>
       </c>
-      <c r="R27" s="11">
+      <c r="R27" s="12">
         <f>IF(OR(P27="",P27=0),"",Q27/P27)</f>
         <v/>
       </c>
-      <c r="S27" s="8" t="n"/>
-      <c r="T27" s="8" t="n"/>
-      <c r="U27" s="8" t="n"/>
-      <c r="V27" s="8" t="n"/>
-      <c r="W27" s="8" t="n"/>
-      <c r="X27" s="12">
-        <f>IF(COUNT(S27:W27)&lt;5,"",(S27*W_TREND+T27*W_BRAND+U27*W_DEMAND+V27*W_COMPETITION+W27*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y27" s="8">
-        <f>IF(X27="","",IF(X27&gt;=BUY_THRESHOLD,"Buy",IF(X27&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z27" s="8" t="n"/>
-      <c r="AA27" s="8" t="n"/>
-      <c r="AB27" s="8" t="n"/>
-      <c r="AC27" s="8" t="n"/>
-      <c r="AD27" s="9" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="9" t="n"/>
+      <c r="AA27" s="9" t="n"/>
+      <c r="AB27" s="9" t="n"/>
+      <c r="AC27" s="13">
+        <f>IF(COUNT(S27:AB27)&lt;10,"",(S27*W_FEMININE+T27*W_TREND+U27*W_AESTHETIC+V27*W_STYLE+W27*W_LIGHT+X27*W_REELS+Y27*W_GIFT+Z27*W_PRICEFIT+AA27*W_DEMAND+AB27*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="9">
+        <f>IF(P27="","",IF(P27&gt;HARD_REJECT_PRICE,"Reject",IF(P27&gt;MAX_PRICE,"Price Review",IF(AC27="","",IF(AND(AC27&gt;=BUY_THRESHOLD,OR(AB27&lt;=2,U27&lt;=2)),"Maybe",IF(AC27&gt;=BUY_THRESHOLD,"Buy",IF(AC27&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="9" t="n"/>
+      <c r="AF27" s="9" t="n"/>
+      <c r="AG27" s="9" t="n"/>
+      <c r="AH27" s="9" t="n"/>
+      <c r="AI27" s="10" t="n"/>
+      <c r="AJ27">
+        <f>IF(AC27="",-9999-ROW()*0.0000001,AC27-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK27">
+        <f>IF(OR(AC27="",P27="",P27&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC27-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL27">
+        <f>IF(AC27="",-9999-ROW()*0.0000001,X27*1000+AC27-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM27">
+        <f>IF(AC27="",-9999-ROW()*0.0000001,Y27*1000+AC27-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN27">
+        <f>IF(AND(OR(AD27="Maybe",AD27="Price Review"),AG27&lt;&gt;"Approved",AG27&lt;&gt;"Rejected"),IF(AC27="",0,AC27)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <f>IF(C28="","","AYN-"&amp;UPPER(LEFT(E28,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B28" s="14" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="15">
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="16">
         <f>IF(I28="","",IF(J28="BDT",I28,IF(J28="USD",I28*USD_BDT,IF(J28="RMB",I28*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="16" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15">
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16">
         <f>IF(K28="","",K28+IFERROR(L28,0)+(K28*IF(M28="",CUSTOMS_PCT,M28))+IF(N28="",MISC_FEE,N28))</f>
         <v/>
       </c>
-      <c r="P28" s="15">
+      <c r="P28" s="16">
         <f>IF(O28="","",ROUND(O28*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q28" s="15">
+      <c r="Q28" s="16">
         <f>IF(P28="","",P28-O28)</f>
         <v/>
       </c>
-      <c r="R28" s="16">
+      <c r="R28" s="17">
         <f>IF(OR(P28="",P28=0),"",Q28/P28)</f>
         <v/>
       </c>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="13" t="n"/>
-      <c r="U28" s="13" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="13" t="n"/>
-      <c r="X28" s="17">
-        <f>IF(COUNT(S28:W28)&lt;5,"",(S28*W_TREND+T28*W_BRAND+U28*W_DEMAND+V28*W_COMPETITION+W28*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y28" s="13">
-        <f>IF(X28="","",IF(X28&gt;=BUY_THRESHOLD,"Buy",IF(X28&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z28" s="13" t="n"/>
-      <c r="AA28" s="13" t="n"/>
-      <c r="AB28" s="13" t="n"/>
-      <c r="AC28" s="13" t="n"/>
-      <c r="AD28" s="14" t="n"/>
+      <c r="S28" s="14" t="n"/>
+      <c r="T28" s="14" t="n"/>
+      <c r="U28" s="14" t="n"/>
+      <c r="V28" s="14" t="n"/>
+      <c r="W28" s="14" t="n"/>
+      <c r="X28" s="14" t="n"/>
+      <c r="Y28" s="14" t="n"/>
+      <c r="Z28" s="14" t="n"/>
+      <c r="AA28" s="14" t="n"/>
+      <c r="AB28" s="14" t="n"/>
+      <c r="AC28" s="18">
+        <f>IF(COUNT(S28:AB28)&lt;10,"",(S28*W_FEMININE+T28*W_TREND+U28*W_AESTHETIC+V28*W_STYLE+W28*W_LIGHT+X28*W_REELS+Y28*W_GIFT+Z28*W_PRICEFIT+AA28*W_DEMAND+AB28*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="14">
+        <f>IF(P28="","",IF(P28&gt;HARD_REJECT_PRICE,"Reject",IF(P28&gt;MAX_PRICE,"Price Review",IF(AC28="","",IF(AND(AC28&gt;=BUY_THRESHOLD,OR(AB28&lt;=2,U28&lt;=2)),"Maybe",IF(AC28&gt;=BUY_THRESHOLD,"Buy",IF(AC28&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="14" t="n"/>
+      <c r="AF28" s="14" t="n"/>
+      <c r="AG28" s="14" t="n"/>
+      <c r="AH28" s="14" t="n"/>
+      <c r="AI28" s="15" t="n"/>
+      <c r="AJ28">
+        <f>IF(AC28="",-9999-ROW()*0.0000001,AC28-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK28">
+        <f>IF(OR(AC28="",P28="",P28&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC28-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL28">
+        <f>IF(AC28="",-9999-ROW()*0.0000001,X28*1000+AC28-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM28">
+        <f>IF(AC28="",-9999-ROW()*0.0000001,Y28*1000+AC28-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN28">
+        <f>IF(AND(OR(AD28="Maybe",AD28="Price Review"),AG28&lt;&gt;"Approved",AG28&lt;&gt;"Rejected"),IF(AC28="",0,AC28)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8">
+      <c r="A29" s="9">
         <f>IF(C29="","","AYN-"&amp;UPPER(LEFT(E29,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="10">
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="11">
         <f>IF(I29="","",IF(J29="BDT",I29,IF(J29="USD",I29*USD_BDT,IF(J29="RMB",I29*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="10" t="n"/>
-      <c r="O29" s="10">
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="11">
         <f>IF(K29="","",K29+IFERROR(L29,0)+(K29*IF(M29="",CUSTOMS_PCT,M29))+IF(N29="",MISC_FEE,N29))</f>
         <v/>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="11">
         <f>IF(O29="","",ROUND(O29*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="11">
         <f>IF(P29="","",P29-O29)</f>
         <v/>
       </c>
-      <c r="R29" s="11">
+      <c r="R29" s="12">
         <f>IF(OR(P29="",P29=0),"",Q29/P29)</f>
         <v/>
       </c>
-      <c r="S29" s="8" t="n"/>
-      <c r="T29" s="8" t="n"/>
-      <c r="U29" s="8" t="n"/>
-      <c r="V29" s="8" t="n"/>
-      <c r="W29" s="8" t="n"/>
-      <c r="X29" s="12">
-        <f>IF(COUNT(S29:W29)&lt;5,"",(S29*W_TREND+T29*W_BRAND+U29*W_DEMAND+V29*W_COMPETITION+W29*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y29" s="8">
-        <f>IF(X29="","",IF(X29&gt;=BUY_THRESHOLD,"Buy",IF(X29&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z29" s="8" t="n"/>
-      <c r="AA29" s="8" t="n"/>
-      <c r="AB29" s="8" t="n"/>
-      <c r="AC29" s="8" t="n"/>
-      <c r="AD29" s="9" t="n"/>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="9" t="n"/>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="9" t="n"/>
+      <c r="Y29" s="9" t="n"/>
+      <c r="Z29" s="9" t="n"/>
+      <c r="AA29" s="9" t="n"/>
+      <c r="AB29" s="9" t="n"/>
+      <c r="AC29" s="13">
+        <f>IF(COUNT(S29:AB29)&lt;10,"",(S29*W_FEMININE+T29*W_TREND+U29*W_AESTHETIC+V29*W_STYLE+W29*W_LIGHT+X29*W_REELS+Y29*W_GIFT+Z29*W_PRICEFIT+AA29*W_DEMAND+AB29*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="9">
+        <f>IF(P29="","",IF(P29&gt;HARD_REJECT_PRICE,"Reject",IF(P29&gt;MAX_PRICE,"Price Review",IF(AC29="","",IF(AND(AC29&gt;=BUY_THRESHOLD,OR(AB29&lt;=2,U29&lt;=2)),"Maybe",IF(AC29&gt;=BUY_THRESHOLD,"Buy",IF(AC29&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="9" t="n"/>
+      <c r="AF29" s="9" t="n"/>
+      <c r="AG29" s="9" t="n"/>
+      <c r="AH29" s="9" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29">
+        <f>IF(AC29="",-9999-ROW()*0.0000001,AC29-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK29">
+        <f>IF(OR(AC29="",P29="",P29&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC29-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL29">
+        <f>IF(AC29="",-9999-ROW()*0.0000001,X29*1000+AC29-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM29">
+        <f>IF(AC29="",-9999-ROW()*0.0000001,Y29*1000+AC29-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN29">
+        <f>IF(AND(OR(AD29="Maybe",AD29="Price Review"),AG29&lt;&gt;"Approved",AG29&lt;&gt;"Rejected"),IF(AC29="",0,AC29)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <f>IF(C30="","","AYN-"&amp;UPPER(LEFT(E30,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B30" s="14" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="15">
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="16">
         <f>IF(I30="","",IF(J30="BDT",I30,IF(J30="USD",I30*USD_BDT,IF(J30="RMB",I30*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15">
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="17" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16">
         <f>IF(K30="","",K30+IFERROR(L30,0)+(K30*IF(M30="",CUSTOMS_PCT,M30))+IF(N30="",MISC_FEE,N30))</f>
         <v/>
       </c>
-      <c r="P30" s="15">
+      <c r="P30" s="16">
         <f>IF(O30="","",ROUND(O30*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q30" s="15">
+      <c r="Q30" s="16">
         <f>IF(P30="","",P30-O30)</f>
         <v/>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="17">
         <f>IF(OR(P30="",P30=0),"",Q30/P30)</f>
         <v/>
       </c>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="13" t="n"/>
-      <c r="U30" s="13" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="13" t="n"/>
-      <c r="X30" s="17">
-        <f>IF(COUNT(S30:W30)&lt;5,"",(S30*W_TREND+T30*W_BRAND+U30*W_DEMAND+V30*W_COMPETITION+W30*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y30" s="13">
-        <f>IF(X30="","",IF(X30&gt;=BUY_THRESHOLD,"Buy",IF(X30&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z30" s="13" t="n"/>
-      <c r="AA30" s="13" t="n"/>
-      <c r="AB30" s="13" t="n"/>
-      <c r="AC30" s="13" t="n"/>
-      <c r="AD30" s="14" t="n"/>
+      <c r="S30" s="14" t="n"/>
+      <c r="T30" s="14" t="n"/>
+      <c r="U30" s="14" t="n"/>
+      <c r="V30" s="14" t="n"/>
+      <c r="W30" s="14" t="n"/>
+      <c r="X30" s="14" t="n"/>
+      <c r="Y30" s="14" t="n"/>
+      <c r="Z30" s="14" t="n"/>
+      <c r="AA30" s="14" t="n"/>
+      <c r="AB30" s="14" t="n"/>
+      <c r="AC30" s="18">
+        <f>IF(COUNT(S30:AB30)&lt;10,"",(S30*W_FEMININE+T30*W_TREND+U30*W_AESTHETIC+V30*W_STYLE+W30*W_LIGHT+X30*W_REELS+Y30*W_GIFT+Z30*W_PRICEFIT+AA30*W_DEMAND+AB30*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="14">
+        <f>IF(P30="","",IF(P30&gt;HARD_REJECT_PRICE,"Reject",IF(P30&gt;MAX_PRICE,"Price Review",IF(AC30="","",IF(AND(AC30&gt;=BUY_THRESHOLD,OR(AB30&lt;=2,U30&lt;=2)),"Maybe",IF(AC30&gt;=BUY_THRESHOLD,"Buy",IF(AC30&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="14" t="n"/>
+      <c r="AF30" s="14" t="n"/>
+      <c r="AG30" s="14" t="n"/>
+      <c r="AH30" s="14" t="n"/>
+      <c r="AI30" s="15" t="n"/>
+      <c r="AJ30">
+        <f>IF(AC30="",-9999-ROW()*0.0000001,AC30-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK30">
+        <f>IF(OR(AC30="",P30="",P30&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC30-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL30">
+        <f>IF(AC30="",-9999-ROW()*0.0000001,X30*1000+AC30-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM30">
+        <f>IF(AC30="",-9999-ROW()*0.0000001,Y30*1000+AC30-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN30">
+        <f>IF(AND(OR(AD30="Maybe",AD30="Price Review"),AG30&lt;&gt;"Approved",AG30&lt;&gt;"Rejected"),IF(AC30="",0,AC30)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <f>IF(C31="","","AYN-"&amp;UPPER(LEFT(E31,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="10">
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="11">
         <f>IF(I31="","",IF(J31="BDT",I31,IF(J31="USD",I31*USD_BDT,IF(J31="RMB",I31*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10">
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11">
         <f>IF(K31="","",K31+IFERROR(L31,0)+(K31*IF(M31="",CUSTOMS_PCT,M31))+IF(N31="",MISC_FEE,N31))</f>
         <v/>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="11">
         <f>IF(O31="","",ROUND(O31*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q31" s="10">
+      <c r="Q31" s="11">
         <f>IF(P31="","",P31-O31)</f>
         <v/>
       </c>
-      <c r="R31" s="11">
+      <c r="R31" s="12">
         <f>IF(OR(P31="",P31=0),"",Q31/P31)</f>
         <v/>
       </c>
-      <c r="S31" s="8" t="n"/>
-      <c r="T31" s="8" t="n"/>
-      <c r="U31" s="8" t="n"/>
-      <c r="V31" s="8" t="n"/>
-      <c r="W31" s="8" t="n"/>
-      <c r="X31" s="12">
-        <f>IF(COUNT(S31:W31)&lt;5,"",(S31*W_TREND+T31*W_BRAND+U31*W_DEMAND+V31*W_COMPETITION+W31*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y31" s="8">
-        <f>IF(X31="","",IF(X31&gt;=BUY_THRESHOLD,"Buy",IF(X31&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z31" s="8" t="n"/>
-      <c r="AA31" s="8" t="n"/>
-      <c r="AB31" s="8" t="n"/>
-      <c r="AC31" s="8" t="n"/>
-      <c r="AD31" s="9" t="n"/>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
+      <c r="Y31" s="9" t="n"/>
+      <c r="Z31" s="9" t="n"/>
+      <c r="AA31" s="9" t="n"/>
+      <c r="AB31" s="9" t="n"/>
+      <c r="AC31" s="13">
+        <f>IF(COUNT(S31:AB31)&lt;10,"",(S31*W_FEMININE+T31*W_TREND+U31*W_AESTHETIC+V31*W_STYLE+W31*W_LIGHT+X31*W_REELS+Y31*W_GIFT+Z31*W_PRICEFIT+AA31*W_DEMAND+AB31*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="9">
+        <f>IF(P31="","",IF(P31&gt;HARD_REJECT_PRICE,"Reject",IF(P31&gt;MAX_PRICE,"Price Review",IF(AC31="","",IF(AND(AC31&gt;=BUY_THRESHOLD,OR(AB31&lt;=2,U31&lt;=2)),"Maybe",IF(AC31&gt;=BUY_THRESHOLD,"Buy",IF(AC31&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="9" t="n"/>
+      <c r="AF31" s="9" t="n"/>
+      <c r="AG31" s="9" t="n"/>
+      <c r="AH31" s="9" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31">
+        <f>IF(AC31="",-9999-ROW()*0.0000001,AC31-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK31">
+        <f>IF(OR(AC31="",P31="",P31&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC31-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL31">
+        <f>IF(AC31="",-9999-ROW()*0.0000001,X31*1000+AC31-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM31">
+        <f>IF(AC31="",-9999-ROW()*0.0000001,Y31*1000+AC31-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN31">
+        <f>IF(AND(OR(AD31="Maybe",AD31="Price Review"),AG31&lt;&gt;"Approved",AG31&lt;&gt;"Rejected"),IF(AC31="",0,AC31)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="13">
+      <c r="A32" s="14">
         <f>IF(C32="","","AYN-"&amp;UPPER(LEFT(E32,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="15">
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="16">
         <f>IF(I32="","",IF(J32="BDT",I32,IF(J32="USD",I32*USD_BDT,IF(J32="RMB",I32*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="16" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15">
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="17" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="16">
         <f>IF(K32="","",K32+IFERROR(L32,0)+(K32*IF(M32="",CUSTOMS_PCT,M32))+IF(N32="",MISC_FEE,N32))</f>
         <v/>
       </c>
-      <c r="P32" s="15">
+      <c r="P32" s="16">
         <f>IF(O32="","",ROUND(O32*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q32" s="16">
         <f>IF(P32="","",P32-O32)</f>
         <v/>
       </c>
-      <c r="R32" s="16">
+      <c r="R32" s="17">
         <f>IF(OR(P32="",P32=0),"",Q32/P32)</f>
         <v/>
       </c>
-      <c r="S32" s="13" t="n"/>
-      <c r="T32" s="13" t="n"/>
-      <c r="U32" s="13" t="n"/>
-      <c r="V32" s="13" t="n"/>
-      <c r="W32" s="13" t="n"/>
-      <c r="X32" s="17">
-        <f>IF(COUNT(S32:W32)&lt;5,"",(S32*W_TREND+T32*W_BRAND+U32*W_DEMAND+V32*W_COMPETITION+W32*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y32" s="13">
-        <f>IF(X32="","",IF(X32&gt;=BUY_THRESHOLD,"Buy",IF(X32&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z32" s="13" t="n"/>
-      <c r="AA32" s="13" t="n"/>
-      <c r="AB32" s="13" t="n"/>
-      <c r="AC32" s="13" t="n"/>
-      <c r="AD32" s="14" t="n"/>
+      <c r="S32" s="14" t="n"/>
+      <c r="T32" s="14" t="n"/>
+      <c r="U32" s="14" t="n"/>
+      <c r="V32" s="14" t="n"/>
+      <c r="W32" s="14" t="n"/>
+      <c r="X32" s="14" t="n"/>
+      <c r="Y32" s="14" t="n"/>
+      <c r="Z32" s="14" t="n"/>
+      <c r="AA32" s="14" t="n"/>
+      <c r="AB32" s="14" t="n"/>
+      <c r="AC32" s="18">
+        <f>IF(COUNT(S32:AB32)&lt;10,"",(S32*W_FEMININE+T32*W_TREND+U32*W_AESTHETIC+V32*W_STYLE+W32*W_LIGHT+X32*W_REELS+Y32*W_GIFT+Z32*W_PRICEFIT+AA32*W_DEMAND+AB32*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD32" s="14">
+        <f>IF(P32="","",IF(P32&gt;HARD_REJECT_PRICE,"Reject",IF(P32&gt;MAX_PRICE,"Price Review",IF(AC32="","",IF(AND(AC32&gt;=BUY_THRESHOLD,OR(AB32&lt;=2,U32&lt;=2)),"Maybe",IF(AC32&gt;=BUY_THRESHOLD,"Buy",IF(AC32&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="14" t="n"/>
+      <c r="AF32" s="14" t="n"/>
+      <c r="AG32" s="14" t="n"/>
+      <c r="AH32" s="14" t="n"/>
+      <c r="AI32" s="15" t="n"/>
+      <c r="AJ32">
+        <f>IF(AC32="",-9999-ROW()*0.0000001,AC32-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK32">
+        <f>IF(OR(AC32="",P32="",P32&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC32-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL32">
+        <f>IF(AC32="",-9999-ROW()*0.0000001,X32*1000+AC32-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM32">
+        <f>IF(AC32="",-9999-ROW()*0.0000001,Y32*1000+AC32-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN32">
+        <f>IF(AND(OR(AD32="Maybe",AD32="Price Review"),AG32&lt;&gt;"Approved",AG32&lt;&gt;"Rejected"),IF(AC32="",0,AC32)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="8">
+      <c r="A33" s="9">
         <f>IF(C33="","","AYN-"&amp;UPPER(LEFT(E33,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="10">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="11">
         <f>IF(I33="","",IF(J33="BDT",I33,IF(J33="USD",I33*USD_BDT,IF(J33="RMB",I33*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10">
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11">
         <f>IF(K33="","",K33+IFERROR(L33,0)+(K33*IF(M33="",CUSTOMS_PCT,M33))+IF(N33="",MISC_FEE,N33))</f>
         <v/>
       </c>
-      <c r="P33" s="10">
+      <c r="P33" s="11">
         <f>IF(O33="","",ROUND(O33*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q33" s="10">
+      <c r="Q33" s="11">
         <f>IF(P33="","",P33-O33)</f>
         <v/>
       </c>
-      <c r="R33" s="11">
+      <c r="R33" s="12">
         <f>IF(OR(P33="",P33=0),"",Q33/P33)</f>
         <v/>
       </c>
-      <c r="S33" s="8" t="n"/>
-      <c r="T33" s="8" t="n"/>
-      <c r="U33" s="8" t="n"/>
-      <c r="V33" s="8" t="n"/>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="12">
-        <f>IF(COUNT(S33:W33)&lt;5,"",(S33*W_TREND+T33*W_BRAND+U33*W_DEMAND+V33*W_COMPETITION+W33*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y33" s="8">
-        <f>IF(X33="","",IF(X33&gt;=BUY_THRESHOLD,"Buy",IF(X33&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z33" s="8" t="n"/>
-      <c r="AA33" s="8" t="n"/>
-      <c r="AB33" s="8" t="n"/>
-      <c r="AC33" s="8" t="n"/>
-      <c r="AD33" s="9" t="n"/>
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="9" t="n"/>
+      <c r="Y33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n"/>
+      <c r="AA33" s="9" t="n"/>
+      <c r="AB33" s="9" t="n"/>
+      <c r="AC33" s="13">
+        <f>IF(COUNT(S33:AB33)&lt;10,"",(S33*W_FEMININE+T33*W_TREND+U33*W_AESTHETIC+V33*W_STYLE+W33*W_LIGHT+X33*W_REELS+Y33*W_GIFT+Z33*W_PRICEFIT+AA33*W_DEMAND+AB33*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="9">
+        <f>IF(P33="","",IF(P33&gt;HARD_REJECT_PRICE,"Reject",IF(P33&gt;MAX_PRICE,"Price Review",IF(AC33="","",IF(AND(AC33&gt;=BUY_THRESHOLD,OR(AB33&lt;=2,U33&lt;=2)),"Maybe",IF(AC33&gt;=BUY_THRESHOLD,"Buy",IF(AC33&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="9" t="n"/>
+      <c r="AF33" s="9" t="n"/>
+      <c r="AG33" s="9" t="n"/>
+      <c r="AH33" s="9" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33">
+        <f>IF(AC33="",-9999-ROW()*0.0000001,AC33-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK33">
+        <f>IF(OR(AC33="",P33="",P33&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC33-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL33">
+        <f>IF(AC33="",-9999-ROW()*0.0000001,X33*1000+AC33-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM33">
+        <f>IF(AC33="",-9999-ROW()*0.0000001,Y33*1000+AC33-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN33">
+        <f>IF(AND(OR(AD33="Maybe",AD33="Price Review"),AG33&lt;&gt;"Approved",AG33&lt;&gt;"Rejected"),IF(AC33="",0,AC33)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <f>IF(C34="","","AYN-"&amp;UPPER(LEFT(E34,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="15">
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="16">
         <f>IF(I34="","",IF(J34="BDT",I34,IF(J34="USD",I34*USD_BDT,IF(J34="RMB",I34*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="16" t="n"/>
-      <c r="N34" s="15" t="n"/>
-      <c r="O34" s="15">
+      <c r="L34" s="16" t="n"/>
+      <c r="M34" s="17" t="n"/>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16">
         <f>IF(K34="","",K34+IFERROR(L34,0)+(K34*IF(M34="",CUSTOMS_PCT,M34))+IF(N34="",MISC_FEE,N34))</f>
         <v/>
       </c>
-      <c r="P34" s="15">
+      <c r="P34" s="16">
         <f>IF(O34="","",ROUND(O34*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q34" s="15">
+      <c r="Q34" s="16">
         <f>IF(P34="","",P34-O34)</f>
         <v/>
       </c>
-      <c r="R34" s="16">
+      <c r="R34" s="17">
         <f>IF(OR(P34="",P34=0),"",Q34/P34)</f>
         <v/>
       </c>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="13" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
-      <c r="X34" s="17">
-        <f>IF(COUNT(S34:W34)&lt;5,"",(S34*W_TREND+T34*W_BRAND+U34*W_DEMAND+V34*W_COMPETITION+W34*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y34" s="13">
-        <f>IF(X34="","",IF(X34&gt;=BUY_THRESHOLD,"Buy",IF(X34&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z34" s="13" t="n"/>
-      <c r="AA34" s="13" t="n"/>
-      <c r="AB34" s="13" t="n"/>
-      <c r="AC34" s="13" t="n"/>
-      <c r="AD34" s="14" t="n"/>
+      <c r="S34" s="14" t="n"/>
+      <c r="T34" s="14" t="n"/>
+      <c r="U34" s="14" t="n"/>
+      <c r="V34" s="14" t="n"/>
+      <c r="W34" s="14" t="n"/>
+      <c r="X34" s="14" t="n"/>
+      <c r="Y34" s="14" t="n"/>
+      <c r="Z34" s="14" t="n"/>
+      <c r="AA34" s="14" t="n"/>
+      <c r="AB34" s="14" t="n"/>
+      <c r="AC34" s="18">
+        <f>IF(COUNT(S34:AB34)&lt;10,"",(S34*W_FEMININE+T34*W_TREND+U34*W_AESTHETIC+V34*W_STYLE+W34*W_LIGHT+X34*W_REELS+Y34*W_GIFT+Z34*W_PRICEFIT+AA34*W_DEMAND+AB34*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="14">
+        <f>IF(P34="","",IF(P34&gt;HARD_REJECT_PRICE,"Reject",IF(P34&gt;MAX_PRICE,"Price Review",IF(AC34="","",IF(AND(AC34&gt;=BUY_THRESHOLD,OR(AB34&lt;=2,U34&lt;=2)),"Maybe",IF(AC34&gt;=BUY_THRESHOLD,"Buy",IF(AC34&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="14" t="n"/>
+      <c r="AF34" s="14" t="n"/>
+      <c r="AG34" s="14" t="n"/>
+      <c r="AH34" s="14" t="n"/>
+      <c r="AI34" s="15" t="n"/>
+      <c r="AJ34">
+        <f>IF(AC34="",-9999-ROW()*0.0000001,AC34-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK34">
+        <f>IF(OR(AC34="",P34="",P34&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC34-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL34">
+        <f>IF(AC34="",-9999-ROW()*0.0000001,X34*1000+AC34-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM34">
+        <f>IF(AC34="",-9999-ROW()*0.0000001,Y34*1000+AC34-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN34">
+        <f>IF(AND(OR(AD34="Maybe",AD34="Price Review"),AG34&lt;&gt;"Approved",AG34&lt;&gt;"Rejected"),IF(AC34="",0,AC34)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="8">
+      <c r="A35" s="9">
         <f>IF(C35="","","AYN-"&amp;UPPER(LEFT(E35,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="10">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="11">
         <f>IF(I35="","",IF(J35="BDT",I35,IF(J35="USD",I35*USD_BDT,IF(J35="RMB",I35*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L35" s="10" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10">
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="11" t="n"/>
+      <c r="O35" s="11">
         <f>IF(K35="","",K35+IFERROR(L35,0)+(K35*IF(M35="",CUSTOMS_PCT,M35))+IF(N35="",MISC_FEE,N35))</f>
         <v/>
       </c>
-      <c r="P35" s="10">
+      <c r="P35" s="11">
         <f>IF(O35="","",ROUND(O35*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q35" s="10">
+      <c r="Q35" s="11">
         <f>IF(P35="","",P35-O35)</f>
         <v/>
       </c>
-      <c r="R35" s="11">
+      <c r="R35" s="12">
         <f>IF(OR(P35="",P35=0),"",Q35/P35)</f>
         <v/>
       </c>
-      <c r="S35" s="8" t="n"/>
-      <c r="T35" s="8" t="n"/>
-      <c r="U35" s="8" t="n"/>
-      <c r="V35" s="8" t="n"/>
-      <c r="W35" s="8" t="n"/>
-      <c r="X35" s="12">
-        <f>IF(COUNT(S35:W35)&lt;5,"",(S35*W_TREND+T35*W_BRAND+U35*W_DEMAND+V35*W_COMPETITION+W35*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y35" s="8">
-        <f>IF(X35="","",IF(X35&gt;=BUY_THRESHOLD,"Buy",IF(X35&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z35" s="8" t="n"/>
-      <c r="AA35" s="8" t="n"/>
-      <c r="AB35" s="8" t="n"/>
-      <c r="AC35" s="8" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="9" t="n"/>
+      <c r="AA35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n"/>
+      <c r="AC35" s="13">
+        <f>IF(COUNT(S35:AB35)&lt;10,"",(S35*W_FEMININE+T35*W_TREND+U35*W_AESTHETIC+V35*W_STYLE+W35*W_LIGHT+X35*W_REELS+Y35*W_GIFT+Z35*W_PRICEFIT+AA35*W_DEMAND+AB35*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="9">
+        <f>IF(P35="","",IF(P35&gt;HARD_REJECT_PRICE,"Reject",IF(P35&gt;MAX_PRICE,"Price Review",IF(AC35="","",IF(AND(AC35&gt;=BUY_THRESHOLD,OR(AB35&lt;=2,U35&lt;=2)),"Maybe",IF(AC35&gt;=BUY_THRESHOLD,"Buy",IF(AC35&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="9" t="n"/>
+      <c r="AF35" s="9" t="n"/>
+      <c r="AG35" s="9" t="n"/>
+      <c r="AH35" s="9" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35">
+        <f>IF(AC35="",-9999-ROW()*0.0000001,AC35-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK35">
+        <f>IF(OR(AC35="",P35="",P35&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC35-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL35">
+        <f>IF(AC35="",-9999-ROW()*0.0000001,X35*1000+AC35-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM35">
+        <f>IF(AC35="",-9999-ROW()*0.0000001,Y35*1000+AC35-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN35">
+        <f>IF(AND(OR(AD35="Maybe",AD35="Price Review"),AG35&lt;&gt;"Approved",AG35&lt;&gt;"Rejected"),IF(AC35="",0,AC35)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <f>IF(C36="","","AYN-"&amp;UPPER(LEFT(E36,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="15">
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="16">
         <f>IF(I36="","",IF(J36="BDT",I36,IF(J36="USD",I36*USD_BDT,IF(J36="RMB",I36*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="15">
+      <c r="L36" s="16" t="n"/>
+      <c r="M36" s="17" t="n"/>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="16">
         <f>IF(K36="","",K36+IFERROR(L36,0)+(K36*IF(M36="",CUSTOMS_PCT,M36))+IF(N36="",MISC_FEE,N36))</f>
         <v/>
       </c>
-      <c r="P36" s="15">
+      <c r="P36" s="16">
         <f>IF(O36="","",ROUND(O36*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q36" s="15">
+      <c r="Q36" s="16">
         <f>IF(P36="","",P36-O36)</f>
         <v/>
       </c>
-      <c r="R36" s="16">
+      <c r="R36" s="17">
         <f>IF(OR(P36="",P36=0),"",Q36/P36)</f>
         <v/>
       </c>
-      <c r="S36" s="13" t="n"/>
-      <c r="T36" s="13" t="n"/>
-      <c r="U36" s="13" t="n"/>
-      <c r="V36" s="13" t="n"/>
-      <c r="W36" s="13" t="n"/>
-      <c r="X36" s="17">
-        <f>IF(COUNT(S36:W36)&lt;5,"",(S36*W_TREND+T36*W_BRAND+U36*W_DEMAND+V36*W_COMPETITION+W36*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y36" s="13">
-        <f>IF(X36="","",IF(X36&gt;=BUY_THRESHOLD,"Buy",IF(X36&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z36" s="13" t="n"/>
-      <c r="AA36" s="13" t="n"/>
-      <c r="AB36" s="13" t="n"/>
-      <c r="AC36" s="13" t="n"/>
-      <c r="AD36" s="14" t="n"/>
+      <c r="S36" s="14" t="n"/>
+      <c r="T36" s="14" t="n"/>
+      <c r="U36" s="14" t="n"/>
+      <c r="V36" s="14" t="n"/>
+      <c r="W36" s="14" t="n"/>
+      <c r="X36" s="14" t="n"/>
+      <c r="Y36" s="14" t="n"/>
+      <c r="Z36" s="14" t="n"/>
+      <c r="AA36" s="14" t="n"/>
+      <c r="AB36" s="14" t="n"/>
+      <c r="AC36" s="18">
+        <f>IF(COUNT(S36:AB36)&lt;10,"",(S36*W_FEMININE+T36*W_TREND+U36*W_AESTHETIC+V36*W_STYLE+W36*W_LIGHT+X36*W_REELS+Y36*W_GIFT+Z36*W_PRICEFIT+AA36*W_DEMAND+AB36*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="14">
+        <f>IF(P36="","",IF(P36&gt;HARD_REJECT_PRICE,"Reject",IF(P36&gt;MAX_PRICE,"Price Review",IF(AC36="","",IF(AND(AC36&gt;=BUY_THRESHOLD,OR(AB36&lt;=2,U36&lt;=2)),"Maybe",IF(AC36&gt;=BUY_THRESHOLD,"Buy",IF(AC36&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="14" t="n"/>
+      <c r="AF36" s="14" t="n"/>
+      <c r="AG36" s="14" t="n"/>
+      <c r="AH36" s="14" t="n"/>
+      <c r="AI36" s="15" t="n"/>
+      <c r="AJ36">
+        <f>IF(AC36="",-9999-ROW()*0.0000001,AC36-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK36">
+        <f>IF(OR(AC36="",P36="",P36&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC36-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL36">
+        <f>IF(AC36="",-9999-ROW()*0.0000001,X36*1000+AC36-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM36">
+        <f>IF(AC36="",-9999-ROW()*0.0000001,Y36*1000+AC36-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN36">
+        <f>IF(AND(OR(AD36="Maybe",AD36="Price Review"),AG36&lt;&gt;"Approved",AG36&lt;&gt;"Rejected"),IF(AC36="",0,AC36)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8">
+      <c r="A37" s="9">
         <f>IF(C37="","","AYN-"&amp;UPPER(LEFT(E37,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="10">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="11">
         <f>IF(I37="","",IF(J37="BDT",I37,IF(J37="USD",I37*USD_BDT,IF(J37="RMB",I37*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10">
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="11">
         <f>IF(K37="","",K37+IFERROR(L37,0)+(K37*IF(M37="",CUSTOMS_PCT,M37))+IF(N37="",MISC_FEE,N37))</f>
         <v/>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="11">
         <f>IF(O37="","",ROUND(O37*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q37" s="10">
+      <c r="Q37" s="11">
         <f>IF(P37="","",P37-O37)</f>
         <v/>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="12">
         <f>IF(OR(P37="",P37=0),"",Q37/P37)</f>
         <v/>
       </c>
-      <c r="S37" s="8" t="n"/>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="8" t="n"/>
-      <c r="V37" s="8" t="n"/>
-      <c r="W37" s="8" t="n"/>
-      <c r="X37" s="12">
-        <f>IF(COUNT(S37:W37)&lt;5,"",(S37*W_TREND+T37*W_BRAND+U37*W_DEMAND+V37*W_COMPETITION+W37*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y37" s="8">
-        <f>IF(X37="","",IF(X37&gt;=BUY_THRESHOLD,"Buy",IF(X37&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z37" s="8" t="n"/>
-      <c r="AA37" s="8" t="n"/>
-      <c r="AB37" s="8" t="n"/>
-      <c r="AC37" s="8" t="n"/>
-      <c r="AD37" s="9" t="n"/>
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="9" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="9" t="n"/>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="9" t="n"/>
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="9" t="n"/>
+      <c r="AA37" s="9" t="n"/>
+      <c r="AB37" s="9" t="n"/>
+      <c r="AC37" s="13">
+        <f>IF(COUNT(S37:AB37)&lt;10,"",(S37*W_FEMININE+T37*W_TREND+U37*W_AESTHETIC+V37*W_STYLE+W37*W_LIGHT+X37*W_REELS+Y37*W_GIFT+Z37*W_PRICEFIT+AA37*W_DEMAND+AB37*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="9">
+        <f>IF(P37="","",IF(P37&gt;HARD_REJECT_PRICE,"Reject",IF(P37&gt;MAX_PRICE,"Price Review",IF(AC37="","",IF(AND(AC37&gt;=BUY_THRESHOLD,OR(AB37&lt;=2,U37&lt;=2)),"Maybe",IF(AC37&gt;=BUY_THRESHOLD,"Buy",IF(AC37&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="9" t="n"/>
+      <c r="AF37" s="9" t="n"/>
+      <c r="AG37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n"/>
+      <c r="AI37" s="10" t="n"/>
+      <c r="AJ37">
+        <f>IF(AC37="",-9999-ROW()*0.0000001,AC37-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK37">
+        <f>IF(OR(AC37="",P37="",P37&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC37-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL37">
+        <f>IF(AC37="",-9999-ROW()*0.0000001,X37*1000+AC37-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM37">
+        <f>IF(AC37="",-9999-ROW()*0.0000001,Y37*1000+AC37-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN37">
+        <f>IF(AND(OR(AD37="Maybe",AD37="Price Review"),AG37&lt;&gt;"Approved",AG37&lt;&gt;"Rejected"),IF(AC37="",0,AC37)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="13">
+      <c r="A38" s="14">
         <f>IF(C38="","","AYN-"&amp;UPPER(LEFT(E38,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="15">
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="16">
         <f>IF(I38="","",IF(J38="BDT",I38,IF(J38="USD",I38*USD_BDT,IF(J38="RMB",I38*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="16" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="15">
+      <c r="L38" s="16" t="n"/>
+      <c r="M38" s="17" t="n"/>
+      <c r="N38" s="16" t="n"/>
+      <c r="O38" s="16">
         <f>IF(K38="","",K38+IFERROR(L38,0)+(K38*IF(M38="",CUSTOMS_PCT,M38))+IF(N38="",MISC_FEE,N38))</f>
         <v/>
       </c>
-      <c r="P38" s="15">
+      <c r="P38" s="16">
         <f>IF(O38="","",ROUND(O38*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q38" s="15">
+      <c r="Q38" s="16">
         <f>IF(P38="","",P38-O38)</f>
         <v/>
       </c>
-      <c r="R38" s="16">
+      <c r="R38" s="17">
         <f>IF(OR(P38="",P38=0),"",Q38/P38)</f>
         <v/>
       </c>
-      <c r="S38" s="13" t="n"/>
-      <c r="T38" s="13" t="n"/>
-      <c r="U38" s="13" t="n"/>
-      <c r="V38" s="13" t="n"/>
-      <c r="W38" s="13" t="n"/>
-      <c r="X38" s="17">
-        <f>IF(COUNT(S38:W38)&lt;5,"",(S38*W_TREND+T38*W_BRAND+U38*W_DEMAND+V38*W_COMPETITION+W38*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y38" s="13">
-        <f>IF(X38="","",IF(X38&gt;=BUY_THRESHOLD,"Buy",IF(X38&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z38" s="13" t="n"/>
-      <c r="AA38" s="13" t="n"/>
-      <c r="AB38" s="13" t="n"/>
-      <c r="AC38" s="13" t="n"/>
-      <c r="AD38" s="14" t="n"/>
+      <c r="S38" s="14" t="n"/>
+      <c r="T38" s="14" t="n"/>
+      <c r="U38" s="14" t="n"/>
+      <c r="V38" s="14" t="n"/>
+      <c r="W38" s="14" t="n"/>
+      <c r="X38" s="14" t="n"/>
+      <c r="Y38" s="14" t="n"/>
+      <c r="Z38" s="14" t="n"/>
+      <c r="AA38" s="14" t="n"/>
+      <c r="AB38" s="14" t="n"/>
+      <c r="AC38" s="18">
+        <f>IF(COUNT(S38:AB38)&lt;10,"",(S38*W_FEMININE+T38*W_TREND+U38*W_AESTHETIC+V38*W_STYLE+W38*W_LIGHT+X38*W_REELS+Y38*W_GIFT+Z38*W_PRICEFIT+AA38*W_DEMAND+AB38*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD38" s="14">
+        <f>IF(P38="","",IF(P38&gt;HARD_REJECT_PRICE,"Reject",IF(P38&gt;MAX_PRICE,"Price Review",IF(AC38="","",IF(AND(AC38&gt;=BUY_THRESHOLD,OR(AB38&lt;=2,U38&lt;=2)),"Maybe",IF(AC38&gt;=BUY_THRESHOLD,"Buy",IF(AC38&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE38" s="14" t="n"/>
+      <c r="AF38" s="14" t="n"/>
+      <c r="AG38" s="14" t="n"/>
+      <c r="AH38" s="14" t="n"/>
+      <c r="AI38" s="15" t="n"/>
+      <c r="AJ38">
+        <f>IF(AC38="",-9999-ROW()*0.0000001,AC38-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK38">
+        <f>IF(OR(AC38="",P38="",P38&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC38-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL38">
+        <f>IF(AC38="",-9999-ROW()*0.0000001,X38*1000+AC38-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM38">
+        <f>IF(AC38="",-9999-ROW()*0.0000001,Y38*1000+AC38-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN38">
+        <f>IF(AND(OR(AD38="Maybe",AD38="Price Review"),AG38&lt;&gt;"Approved",AG38&lt;&gt;"Rejected"),IF(AC38="",0,AC38)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="8">
+      <c r="A39" s="9">
         <f>IF(C39="","","AYN-"&amp;UPPER(LEFT(E39,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="10">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="11">
         <f>IF(I39="","",IF(J39="BDT",I39,IF(J39="USD",I39*USD_BDT,IF(J39="RMB",I39*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="11" t="n"/>
-      <c r="N39" s="10" t="n"/>
-      <c r="O39" s="10">
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="O39" s="11">
         <f>IF(K39="","",K39+IFERROR(L39,0)+(K39*IF(M39="",CUSTOMS_PCT,M39))+IF(N39="",MISC_FEE,N39))</f>
         <v/>
       </c>
-      <c r="P39" s="10">
+      <c r="P39" s="11">
         <f>IF(O39="","",ROUND(O39*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q39" s="10">
+      <c r="Q39" s="11">
         <f>IF(P39="","",P39-O39)</f>
         <v/>
       </c>
-      <c r="R39" s="11">
+      <c r="R39" s="12">
         <f>IF(OR(P39="",P39=0),"",Q39/P39)</f>
         <v/>
       </c>
-      <c r="S39" s="8" t="n"/>
-      <c r="T39" s="8" t="n"/>
-      <c r="U39" s="8" t="n"/>
-      <c r="V39" s="8" t="n"/>
-      <c r="W39" s="8" t="n"/>
-      <c r="X39" s="12">
-        <f>IF(COUNT(S39:W39)&lt;5,"",(S39*W_TREND+T39*W_BRAND+U39*W_DEMAND+V39*W_COMPETITION+W39*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y39" s="8">
-        <f>IF(X39="","",IF(X39&gt;=BUY_THRESHOLD,"Buy",IF(X39&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z39" s="8" t="n"/>
-      <c r="AA39" s="8" t="n"/>
-      <c r="AB39" s="8" t="n"/>
-      <c r="AC39" s="8" t="n"/>
-      <c r="AD39" s="9" t="n"/>
+      <c r="S39" s="9" t="n"/>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="9" t="n"/>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="9" t="n"/>
+      <c r="Y39" s="9" t="n"/>
+      <c r="Z39" s="9" t="n"/>
+      <c r="AA39" s="9" t="n"/>
+      <c r="AB39" s="9" t="n"/>
+      <c r="AC39" s="13">
+        <f>IF(COUNT(S39:AB39)&lt;10,"",(S39*W_FEMININE+T39*W_TREND+U39*W_AESTHETIC+V39*W_STYLE+W39*W_LIGHT+X39*W_REELS+Y39*W_GIFT+Z39*W_PRICEFIT+AA39*W_DEMAND+AB39*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD39" s="9">
+        <f>IF(P39="","",IF(P39&gt;HARD_REJECT_PRICE,"Reject",IF(P39&gt;MAX_PRICE,"Price Review",IF(AC39="","",IF(AND(AC39&gt;=BUY_THRESHOLD,OR(AB39&lt;=2,U39&lt;=2)),"Maybe",IF(AC39&gt;=BUY_THRESHOLD,"Buy",IF(AC39&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE39" s="9" t="n"/>
+      <c r="AF39" s="9" t="n"/>
+      <c r="AG39" s="9" t="n"/>
+      <c r="AH39" s="9" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39">
+        <f>IF(AC39="",-9999-ROW()*0.0000001,AC39-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK39">
+        <f>IF(OR(AC39="",P39="",P39&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC39-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL39">
+        <f>IF(AC39="",-9999-ROW()*0.0000001,X39*1000+AC39-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM39">
+        <f>IF(AC39="",-9999-ROW()*0.0000001,Y39*1000+AC39-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN39">
+        <f>IF(AND(OR(AD39="Maybe",AD39="Price Review"),AG39&lt;&gt;"Approved",AG39&lt;&gt;"Rejected"),IF(AC39="",0,AC39)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="13">
+      <c r="A40" s="14">
         <f>IF(C40="","","AYN-"&amp;UPPER(LEFT(E40,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="15">
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="16">
         <f>IF(I40="","",IF(J40="BDT",I40,IF(J40="USD",I40*USD_BDT,IF(J40="RMB",I40*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="16" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="15">
+      <c r="L40" s="16" t="n"/>
+      <c r="M40" s="17" t="n"/>
+      <c r="N40" s="16" t="n"/>
+      <c r="O40" s="16">
         <f>IF(K40="","",K40+IFERROR(L40,0)+(K40*IF(M40="",CUSTOMS_PCT,M40))+IF(N40="",MISC_FEE,N40))</f>
         <v/>
       </c>
-      <c r="P40" s="15">
+      <c r="P40" s="16">
         <f>IF(O40="","",ROUND(O40*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q40" s="15">
+      <c r="Q40" s="16">
         <f>IF(P40="","",P40-O40)</f>
         <v/>
       </c>
-      <c r="R40" s="16">
+      <c r="R40" s="17">
         <f>IF(OR(P40="",P40=0),"",Q40/P40)</f>
         <v/>
       </c>
-      <c r="S40" s="13" t="n"/>
-      <c r="T40" s="13" t="n"/>
-      <c r="U40" s="13" t="n"/>
-      <c r="V40" s="13" t="n"/>
-      <c r="W40" s="13" t="n"/>
-      <c r="X40" s="17">
-        <f>IF(COUNT(S40:W40)&lt;5,"",(S40*W_TREND+T40*W_BRAND+U40*W_DEMAND+V40*W_COMPETITION+W40*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y40" s="13">
-        <f>IF(X40="","",IF(X40&gt;=BUY_THRESHOLD,"Buy",IF(X40&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z40" s="13" t="n"/>
-      <c r="AA40" s="13" t="n"/>
-      <c r="AB40" s="13" t="n"/>
-      <c r="AC40" s="13" t="n"/>
-      <c r="AD40" s="14" t="n"/>
+      <c r="S40" s="14" t="n"/>
+      <c r="T40" s="14" t="n"/>
+      <c r="U40" s="14" t="n"/>
+      <c r="V40" s="14" t="n"/>
+      <c r="W40" s="14" t="n"/>
+      <c r="X40" s="14" t="n"/>
+      <c r="Y40" s="14" t="n"/>
+      <c r="Z40" s="14" t="n"/>
+      <c r="AA40" s="14" t="n"/>
+      <c r="AB40" s="14" t="n"/>
+      <c r="AC40" s="18">
+        <f>IF(COUNT(S40:AB40)&lt;10,"",(S40*W_FEMININE+T40*W_TREND+U40*W_AESTHETIC+V40*W_STYLE+W40*W_LIGHT+X40*W_REELS+Y40*W_GIFT+Z40*W_PRICEFIT+AA40*W_DEMAND+AB40*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD40" s="14">
+        <f>IF(P40="","",IF(P40&gt;HARD_REJECT_PRICE,"Reject",IF(P40&gt;MAX_PRICE,"Price Review",IF(AC40="","",IF(AND(AC40&gt;=BUY_THRESHOLD,OR(AB40&lt;=2,U40&lt;=2)),"Maybe",IF(AC40&gt;=BUY_THRESHOLD,"Buy",IF(AC40&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE40" s="14" t="n"/>
+      <c r="AF40" s="14" t="n"/>
+      <c r="AG40" s="14" t="n"/>
+      <c r="AH40" s="14" t="n"/>
+      <c r="AI40" s="15" t="n"/>
+      <c r="AJ40">
+        <f>IF(AC40="",-9999-ROW()*0.0000001,AC40-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK40">
+        <f>IF(OR(AC40="",P40="",P40&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC40-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL40">
+        <f>IF(AC40="",-9999-ROW()*0.0000001,X40*1000+AC40-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM40">
+        <f>IF(AC40="",-9999-ROW()*0.0000001,Y40*1000+AC40-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN40">
+        <f>IF(AND(OR(AD40="Maybe",AD40="Price Review"),AG40&lt;&gt;"Approved",AG40&lt;&gt;"Rejected"),IF(AC40="",0,AC40)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="8">
+      <c r="A41" s="9">
         <f>IF(C41="","","AYN-"&amp;UPPER(LEFT(E41,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="10">
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="11">
         <f>IF(I41="","",IF(J41="BDT",I41,IF(J41="USD",I41*USD_BDT,IF(J41="RMB",I41*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L41" s="10" t="n"/>
-      <c r="M41" s="11" t="n"/>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10">
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="12" t="n"/>
+      <c r="N41" s="11" t="n"/>
+      <c r="O41" s="11">
         <f>IF(K41="","",K41+IFERROR(L41,0)+(K41*IF(M41="",CUSTOMS_PCT,M41))+IF(N41="",MISC_FEE,N41))</f>
         <v/>
       </c>
-      <c r="P41" s="10">
+      <c r="P41" s="11">
         <f>IF(O41="","",ROUND(O41*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q41" s="10">
+      <c r="Q41" s="11">
         <f>IF(P41="","",P41-O41)</f>
         <v/>
       </c>
-      <c r="R41" s="11">
+      <c r="R41" s="12">
         <f>IF(OR(P41="",P41=0),"",Q41/P41)</f>
         <v/>
       </c>
-      <c r="S41" s="8" t="n"/>
-      <c r="T41" s="8" t="n"/>
-      <c r="U41" s="8" t="n"/>
-      <c r="V41" s="8" t="n"/>
-      <c r="W41" s="8" t="n"/>
-      <c r="X41" s="12">
-        <f>IF(COUNT(S41:W41)&lt;5,"",(S41*W_TREND+T41*W_BRAND+U41*W_DEMAND+V41*W_COMPETITION+W41*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y41" s="8">
-        <f>IF(X41="","",IF(X41&gt;=BUY_THRESHOLD,"Buy",IF(X41&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z41" s="8" t="n"/>
-      <c r="AA41" s="8" t="n"/>
-      <c r="AB41" s="8" t="n"/>
-      <c r="AC41" s="8" t="n"/>
-      <c r="AD41" s="9" t="n"/>
+      <c r="S41" s="9" t="n"/>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="V41" s="9" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n"/>
+      <c r="Y41" s="9" t="n"/>
+      <c r="Z41" s="9" t="n"/>
+      <c r="AA41" s="9" t="n"/>
+      <c r="AB41" s="9" t="n"/>
+      <c r="AC41" s="13">
+        <f>IF(COUNT(S41:AB41)&lt;10,"",(S41*W_FEMININE+T41*W_TREND+U41*W_AESTHETIC+V41*W_STYLE+W41*W_LIGHT+X41*W_REELS+Y41*W_GIFT+Z41*W_PRICEFIT+AA41*W_DEMAND+AB41*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD41" s="9">
+        <f>IF(P41="","",IF(P41&gt;HARD_REJECT_PRICE,"Reject",IF(P41&gt;MAX_PRICE,"Price Review",IF(AC41="","",IF(AND(AC41&gt;=BUY_THRESHOLD,OR(AB41&lt;=2,U41&lt;=2)),"Maybe",IF(AC41&gt;=BUY_THRESHOLD,"Buy",IF(AC41&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE41" s="9" t="n"/>
+      <c r="AF41" s="9" t="n"/>
+      <c r="AG41" s="9" t="n"/>
+      <c r="AH41" s="9" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41">
+        <f>IF(AC41="",-9999-ROW()*0.0000001,AC41-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK41">
+        <f>IF(OR(AC41="",P41="",P41&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC41-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL41">
+        <f>IF(AC41="",-9999-ROW()*0.0000001,X41*1000+AC41-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM41">
+        <f>IF(AC41="",-9999-ROW()*0.0000001,Y41*1000+AC41-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN41">
+        <f>IF(AND(OR(AD41="Maybe",AD41="Price Review"),AG41&lt;&gt;"Approved",AG41&lt;&gt;"Rejected"),IF(AC41="",0,AC41)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="13">
+      <c r="A42" s="14">
         <f>IF(C42="","","AYN-"&amp;UPPER(LEFT(E42,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="15">
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="16">
         <f>IF(I42="","",IF(J42="BDT",I42,IF(J42="USD",I42*USD_BDT,IF(J42="RMB",I42*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L42" s="15" t="n"/>
-      <c r="M42" s="16" t="n"/>
-      <c r="N42" s="15" t="n"/>
-      <c r="O42" s="15">
+      <c r="L42" s="16" t="n"/>
+      <c r="M42" s="17" t="n"/>
+      <c r="N42" s="16" t="n"/>
+      <c r="O42" s="16">
         <f>IF(K42="","",K42+IFERROR(L42,0)+(K42*IF(M42="",CUSTOMS_PCT,M42))+IF(N42="",MISC_FEE,N42))</f>
         <v/>
       </c>
-      <c r="P42" s="15">
+      <c r="P42" s="16">
         <f>IF(O42="","",ROUND(O42*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q42" s="15">
+      <c r="Q42" s="16">
         <f>IF(P42="","",P42-O42)</f>
         <v/>
       </c>
-      <c r="R42" s="16">
+      <c r="R42" s="17">
         <f>IF(OR(P42="",P42=0),"",Q42/P42)</f>
         <v/>
       </c>
-      <c r="S42" s="13" t="n"/>
-      <c r="T42" s="13" t="n"/>
-      <c r="U42" s="13" t="n"/>
-      <c r="V42" s="13" t="n"/>
-      <c r="W42" s="13" t="n"/>
-      <c r="X42" s="17">
-        <f>IF(COUNT(S42:W42)&lt;5,"",(S42*W_TREND+T42*W_BRAND+U42*W_DEMAND+V42*W_COMPETITION+W42*W_PRICEFIT)/5*100)</f>
-        <v/>
-      </c>
-      <c r="Y42" s="13">
-        <f>IF(X42="","",IF(X42&gt;=BUY_THRESHOLD,"Buy",IF(X42&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))</f>
-        <v/>
-      </c>
-      <c r="Z42" s="13" t="n"/>
-      <c r="AA42" s="13" t="n"/>
-      <c r="AB42" s="13" t="n"/>
-      <c r="AC42" s="13" t="n"/>
-      <c r="AD42" s="14" t="n"/>
+      <c r="S42" s="14" t="n"/>
+      <c r="T42" s="14" t="n"/>
+      <c r="U42" s="14" t="n"/>
+      <c r="V42" s="14" t="n"/>
+      <c r="W42" s="14" t="n"/>
+      <c r="X42" s="14" t="n"/>
+      <c r="Y42" s="14" t="n"/>
+      <c r="Z42" s="14" t="n"/>
+      <c r="AA42" s="14" t="n"/>
+      <c r="AB42" s="14" t="n"/>
+      <c r="AC42" s="18">
+        <f>IF(COUNT(S42:AB42)&lt;10,"",(S42*W_FEMININE+T42*W_TREND+U42*W_AESTHETIC+V42*W_STYLE+W42*W_LIGHT+X42*W_REELS+Y42*W_GIFT+Z42*W_PRICEFIT+AA42*W_DEMAND+AB42*W_QUALITY)/5*100)</f>
+        <v/>
+      </c>
+      <c r="AD42" s="14">
+        <f>IF(P42="","",IF(P42&gt;HARD_REJECT_PRICE,"Reject",IF(P42&gt;MAX_PRICE,"Price Review",IF(AC42="","",IF(AND(AC42&gt;=BUY_THRESHOLD,OR(AB42&lt;=2,U42&lt;=2)),"Maybe",IF(AC42&gt;=BUY_THRESHOLD,"Buy",IF(AC42&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
+        <v/>
+      </c>
+      <c r="AE42" s="14" t="n"/>
+      <c r="AF42" s="14" t="n"/>
+      <c r="AG42" s="14" t="n"/>
+      <c r="AH42" s="14" t="n"/>
+      <c r="AI42" s="15" t="n"/>
+      <c r="AJ42">
+        <f>IF(AC42="",-9999-ROW()*0.0000001,AC42-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AK42">
+        <f>IF(OR(AC42="",P42="",P42&gt;MAX_PRICE),-9999-ROW()*0.0000001,AC42-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AL42">
+        <f>IF(AC42="",-9999-ROW()*0.0000001,X42*1000+AC42-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AM42">
+        <f>IF(AC42="",-9999-ROW()*0.0000001,Y42*1000+AC42-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AN42">
+        <f>IF(AND(OR(AD42="Maybe",AD42="Price Review"),AG42&lt;&gt;"Approved",AG42&lt;&gt;"Rejected"),IF(AC42="",0,AC42)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="I1:T1"/>
+    <mergeCell ref="I1:R1"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Y3:Y42">
+  <conditionalFormatting sqref="AD3:AD42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Buy"</formula>
     </cfRule>
@@ -3209,26 +4564,42 @@
       <formula>"Maybe"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Price Review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"Reject"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P42">
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>P3&gt;MAX_PRICE</formula>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>P3&gt;HARD_REJECT_PRICE</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="5">
+      <formula>AND(P3&gt;MAX_PRICE,P3&lt;=HARD_REJECT_PRICE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:U42">
+    <cfRule type="cellIs" priority="7" operator="lessThanOrEqual" dxfId="3">
+      <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB3:AB42">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="8" operator="lessThanOrEqual" dxfId="3">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG3:AG42">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="6">
       <formula>"Approved"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="7">
       <formula>"Rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
       <formula>"Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="14">
     <dataValidation sqref="F3:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Where this product is sourced from" type="list">
       <formula1>LIST_PLATFORM</formula1>
     </dataValidation>
@@ -3238,7 +4609,7 @@
     <dataValidation sqref="J3:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Currency the unit cost is quoted in" type="list">
       <formula1>LIST_CURRENCY</formula1>
     </dataValidation>
-    <dataValidation sqref="AB3:AB42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Partner approval status" type="list">
+    <dataValidation sqref="AG3:AG42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Partner approval status" type="list">
       <formula1>LIST_APPROVAL</formula1>
     </dataValidation>
     <dataValidation sqref="S3:S42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
@@ -3256,6 +4627,21 @@
     <dataValidation sqref="W3:W42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
       <formula1>LIST_SCORE</formula1>
     </dataValidation>
+    <dataValidation sqref="X3:X42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
+      <formula1>LIST_SCORE</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y3:Y42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
+      <formula1>LIST_SCORE</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z3:Z42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
+      <formula1>LIST_SCORE</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA3:AA42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
+      <formula1>LIST_SCORE</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB3:AB42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
+      <formula1>LIST_SCORE</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3264,16 +4650,1397 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008FA98E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AAYNA Product Scout Lite — Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Live view of the Product Tracker tab. Nothing here is editable — everything updates automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Total products scouted</t>
+        </is>
+      </c>
+      <c r="B5" s="22">
+        <f>COUNTA('Product Tracker'!C3:C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="B6" s="22">
+        <f>COUNTIF('Product Tracker'!AD3:AD42,"Buy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>COUNTIF('Product Tracker'!AD3:AD42,"Maybe")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Price Review</t>
+        </is>
+      </c>
+      <c r="B8" s="22">
+        <f>COUNTIF('Product Tracker'!AD3:AD42,"Price Review")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
+        <f>COUNTIF('Product Tracker'!AD3:AD42,"Reject")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Top 10 Highest Scoring Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Suggested Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="25">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="26">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="27">
+        <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Best Products Under BDT 700</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Suggested Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="26">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="27">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="26">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="27">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="26">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="27">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="26">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="27">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="26">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="27">
+        <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Best Products for Reels/Photos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Suggested Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="26">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="24">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="27">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="26">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="24">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="27">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="26">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="27">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="26">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="27">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="25">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="26">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="27">
+        <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Best Giftable Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>Suggested Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="24">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="27">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="26">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="24">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="27">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="26">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="27">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="26">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="27">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="25">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="26">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="24">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="27">
+        <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>Products Needing Partner Review (Maybe / Price Review, not yet decided)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>Suggested Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B57" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B60" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="25">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="26">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="24">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="27">
+        <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B4F4F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AAYNA Product Scout Lite — Claude Scoring Prompt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Copy everything in the box below into Claude (or another AI assistant), paste in the product photo/link/description where indicated, then copy Claude's reply back into the matching score columns on the Product Tracker tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="520" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>You are helping AAYNA, a Bangladesh-based women's accessories brand, evaluate a sourcing candidate product.
+AAYNA's brand identity: feminine, trendy, affordable, clean and modern, with a warm, social-media-friendly feel. Visual aesthetic: dusty rose, cream white, antique gold, and espresso charcoal. Most products sell under BDT 700.
+Here is the product: [paste product name, description, photos/link, and supplier price here]
+Score this product from 1 (worst) to 5 (best) on each of these 10 criteria, with a one-line reason for each score:
+1. Feminine Score - how feminine/delicate does it look?
+2. Trend Score - how on-trend is it right now (TikTok/Instagram/competitors)?
+3. AAYNA Aesthetic Fit Score - how well does it match our dusty rose / cream / antique gold look?
+4. Easy to Style Score - how easily can a customer style this with everyday outfits?
+5. Lightweight Score - how light/comfortable is it to wear or carry?
+6. Reels/Photo Potential Score - how good would this look in a Reel, photo, or unboxing video?
+7. Giftability Score - how good is this as a gift?
+8. Price Fit Score - how comfortably can we sell this under BDT 700 and still profit?
+9. Demand Score - how likely is our target customer to actually want and buy this?
+10. Quality/Risk Score - how low is the risk of poor quality, damage in transit, or returns?
+Then give:
+- A Recommended Decision: Buy, Maybe, Price Review, or Reject
+- A one-sentence Reason for that decision
+- A short Content/Reel Idea for how we'd promote this product
+Format your answer exactly like this so it's easy to paste into the sheet:
+Feminine: _ - reason
+Trend: _ - reason
+Aesthetic Fit: _ - reason
+Easy to Style: _ - reason
+Lightweight: _ - reason
+Reels/Photo: _ - reason
+Giftability: _ - reason
+Price Fit: _ - reason
+Demand: _ - reason
+Quality/Risk: _ - reason
+Recommended Decision: _
+Reason: _
+Content/Reel Idea: _</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Tip: if you ever change the 10 scoring criteria, their order, or the price ceiling in the Settings tab, update this prompt to match so Claude's answers keep lining up with the Product Tracker columns.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00B89B5E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3284,31 +6051,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Tune these numbers once. Every formula in the Product Tracker tab reads from here.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>USD to BDT exchange rate</t>
         </is>
@@ -3316,14 +6083,14 @@
       <c r="B5" t="n">
         <v>122</v>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Update when BDT/USD rate changes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>RMB (CNY) to BDT exchange rate</t>
         </is>
@@ -3331,14 +6098,14 @@
       <c r="B6" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Update when BDT/CNY rate changes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Default customs/duty %</t>
         </is>
@@ -3346,14 +6113,14 @@
       <c r="B7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>As decimal, e.g. 0.07 = 7%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Default misc fee per unit (BDT)</t>
         </is>
@@ -3361,14 +6128,14 @@
       <c r="B8" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Packaging, handling, platform fees per piece</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Default markup % over landed cost</t>
         </is>
@@ -3376,14 +6143,14 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>1.0 = 100% markup (sell at 2x landed cost)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Target max selling price (BDT)</t>
         </is>
@@ -3391,96 +6158,166 @@
       <c r="B10" t="n">
         <v>700</v>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>AAYNA's 'mostly under' price ceiling</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Hard reject price ceiling (BDT)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Above the target price but at/under this = 'Price Review' (negotiable). Above this = automatic 'Reject'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Feminine Score</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>All 10 weights below must add up to 1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Weight: Trend Score</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Must add up to 1.00 across the 5 weights</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Weight: Brand Fit Score</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Weight: Demand Score</t>
-        </is>
-      </c>
       <c r="B13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C13" s="18" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="19" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>Weight: Competition Score</t>
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Weight: AAYNA Aesthetic Fit Score</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.15</v>
       </c>
-      <c r="C14" s="18" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Easy to Style Score</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C15" s="19" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Lightweight Score</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C16" s="19" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Reels/Photo Potential Score</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" s="19" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Giftability Score</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C18" s="19" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Weight: Price Fit Score</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="B19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C19" s="19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Demand Score</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C20" s="19" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Weight: Quality/Risk Score</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C21" s="19" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Buy threshold (score &gt;=)</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B22" t="n">
         <v>75</v>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Total Product Score is out of 100</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Maybe threshold (score &gt;=)</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B23" t="n">
         <v>50</v>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Below this = Reject</t>
         </is>
@@ -3495,7 +6332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B89B5E"/>
@@ -3514,32 +6351,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Source Platform</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Source Currency</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Approval Status</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>Score (1-5)</t>
         </is>
@@ -3623,7 +6460,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Price Review</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3644,6 +6481,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Ring</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Reject</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3729,14 +6571,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003B2F2A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3750,124 +6592,148 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>This sheet helps the 3 of us score and decide on products from SkyBuyBD, AliExpress, or other China sourcing platforms — fast, consistently, and without spreadsheets fights.
-Workflow: Whoever finds a product adds a new row and fills in the WHITE input columns only. The colored formula columns calculate themselves. Then each partner fills their Score columns, and the sheet tells you Buy / Maybe / Reject automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+Workflow: Whoever finds a product adds a new row and fills in the WHITE input columns only. The colored formula columns calculate themselves. Then each partner fills in the 10 score columns (or pastes in Claude's scores from the Claude Scoring Prompt tab), and the sheet tells you Buy / Maybe / Price Review / Reject automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Step 1 — Add the product</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Fill SKU is automatic. Enter Date Added, Product Name, Image/Link, Category, Source Platform, Source URL, Supplier Name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>SKU fills in automatically. Enter Date Added, Product Name, Image/Link, Category, Source Platform, Source URL, Supplier Name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Step 2 — Enter cost info</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Enter Unit Cost in whatever currency the supplier quoted (USD/RMB/BDT), pick the currency, then enter Shipping Cost/Unit and Misc Fees if known. Customs % and Misc Fees auto-fill from Settings tab if left blank.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+    <row r="6" ht="75" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Step 3 — Let it calculate</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Unit Cost (BDT), Estimated Landed Cost, Suggested Selling Price, Expected Profit, and Profit Margin % fill in automatically.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+    <row r="7" ht="75" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Step 4 — Score it (1 = worst, 5 = best)</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>Trend Score: how hot is this right now (TikTok/IG/competitors)? Brand Fit Score: does it match AAYNA's dusty rose / cream / antique gold, feminine-trendy vibe? Demand Score: would our audience actually buy this? Competition Score: 5 = very few sellers have it, 1 = everyone already sells it. Price Fit Score: 5 = comfortably sits under our ~700 BDT price point, 1 = priced way above it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Feminine: how feminine/delicate does it look? Trend: how hot is this right now (TikTok/IG/competitors)? AAYNA Aesthetic Fit: how well does it match our dusty rose / cream / antique gold look? Easy to Style: how easily can a customer style this with everyday outfits? Lightweight: how light/comfortable is it to wear or carry? Reels/Photo Potential: how good would this look in a Reel, photo, or unboxing video? Giftability: how good is this as a gift? Price Fit: how comfortably can we sell this under BDT 700 and still profit? Demand: how likely is our target customer to actually want and buy this? Quality/Risk: how low is the risk of poor quality, damage in transit, or returns? Tip: use the Claude Scoring Prompt tab to get an AI first opinion on all 10 scores at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Step 5 — Read the verdict</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Total Product Score (0-100) and Decision (Buy/Maybe/Reject) calculate automatically using the weights set in the Settings tab. Buy = green, Maybe = yellow, Reject = red.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Total Product Score (0-100) calculates automatically using the weights set in the Settings tab. Decision applies these hard rules on top of the score: if Suggested Selling Price is over BDT 700, Decision becomes 'Price Review' (and 'Reject' if it's far over, above the Hard Reject Price Ceiling in Settings); if Quality/Risk or AAYNA Aesthetic Fit score is 1 or 2, Decision can never be 'Buy' (it caps at 'Maybe') even if the total score is high. Buy = green, Maybe = yellow, Price Review = orange, Reject = red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Step 6 — Decide together</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Add a short Reason so the other partners know WHY. Add a Content/Reel Idea so marketing has a head start. Set Approval Status once all partners agree, note who Approved and the date.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+    <row r="10" ht="75" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Adjusting the formulas</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Don't like the default markup, exchange rate, or scoring weights? Change them ONCE in the Settings tab — every row updates automatically. No need to touch the Product Tracker formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Don't like the default markup, exchange rate, price ceilings, or scoring weights? Change them ONCE in the Settings tab — every row updates automatically. No need to touch the Product Tracker formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>The Dashboard tab</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>A live, read-only overview: how many products are Buy/Maybe/Price Review/Reject, the Top 10 highest scoring products, the best products under BDT 700, the best products for reels/photos, the best giftable products, and everything still waiting on partner review. Nothing on this tab needs to be filled in by hand — it reads straight from the Product Tracker tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>The Claude Scoring Prompt tab</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>A ready-to-copy prompt for getting an AI first opinion on a product's 10 scores, a recommended decision, and a content/reel idea, formatted so the reply is easy to paste back into the right columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Color key</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>Green = Buy / Approved. Yellow = Maybe / Pending. Red = Reject / Rejected, or a price above our 700 BDT ceiling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Green = Buy / Approved. Yellow = Maybe / Pending. Orange = Price Review (price is over our 700 BDT target but might still be worth negotiating). Red = Reject / Rejected, or a Quality/Risk or Aesthetic Fit score of 1-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Tips for 3-partner teams</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Assign one column block per partner if you want speed (e.g. Partner A scores Trend+Demand, Partner B scores Brand Fit+Price Fit, Partner C scores Competition) — or all 3 score independently and average manually before finalizing. Keep the Reason column honest; it's your shared memory.</t>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Assign one score block per partner if you want speed (e.g. Partner A scores Feminine + Trend + Aesthetic Fit, Partner B scores Easy to Style + Lightweight + Reels/Photo, Partner C scores Giftability + Price Fit + Demand + Quality/Risk) — or all 3 score independently and average manually before finalizing. Keep the Reason column honest; it's your shared memory.</t>
         </is>
       </c>
     </row>

--- a/sheets/AAYNA_Product_Scout_Lite.xlsx
+++ b/sheets/AAYNA_Product_Scout_Lite.xlsx
@@ -34,12 +34,18 @@
     <definedName name="W_QUALITY">Settings!$B$21</definedName>
     <definedName name="BUY_THRESHOLD">Settings!$B$22</definedName>
     <definedName name="MAYBE_THRESHOLD">Settings!$B$23</definedName>
+    <definedName name="LOW_PROFIT_PCT">Settings!$B$24</definedName>
+    <definedName name="MOQ_WARNING">Settings!$B$25</definedName>
     <definedName name="LIST_PLATFORM">'Dropdown Lists'!$A$2:$A$7</definedName>
     <definedName name="LIST_CATEGORY">'Dropdown Lists'!$B$2:$B$13</definedName>
     <definedName name="LIST_CURRENCY">'Dropdown Lists'!$C$2:$C$4</definedName>
     <definedName name="LIST_DECISION">'Dropdown Lists'!$D$2:$D$5</definedName>
     <definedName name="LIST_APPROVAL">'Dropdown Lists'!$E$2:$E$5</definedName>
     <definedName name="LIST_SCORE">'Dropdown Lists'!$F$2:$F$6</definedName>
+    <definedName name="LIST_YESNO">'Dropdown Lists'!$G$2:$G$3</definedName>
+    <definedName name="LIST_LEVEL">'Dropdown Lists'!$H$2:$H$4</definedName>
+    <definedName name="LIST_PACKAGING">'Dropdown Lists'!$I$2:$I$4</definedName>
+    <definedName name="LIST_SOURCING_STATUS">'Dropdown Lists'!$J$2:$J$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,9 +53,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0 &quot;BDT&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -104,7 +111,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -139,6 +146,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9A66B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AD8350"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A4626C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006E5C54"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,6 +241,18 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -229,19 +268,31 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,7 +301,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -268,7 +322,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:BL42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -765,6 +819,30 @@
     <col hidden="1" width="10" customWidth="1" min="38" max="38"/>
     <col hidden="1" width="10" customWidth="1" min="39" max="39"/>
     <col hidden="1" width="10" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
+    <col width="17" customWidth="1" min="57" max="57"/>
+    <col width="16" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
+    <col width="13" customWidth="1" min="62" max="62"/>
+    <col width="13" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -980,141 +1058,261 @@
           <t>Rank Key: Needs Review (hidden)</t>
         </is>
       </c>
+      <c r="AO2" s="9" t="inlineStr">
+        <is>
+          <t>Supplier Rating</t>
+        </is>
+      </c>
+      <c r="AP2" s="9" t="inlineStr">
+        <is>
+          <t>Product Rating</t>
+        </is>
+      </c>
+      <c r="AQ2" s="9" t="inlineStr">
+        <is>
+          <t>Sold Count / Order Count</t>
+        </is>
+      </c>
+      <c r="AR2" s="9" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AS2" s="9" t="inlineStr">
+        <is>
+          <t>Real Review Photos?</t>
+        </is>
+      </c>
+      <c r="AT2" s="10" t="inlineStr">
+        <is>
+          <t>MOQ</t>
+        </is>
+      </c>
+      <c r="AU2" s="10" t="inlineStr">
+        <is>
+          <t>Recommended Test Quantity</t>
+        </is>
+      </c>
+      <c r="AV2" s="10" t="inlineStr">
+        <is>
+          <t>Final Approved Quantity</t>
+        </is>
+      </c>
+      <c r="AW2" s="10" t="inlineStr">
+        <is>
+          <t>Total Purchase Cost (BDT)</t>
+        </is>
+      </c>
+      <c r="AX2" s="11" t="inlineStr">
+        <is>
+          <t>Weight / Size</t>
+        </is>
+      </c>
+      <c r="AY2" s="11" t="inlineStr">
+        <is>
+          <t>Fragility Level</t>
+        </is>
+      </c>
+      <c r="AZ2" s="11" t="inlineStr">
+        <is>
+          <t>Packaging Difficulty</t>
+        </is>
+      </c>
+      <c r="BA2" s="11" t="inlineStr">
+        <is>
+          <t>Courier Risk</t>
+        </is>
+      </c>
+      <c r="BB2" s="11" t="inlineStr">
+        <is>
+          <t>Duplicate Found on BD Market?</t>
+        </is>
+      </c>
+      <c r="BC2" s="11" t="inlineStr">
+        <is>
+          <t>Competitor Price (BDT)</t>
+        </is>
+      </c>
+      <c r="BD2" s="11" t="inlineStr">
+        <is>
+          <t>Market Saturation Level</t>
+        </is>
+      </c>
+      <c r="BE2" s="6" t="inlineStr">
+        <is>
+          <t>Auto Flag / Warning</t>
+        </is>
+      </c>
+      <c r="BF2" s="6" t="inlineStr">
+        <is>
+          <t>Sourcing Status</t>
+        </is>
+      </c>
+      <c r="BG2" s="12" t="inlineStr">
+        <is>
+          <t>Product Name Finalized?</t>
+        </is>
+      </c>
+      <c r="BH2" s="12" t="inlineStr">
+        <is>
+          <t>SKU Finalized?</t>
+        </is>
+      </c>
+      <c r="BI2" s="12" t="inlineStr">
+        <is>
+          <t>Photos Ready?</t>
+        </is>
+      </c>
+      <c r="BJ2" s="12" t="inlineStr">
+        <is>
+          <t>Description Ready?</t>
+        </is>
+      </c>
+      <c r="BK2" s="12" t="inlineStr">
+        <is>
+          <t>Price Approved?</t>
+        </is>
+      </c>
+      <c r="BL2" s="12" t="inlineStr">
+        <is>
+          <t>Ready for Website Upload?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="13">
         <f>IF(C3="","","AYN-"&amp;UPPER(LEFT(E3,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Antique Gold Hoop Earrings</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>drive.google.com/sample1</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Earrings</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>aliexpress.com/item/sample1</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Lin Wei Trading</t>
         </is>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="13" t="n">
         <v>1.8</v>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="15">
         <f>IF(I3="","",IF(J3="BDT",I3,IF(J3="USD",I3*USD_BDT,IF(J3="RMB",I3*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="11" t="n">
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="15">
         <f>IF(K3="","",K3+IFERROR(L3,0)+(K3*IF(M3="",CUSTOMS_PCT,M3))+IF(N3="",MISC_FEE,N3))</f>
         <v/>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="15">
         <f>IF(O3="","",ROUND(O3*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="15">
         <f>IF(P3="","",P3-O3)</f>
         <v/>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="16">
         <f>IF(OR(P3="",P3=0),"",Q3/P3)</f>
         <v/>
       </c>
-      <c r="S3" s="9" t="n">
+      <c r="S3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="T3" s="9" t="n">
+      <c r="T3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="U3" s="9" t="n">
+      <c r="U3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="V3" s="9" t="n">
+      <c r="V3" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="W3" s="9" t="n">
+      <c r="W3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="X3" s="9" t="n">
+      <c r="X3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="Y3" s="9" t="n">
+      <c r="Y3" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="Z3" s="9" t="n">
+      <c r="Z3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AA3" s="9" t="n">
+      <c r="AA3" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="AB3" s="9" t="n">
+      <c r="AB3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AC3" s="13">
+      <c r="AC3" s="17">
         <f>IF(COUNT(S3:AB3)&lt;10,"",(S3*W_FEMININE+T3*W_TREND+U3*W_AESTHETIC+V3*W_STYLE+W3*W_LIGHT+X3*W_REELS+Y3*W_GIFT+Z3*W_PRICEFIT+AA3*W_DEMAND+AB3*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD3" s="9">
+      <c r="AD3" s="13">
         <f>IF(P3="","",IF(P3&gt;HARD_REJECT_PRICE,"Reject",IF(P3&gt;MAX_PRICE,"Price Review",IF(AC3="","",IF(AND(AC3&gt;=BUY_THRESHOLD,OR(AB3&lt;=2,U3&lt;=2)),"Maybe",IF(AC3&gt;=BUY_THRESHOLD,"Buy",IF(AC3&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE3" s="9" t="inlineStr">
+      <c r="AE3" s="13" t="inlineStr">
         <is>
           <t>Strong rose-gold match, trending on TikTok, lightweight and giftable.</t>
         </is>
       </c>
-      <c r="AF3" s="9" t="inlineStr">
+      <c r="AF3" s="13" t="inlineStr">
         <is>
           <t>Reel: 'Get Ready With Me' earring swap, 3 looks in 15 sec.</t>
         </is>
       </c>
-      <c r="AG3" s="9" t="inlineStr">
+      <c r="AG3" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AH3" s="9" t="inlineStr">
+      <c r="AH3" s="13" t="inlineStr">
         <is>
           <t>Nadia</t>
         </is>
       </c>
-      <c r="AI3" s="10" t="inlineStr">
+      <c r="AI3" s="14" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
@@ -1139,137 +1337,238 @@
         <f>IF(AND(OR(AD3="Maybe",AD3="Price Review"),AG3&lt;&gt;"Approved",AG3&lt;&gt;"Rejected"),IF(AC3="",0,AC3)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO3" s="18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AP3" s="18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ3" s="19" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AR3" s="19" t="n">
+        <v>340</v>
+      </c>
+      <c r="AS3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AT3" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU3" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AV3" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW3" s="15">
+        <f>IF(OR(O3="",AV3=""),"",O3*AV3)</f>
+        <v/>
+      </c>
+      <c r="AX3" s="13" t="inlineStr">
+        <is>
+          <t>15g, 3 x 4 cm</t>
+        </is>
+      </c>
+      <c r="AY3" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ3" s="13" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="BA3" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BB3" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BC3" s="15" t="n">
+        <v>650</v>
+      </c>
+      <c r="BD3" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BE3" s="13">
+        <f>IF(C3="","",IF(AND(ISNUMBER(P3),P3&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB3),AB3&lt;=2),"Quality risk",IF(AND(ISNUMBER(U3),U3&lt;=2),"Aesthetic mismatch",IF(AY3="High","Too fragile",IF(AND(ISNUMBER(R3),R3&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT3),AT3&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD3="Maybe",AD3="Price Review"),"Needs partner review",IF(AD3="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF3" s="13" t="inlineStr">
+        <is>
+          <t>Approved - Not Ordered</t>
+        </is>
+      </c>
+      <c r="BG3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BH3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BK3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BL3" s="13">
+        <f>IF(C3="","",IF(AND(BG3="Yes",BH3="Yes",BI3="Yes",BJ3="Yes",BK3="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="20">
         <f>IF(C4="","","AYN-"&amp;UPPER(LEFT(E4,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Beaded Choker Necklace</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>drive.google.com/sample2</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>SkyBuyBD</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>skybuybd.com/item/sample2</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>Skybuy Supplier 14</t>
         </is>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>BDT</t>
         </is>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="22">
         <f>IF(I4="","",IF(J4="BDT",I4,IF(J4="USD",I4*USD_BDT,IF(J4="RMB",I4*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n">
+      <c r="L4" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="M4" s="17" t="n"/>
-      <c r="N4" s="16" t="n">
+      <c r="M4" s="23" t="n"/>
+      <c r="N4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="O4" s="16">
+      <c r="O4" s="22">
         <f>IF(K4="","",K4+IFERROR(L4,0)+(K4*IF(M4="",CUSTOMS_PCT,M4))+IF(N4="",MISC_FEE,N4))</f>
         <v/>
       </c>
-      <c r="P4" s="16">
+      <c r="P4" s="22">
         <f>IF(O4="","",ROUND(O4*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="22">
         <f>IF(P4="","",P4-O4)</f>
         <v/>
       </c>
-      <c r="R4" s="17">
+      <c r="R4" s="23">
         <f>IF(OR(P4="",P4=0),"",Q4/P4)</f>
         <v/>
       </c>
-      <c r="S4" s="14" t="n">
+      <c r="S4" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="14" t="n">
+      <c r="T4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="U4" s="14" t="n">
+      <c r="U4" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="14" t="n">
+      <c r="V4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="W4" s="14" t="n">
+      <c r="W4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="X4" s="14" t="n">
+      <c r="X4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="Y4" s="14" t="n">
+      <c r="Y4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="Z4" s="14" t="n">
+      <c r="Z4" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="AA4" s="14" t="n">
+      <c r="AA4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="AB4" s="14" t="n">
+      <c r="AB4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="AC4" s="18">
+      <c r="AC4" s="24">
         <f>IF(COUNT(S4:AB4)&lt;10,"",(S4*W_FEMININE+T4*W_TREND+U4*W_AESTHETIC+V4*W_STYLE+W4*W_LIGHT+X4*W_REELS+Y4*W_GIFT+Z4*W_PRICEFIT+AA4*W_DEMAND+AB4*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD4" s="14">
+      <c r="AD4" s="20">
         <f>IF(P4="","",IF(P4&gt;HARD_REJECT_PRICE,"Reject",IF(P4&gt;MAX_PRICE,"Price Review",IF(AC4="","",IF(AND(AC4&gt;=BUY_THRESHOLD,OR(AB4&lt;=2,U4&lt;=2)),"Maybe",IF(AC4&gt;=BUY_THRESHOLD,"Buy",IF(AC4&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE4" s="14" t="inlineStr">
+      <c r="AE4" s="20" t="inlineStr">
         <is>
           <t>Gorgeous and on-trend, but beads chip easily in transit — quality/return risk caps this at Maybe.</t>
         </is>
       </c>
-      <c r="AF4" s="14" t="inlineStr">
+      <c r="AF4" s="20" t="inlineStr">
         <is>
           <t>Try-on reel layering 3 chokers.</t>
         </is>
       </c>
-      <c r="AG4" s="14" t="inlineStr">
+      <c r="AG4" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AH4" s="14" t="n"/>
-      <c r="AI4" s="15" t="n"/>
+      <c r="AH4" s="20" t="n"/>
+      <c r="AI4" s="21" t="n"/>
       <c r="AJ4">
         <f>IF(AC4="",-9999-ROW()*0.0000001,AC4-ROW()*0.0000001)</f>
         <v/>
@@ -1290,133 +1589,212 @@
         <f>IF(AND(OR(AD4="Maybe",AD4="Price Review"),AG4&lt;&gt;"Approved",AG4&lt;&gt;"Rejected"),IF(AC4="",0,AC4)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO4" s="25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AP4" s="25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ4" s="26" t="n">
+        <v>650</v>
+      </c>
+      <c r="AR4" s="26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS4" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AT4" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU4" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV4" s="26" t="n"/>
+      <c r="AW4" s="22">
+        <f>IF(OR(O4="",AV4=""),"",O4*AV4)</f>
+        <v/>
+      </c>
+      <c r="AX4" s="20" t="inlineStr">
+        <is>
+          <t>25g, one size</t>
+        </is>
+      </c>
+      <c r="AY4" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AZ4" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BA4" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BB4" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BC4" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD4" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BE4" s="20">
+        <f>IF(C4="","",IF(AND(ISNUMBER(P4),P4&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB4),AB4&lt;=2),"Quality risk",IF(AND(ISNUMBER(U4),U4&lt;=2),"Aesthetic mismatch",IF(AY4="High","Too fragile",IF(AND(ISNUMBER(R4),R4&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT4),AT4&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD4="Maybe",AD4="Price Review"),"Needs partner review",IF(AD4="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF4" s="20" t="inlineStr">
+        <is>
+          <t>Sample Ordered</t>
+        </is>
+      </c>
+      <c r="BG4" s="20" t="n"/>
+      <c r="BH4" s="20" t="n"/>
+      <c r="BI4" s="20" t="n"/>
+      <c r="BJ4" s="20" t="n"/>
+      <c r="BK4" s="20" t="n"/>
+      <c r="BL4" s="20">
+        <f>IF(C4="","",IF(AND(BG4="Yes",BH4="Yes",BI4="Yes",BJ4="Yes",BK4="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="13">
         <f>IF(C5="","","AYN-"&amp;UPPER(LEFT(E5,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Plain Plastic Hair Clip</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>drive.google.com/sample3</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Hair Accessory</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>1688</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>1688.com/item/sample3</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Generic Factory 8</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>BDT</t>
         </is>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="15">
         <f>IF(I5="","",IF(J5="BDT",I5,IF(J5="USD",I5*USD_BDT,IF(J5="RMB",I5*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="11" t="n">
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="15">
         <f>IF(K5="","",K5+IFERROR(L5,0)+(K5*IF(M5="",CUSTOMS_PCT,M5))+IF(N5="",MISC_FEE,N5))</f>
         <v/>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="15">
         <f>IF(O5="","",ROUND(O5*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="15">
         <f>IF(P5="","",P5-O5)</f>
         <v/>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="16">
         <f>IF(OR(P5="",P5=0),"",Q5/P5)</f>
         <v/>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="Z5" s="9" t="n">
+      <c r="Z5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="AA5" s="9" t="n">
+      <c r="AA5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="9" t="n">
+      <c r="AB5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AC5" s="17">
         <f>IF(COUNT(S5:AB5)&lt;10,"",(S5*W_FEMININE+T5*W_TREND+U5*W_AESTHETIC+V5*W_STYLE+W5*W_LIGHT+X5*W_REELS+Y5*W_GIFT+Z5*W_PRICEFIT+AA5*W_DEMAND+AB5*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD5" s="9">
+      <c r="AD5" s="13">
         <f>IF(P5="","",IF(P5&gt;HARD_REJECT_PRICE,"Reject",IF(P5&gt;MAX_PRICE,"Price Review",IF(AC5="","",IF(AND(AC5&gt;=BUY_THRESHOLD,OR(AB5&lt;=2,U5&lt;=2)),"Maybe",IF(AC5&gt;=BUY_THRESHOLD,"Buy",IF(AC5&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE5" s="9" t="inlineStr">
+      <c r="AE5" s="13" t="inlineStr">
         <is>
           <t>Generic look, low trend/demand/aesthetic fit — total score too low to justify stocking.</t>
         </is>
       </c>
-      <c r="AF5" s="9" t="inlineStr"/>
-      <c r="AG5" s="9" t="inlineStr">
+      <c r="AF5" s="13" t="inlineStr"/>
+      <c r="AG5" s="13" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="10" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="14" t="n"/>
       <c r="AJ5">
         <f>IF(AC5="",-9999-ROW()*0.0000001,AC5-ROW()*0.0000001)</f>
         <v/>
@@ -1437,137 +1815,214 @@
         <f>IF(AND(OR(AD5="Maybe",AD5="Price Review"),AG5&lt;&gt;"Approved",AG5&lt;&gt;"Rejected"),IF(AC5="",0,AC5)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO5" s="18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP5" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" s="19" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AR5" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS5" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT5" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU5" s="19" t="n"/>
+      <c r="AV5" s="19" t="n"/>
+      <c r="AW5" s="15">
+        <f>IF(OR(O5="",AV5=""),"",O5*AV5)</f>
+        <v/>
+      </c>
+      <c r="AX5" s="13" t="inlineStr">
+        <is>
+          <t>5g, 6 cm clip</t>
+        </is>
+      </c>
+      <c r="AY5" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ5" s="13" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="BA5" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BB5" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BC5" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD5" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BE5" s="13">
+        <f>IF(C5="","",IF(AND(ISNUMBER(P5),P5&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB5),AB5&lt;=2),"Quality risk",IF(AND(ISNUMBER(U5),U5&lt;=2),"Aesthetic mismatch",IF(AY5="High","Too fragile",IF(AND(ISNUMBER(R5),R5&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT5),AT5&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD5="Maybe",AD5="Price Review"),"Needs partner review",IF(AD5="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF5" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="BG5" s="13" t="n"/>
+      <c r="BH5" s="13" t="n"/>
+      <c r="BI5" s="13" t="n"/>
+      <c r="BJ5" s="13" t="n"/>
+      <c r="BK5" s="13" t="n"/>
+      <c r="BL5" s="13">
+        <f>IF(C5="","",IF(AND(BG5="Yes",BH5="Yes",BI5="Yes",BJ5="Yes",BK5="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="20">
         <f>IF(C6="","","AYN-"&amp;UPPER(LEFT(E6,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Embroidered Tote Bag</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>drive.google.com/sample4</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>aliexpress.com/item/sample4</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Lin Wei Trading</t>
         </is>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="20" t="n">
         <v>300</v>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>BDT</t>
         </is>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="22">
         <f>IF(I6="","",IF(J6="BDT",I6,IF(J6="USD",I6*USD_BDT,IF(J6="RMB",I6*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n">
+      <c r="L6" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="16" t="n">
+      <c r="M6" s="23" t="n"/>
+      <c r="N6" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="22">
         <f>IF(K6="","",K6+IFERROR(L6,0)+(K6*IF(M6="",CUSTOMS_PCT,M6))+IF(N6="",MISC_FEE,N6))</f>
         <v/>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="22">
         <f>IF(O6="","",ROUND(O6*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="22">
         <f>IF(P6="","",P6-O6)</f>
         <v/>
       </c>
-      <c r="R6" s="17">
+      <c r="R6" s="23">
         <f>IF(OR(P6="",P6=0),"",Q6/P6)</f>
         <v/>
       </c>
-      <c r="S6" s="14" t="n">
+      <c r="S6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="T6" s="14" t="n">
+      <c r="T6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="U6" s="14" t="n">
+      <c r="U6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="14" t="n">
+      <c r="V6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="W6" s="14" t="n">
+      <c r="W6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="X6" s="14" t="n">
+      <c r="X6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="Y6" s="14" t="n">
+      <c r="Y6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="Z6" s="14" t="n">
+      <c r="Z6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="AA6" s="14" t="n">
+      <c r="AA6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="AB6" s="14" t="n">
+      <c r="AB6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="AC6" s="18">
+      <c r="AC6" s="24">
         <f>IF(COUNT(S6:AB6)&lt;10,"",(S6*W_FEMININE+T6*W_TREND+U6*W_AESTHETIC+V6*W_STYLE+W6*W_LIGHT+X6*W_REELS+Y6*W_GIFT+Z6*W_PRICEFIT+AA6*W_DEMAND+AB6*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD6" s="14">
+      <c r="AD6" s="20">
         <f>IF(P6="","",IF(P6&gt;HARD_REJECT_PRICE,"Reject",IF(P6&gt;MAX_PRICE,"Price Review",IF(AC6="","",IF(AND(AC6&gt;=BUY_THRESHOLD,OR(AB6&lt;=2,U6&lt;=2)),"Maybe",IF(AC6&gt;=BUY_THRESHOLD,"Buy",IF(AC6&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE6" s="14" t="inlineStr">
+      <c r="AE6" s="20" t="inlineStr">
         <is>
           <t>Lovely design, but landed cost pushes selling price over 700 — needs supplier price negotiation.</t>
         </is>
       </c>
-      <c r="AF6" s="14" t="inlineStr">
+      <c r="AF6" s="20" t="inlineStr">
         <is>
           <t>Flatlay reel with 3 outfit pairings.</t>
         </is>
       </c>
-      <c r="AG6" s="14" t="inlineStr">
+      <c r="AG6" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AH6" s="14" t="n"/>
-      <c r="AI6" s="15" t="n"/>
+      <c r="AH6" s="20" t="n"/>
+      <c r="AI6" s="21" t="n"/>
       <c r="AJ6">
         <f>IF(AC6="",-9999-ROW()*0.0000001,AC6-ROW()*0.0000001)</f>
         <v/>
@@ -1588,113 +2043,200 @@
         <f>IF(AND(OR(AD6="Maybe",AD6="Price Review"),AG6&lt;&gt;"Approved",AG6&lt;&gt;"Rejected"),IF(AC6="",0,AC6)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO6" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP6" s="25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ6" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="AR6" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS6" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AT6" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU6" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV6" s="26" t="n"/>
+      <c r="AW6" s="22">
+        <f>IF(OR(O6="",AV6=""),"",O6*AV6)</f>
+        <v/>
+      </c>
+      <c r="AX6" s="20" t="inlineStr">
+        <is>
+          <t>320g, 30 x 35 cm</t>
+        </is>
+      </c>
+      <c r="AY6" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ6" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BA6" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BB6" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BC6" s="22" t="n">
+        <v>720</v>
+      </c>
+      <c r="BD6" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BE6" s="20">
+        <f>IF(C6="","",IF(AND(ISNUMBER(P6),P6&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB6),AB6&lt;=2),"Quality risk",IF(AND(ISNUMBER(U6),U6&lt;=2),"Aesthetic mismatch",IF(AY6="High","Too fragile",IF(AND(ISNUMBER(R6),R6&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT6),AT6&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD6="Maybe",AD6="Price Review"),"Needs partner review",IF(AD6="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF6" s="20" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+      <c r="BG6" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BH6" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI6" s="20" t="n"/>
+      <c r="BJ6" s="20" t="n"/>
+      <c r="BK6" s="20" t="n"/>
+      <c r="BL6" s="20">
+        <f>IF(C6="","",IF(AND(BG6="Yes",BH6="Yes",BI6="Yes",BJ6="Yes",BK6="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="13">
         <f>IF(C7="","","AYN-"&amp;UPPER(LEFT(E7,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Designer-Inspired Sunglasses</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>drive.google.com/sample5</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Sunglasses</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>aliexpress.com/item/sample5</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>Guangzhou Eyewear Co</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="15">
         <f>IF(I7="","",IF(J7="BDT",I7,IF(J7="USD",I7*USD_BDT,IF(J7="RMB",I7*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="11" t="n">
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="15">
         <f>IF(K7="","",K7+IFERROR(L7,0)+(K7*IF(M7="",CUSTOMS_PCT,M7))+IF(N7="",MISC_FEE,N7))</f>
         <v/>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="15">
         <f>IF(O7="","",ROUND(O7*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="15">
         <f>IF(P7="","",P7-O7)</f>
         <v/>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="16">
         <f>IF(OR(P7="",P7=0),"",Q7/P7)</f>
         <v/>
       </c>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="9" t="n"/>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="9" t="n"/>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="9" t="n"/>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="13">
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="13" t="n"/>
+      <c r="Y7" s="13" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="13" t="n"/>
+      <c r="AB7" s="13" t="n"/>
+      <c r="AC7" s="17">
         <f>IF(COUNT(S7:AB7)&lt;10,"",(S7*W_FEMININE+T7*W_TREND+U7*W_AESTHETIC+V7*W_STYLE+W7*W_LIGHT+X7*W_REELS+Y7*W_GIFT+Z7*W_PRICEFIT+AA7*W_DEMAND+AB7*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD7" s="9">
+      <c r="AD7" s="13">
         <f>IF(P7="","",IF(P7&gt;HARD_REJECT_PRICE,"Reject",IF(P7&gt;MAX_PRICE,"Price Review",IF(AC7="","",IF(AND(AC7&gt;=BUY_THRESHOLD,OR(AB7&lt;=2,U7&lt;=2)),"Maybe",IF(AC7&gt;=BUY_THRESHOLD,"Buy",IF(AC7&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE7" s="9" t="inlineStr">
+      <c r="AE7" s="13" t="inlineStr">
         <is>
           <t>Cost alone puts this far above our price ceiling even before scoring — auto-rejected.</t>
         </is>
       </c>
-      <c r="AF7" s="9" t="inlineStr"/>
-      <c r="AG7" s="9" t="inlineStr">
+      <c r="AF7" s="13" t="inlineStr"/>
+      <c r="AG7" s="13" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="10" t="n"/>
+      <c r="AH7" s="13" t="n"/>
+      <c r="AI7" s="14" t="n"/>
       <c r="AJ7">
         <f>IF(AC7="",-9999-ROW()*0.0000001,AC7-ROW()*0.0000001)</f>
         <v/>
@@ -1715,67 +2257,144 @@
         <f>IF(AND(OR(AD7="Maybe",AD7="Price Review"),AG7&lt;&gt;"Approved",AG7&lt;&gt;"Rejected"),IF(AC7="",0,AC7)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO7" s="18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AP7" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ7" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="AR7" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="AS7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT7" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AU7" s="19" t="n"/>
+      <c r="AV7" s="19" t="n"/>
+      <c r="AW7" s="15">
+        <f>IF(OR(O7="",AV7=""),"",O7*AV7)</f>
+        <v/>
+      </c>
+      <c r="AX7" s="13" t="inlineStr">
+        <is>
+          <t>28g, with case</t>
+        </is>
+      </c>
+      <c r="AY7" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AZ7" s="13" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="BA7" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BB7" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BC7" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="BD7" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BE7" s="13">
+        <f>IF(C7="","",IF(AND(ISNUMBER(P7),P7&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB7),AB7&lt;=2),"Quality risk",IF(AND(ISNUMBER(U7),U7&lt;=2),"Aesthetic mismatch",IF(AY7="High","Too fragile",IF(AND(ISNUMBER(R7),R7&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT7),AT7&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD7="Maybe",AD7="Price Review"),"Needs partner review",IF(AD7="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF7" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="BG7" s="13" t="n"/>
+      <c r="BH7" s="13" t="n"/>
+      <c r="BI7" s="13" t="n"/>
+      <c r="BJ7" s="13" t="n"/>
+      <c r="BK7" s="13" t="n"/>
+      <c r="BL7" s="13">
+        <f>IF(C7="","",IF(AND(BG7="Yes",BH7="Yes",BI7="Yes",BJ7="Yes",BK7="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="20">
         <f>IF(C8="","","AYN-"&amp;UPPER(LEFT(E8,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="16">
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="22">
         <f>IF(I8="","",IF(J8="BDT",I8,IF(J8="USD",I8*USD_BDT,IF(J8="RMB",I8*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16">
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22">
         <f>IF(K8="","",K8+IFERROR(L8,0)+(K8*IF(M8="",CUSTOMS_PCT,M8))+IF(N8="",MISC_FEE,N8))</f>
         <v/>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="22">
         <f>IF(O8="","",ROUND(O8*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="22">
         <f>IF(P8="","",P8-O8)</f>
         <v/>
       </c>
-      <c r="R8" s="17">
+      <c r="R8" s="23">
         <f>IF(OR(P8="",P8=0),"",Q8/P8)</f>
         <v/>
       </c>
-      <c r="S8" s="14" t="n"/>
-      <c r="T8" s="14" t="n"/>
-      <c r="U8" s="14" t="n"/>
-      <c r="V8" s="14" t="n"/>
-      <c r="W8" s="14" t="n"/>
-      <c r="X8" s="14" t="n"/>
-      <c r="Y8" s="14" t="n"/>
-      <c r="Z8" s="14" t="n"/>
-      <c r="AA8" s="14" t="n"/>
-      <c r="AB8" s="14" t="n"/>
-      <c r="AC8" s="18">
+      <c r="S8" s="20" t="n"/>
+      <c r="T8" s="20" t="n"/>
+      <c r="U8" s="20" t="n"/>
+      <c r="V8" s="20" t="n"/>
+      <c r="W8" s="20" t="n"/>
+      <c r="X8" s="20" t="n"/>
+      <c r="Y8" s="20" t="n"/>
+      <c r="Z8" s="20" t="n"/>
+      <c r="AA8" s="20" t="n"/>
+      <c r="AB8" s="20" t="n"/>
+      <c r="AC8" s="24">
         <f>IF(COUNT(S8:AB8)&lt;10,"",(S8*W_FEMININE+T8*W_TREND+U8*W_AESTHETIC+V8*W_STYLE+W8*W_LIGHT+X8*W_REELS+Y8*W_GIFT+Z8*W_PRICEFIT+AA8*W_DEMAND+AB8*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD8" s="14">
+      <c r="AD8" s="20">
         <f>IF(P8="","",IF(P8&gt;HARD_REJECT_PRICE,"Reject",IF(P8&gt;MAX_PRICE,"Price Review",IF(AC8="","",IF(AND(AC8&gt;=BUY_THRESHOLD,OR(AB8&lt;=2,U8&lt;=2)),"Maybe",IF(AC8&gt;=BUY_THRESHOLD,"Buy",IF(AC8&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE8" s="14" t="n"/>
-      <c r="AF8" s="14" t="n"/>
-      <c r="AG8" s="14" t="n"/>
-      <c r="AH8" s="14" t="n"/>
-      <c r="AI8" s="15" t="n"/>
+      <c r="AE8" s="20" t="n"/>
+      <c r="AF8" s="20" t="n"/>
+      <c r="AG8" s="20" t="n"/>
+      <c r="AH8" s="20" t="n"/>
+      <c r="AI8" s="21" t="n"/>
       <c r="AJ8">
         <f>IF(AC8="",-9999-ROW()*0.0000001,AC8-ROW()*0.0000001)</f>
         <v/>
@@ -1796,67 +2415,100 @@
         <f>IF(AND(OR(AD8="Maybe",AD8="Price Review"),AG8&lt;&gt;"Approved",AG8&lt;&gt;"Rejected"),IF(AC8="",0,AC8)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO8" s="25" t="n"/>
+      <c r="AP8" s="25" t="n"/>
+      <c r="AQ8" s="26" t="n"/>
+      <c r="AR8" s="26" t="n"/>
+      <c r="AS8" s="20" t="n"/>
+      <c r="AT8" s="26" t="n"/>
+      <c r="AU8" s="26" t="n"/>
+      <c r="AV8" s="26" t="n"/>
+      <c r="AW8" s="22">
+        <f>IF(OR(O8="",AV8=""),"",O8*AV8)</f>
+        <v/>
+      </c>
+      <c r="AX8" s="20" t="n"/>
+      <c r="AY8" s="20" t="n"/>
+      <c r="AZ8" s="20" t="n"/>
+      <c r="BA8" s="20" t="n"/>
+      <c r="BB8" s="20" t="n"/>
+      <c r="BC8" s="22" t="n"/>
+      <c r="BD8" s="20" t="n"/>
+      <c r="BE8" s="20">
+        <f>IF(C8="","",IF(AND(ISNUMBER(P8),P8&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB8),AB8&lt;=2),"Quality risk",IF(AND(ISNUMBER(U8),U8&lt;=2),"Aesthetic mismatch",IF(AY8="High","Too fragile",IF(AND(ISNUMBER(R8),R8&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT8),AT8&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD8="Maybe",AD8="Price Review"),"Needs partner review",IF(AD8="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF8" s="20" t="n"/>
+      <c r="BG8" s="20" t="n"/>
+      <c r="BH8" s="20" t="n"/>
+      <c r="BI8" s="20" t="n"/>
+      <c r="BJ8" s="20" t="n"/>
+      <c r="BK8" s="20" t="n"/>
+      <c r="BL8" s="20">
+        <f>IF(C8="","",IF(AND(BG8="Yes",BH8="Yes",BI8="Yes",BJ8="Yes",BK8="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="13">
         <f>IF(C9="","","AYN-"&amp;UPPER(LEFT(E9,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="11">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="15">
         <f>IF(I9="","",IF(J9="BDT",I9,IF(J9="USD",I9*USD_BDT,IF(J9="RMB",I9*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11">
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15">
         <f>IF(K9="","",K9+IFERROR(L9,0)+(K9*IF(M9="",CUSTOMS_PCT,M9))+IF(N9="",MISC_FEE,N9))</f>
         <v/>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="15">
         <f>IF(O9="","",ROUND(O9*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="15">
         <f>IF(P9="","",P9-O9)</f>
         <v/>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="16">
         <f>IF(OR(P9="",P9=0),"",Q9/P9)</f>
         <v/>
       </c>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="9" t="n"/>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="9" t="n"/>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="9" t="n"/>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="13">
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="n"/>
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="13" t="n"/>
+      <c r="Z9" s="13" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="13" t="n"/>
+      <c r="AC9" s="17">
         <f>IF(COUNT(S9:AB9)&lt;10,"",(S9*W_FEMININE+T9*W_TREND+U9*W_AESTHETIC+V9*W_STYLE+W9*W_LIGHT+X9*W_REELS+Y9*W_GIFT+Z9*W_PRICEFIT+AA9*W_DEMAND+AB9*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD9" s="9">
+      <c r="AD9" s="13">
         <f>IF(P9="","",IF(P9&gt;HARD_REJECT_PRICE,"Reject",IF(P9&gt;MAX_PRICE,"Price Review",IF(AC9="","",IF(AND(AC9&gt;=BUY_THRESHOLD,OR(AB9&lt;=2,U9&lt;=2)),"Maybe",IF(AC9&gt;=BUY_THRESHOLD,"Buy",IF(AC9&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="9" t="n"/>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="10" t="n"/>
+      <c r="AE9" s="13" t="n"/>
+      <c r="AF9" s="13" t="n"/>
+      <c r="AG9" s="13" t="n"/>
+      <c r="AH9" s="13" t="n"/>
+      <c r="AI9" s="14" t="n"/>
       <c r="AJ9">
         <f>IF(AC9="",-9999-ROW()*0.0000001,AC9-ROW()*0.0000001)</f>
         <v/>
@@ -1877,67 +2529,100 @@
         <f>IF(AND(OR(AD9="Maybe",AD9="Price Review"),AG9&lt;&gt;"Approved",AG9&lt;&gt;"Rejected"),IF(AC9="",0,AC9)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO9" s="18" t="n"/>
+      <c r="AP9" s="18" t="n"/>
+      <c r="AQ9" s="19" t="n"/>
+      <c r="AR9" s="19" t="n"/>
+      <c r="AS9" s="13" t="n"/>
+      <c r="AT9" s="19" t="n"/>
+      <c r="AU9" s="19" t="n"/>
+      <c r="AV9" s="19" t="n"/>
+      <c r="AW9" s="15">
+        <f>IF(OR(O9="",AV9=""),"",O9*AV9)</f>
+        <v/>
+      </c>
+      <c r="AX9" s="13" t="n"/>
+      <c r="AY9" s="13" t="n"/>
+      <c r="AZ9" s="13" t="n"/>
+      <c r="BA9" s="13" t="n"/>
+      <c r="BB9" s="13" t="n"/>
+      <c r="BC9" s="15" t="n"/>
+      <c r="BD9" s="13" t="n"/>
+      <c r="BE9" s="13">
+        <f>IF(C9="","",IF(AND(ISNUMBER(P9),P9&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB9),AB9&lt;=2),"Quality risk",IF(AND(ISNUMBER(U9),U9&lt;=2),"Aesthetic mismatch",IF(AY9="High","Too fragile",IF(AND(ISNUMBER(R9),R9&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT9),AT9&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD9="Maybe",AD9="Price Review"),"Needs partner review",IF(AD9="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF9" s="13" t="n"/>
+      <c r="BG9" s="13" t="n"/>
+      <c r="BH9" s="13" t="n"/>
+      <c r="BI9" s="13" t="n"/>
+      <c r="BJ9" s="13" t="n"/>
+      <c r="BK9" s="13" t="n"/>
+      <c r="BL9" s="13">
+        <f>IF(C9="","",IF(AND(BG9="Yes",BH9="Yes",BI9="Yes",BJ9="Yes",BK9="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="20">
         <f>IF(C10="","","AYN-"&amp;UPPER(LEFT(E10,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="16">
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="22">
         <f>IF(I10="","",IF(J10="BDT",I10,IF(J10="USD",I10*USD_BDT,IF(J10="RMB",I10*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16">
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22">
         <f>IF(K10="","",K10+IFERROR(L10,0)+(K10*IF(M10="",CUSTOMS_PCT,M10))+IF(N10="",MISC_FEE,N10))</f>
         <v/>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="22">
         <f>IF(O10="","",ROUND(O10*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="22">
         <f>IF(P10="","",P10-O10)</f>
         <v/>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="23">
         <f>IF(OR(P10="",P10=0),"",Q10/P10)</f>
         <v/>
       </c>
-      <c r="S10" s="14" t="n"/>
-      <c r="T10" s="14" t="n"/>
-      <c r="U10" s="14" t="n"/>
-      <c r="V10" s="14" t="n"/>
-      <c r="W10" s="14" t="n"/>
-      <c r="X10" s="14" t="n"/>
-      <c r="Y10" s="14" t="n"/>
-      <c r="Z10" s="14" t="n"/>
-      <c r="AA10" s="14" t="n"/>
-      <c r="AB10" s="14" t="n"/>
-      <c r="AC10" s="18">
+      <c r="S10" s="20" t="n"/>
+      <c r="T10" s="20" t="n"/>
+      <c r="U10" s="20" t="n"/>
+      <c r="V10" s="20" t="n"/>
+      <c r="W10" s="20" t="n"/>
+      <c r="X10" s="20" t="n"/>
+      <c r="Y10" s="20" t="n"/>
+      <c r="Z10" s="20" t="n"/>
+      <c r="AA10" s="20" t="n"/>
+      <c r="AB10" s="20" t="n"/>
+      <c r="AC10" s="24">
         <f>IF(COUNT(S10:AB10)&lt;10,"",(S10*W_FEMININE+T10*W_TREND+U10*W_AESTHETIC+V10*W_STYLE+W10*W_LIGHT+X10*W_REELS+Y10*W_GIFT+Z10*W_PRICEFIT+AA10*W_DEMAND+AB10*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD10" s="14">
+      <c r="AD10" s="20">
         <f>IF(P10="","",IF(P10&gt;HARD_REJECT_PRICE,"Reject",IF(P10&gt;MAX_PRICE,"Price Review",IF(AC10="","",IF(AND(AC10&gt;=BUY_THRESHOLD,OR(AB10&lt;=2,U10&lt;=2)),"Maybe",IF(AC10&gt;=BUY_THRESHOLD,"Buy",IF(AC10&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE10" s="14" t="n"/>
-      <c r="AF10" s="14" t="n"/>
-      <c r="AG10" s="14" t="n"/>
-      <c r="AH10" s="14" t="n"/>
-      <c r="AI10" s="15" t="n"/>
+      <c r="AE10" s="20" t="n"/>
+      <c r="AF10" s="20" t="n"/>
+      <c r="AG10" s="20" t="n"/>
+      <c r="AH10" s="20" t="n"/>
+      <c r="AI10" s="21" t="n"/>
       <c r="AJ10">
         <f>IF(AC10="",-9999-ROW()*0.0000001,AC10-ROW()*0.0000001)</f>
         <v/>
@@ -1958,67 +2643,100 @@
         <f>IF(AND(OR(AD10="Maybe",AD10="Price Review"),AG10&lt;&gt;"Approved",AG10&lt;&gt;"Rejected"),IF(AC10="",0,AC10)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO10" s="25" t="n"/>
+      <c r="AP10" s="25" t="n"/>
+      <c r="AQ10" s="26" t="n"/>
+      <c r="AR10" s="26" t="n"/>
+      <c r="AS10" s="20" t="n"/>
+      <c r="AT10" s="26" t="n"/>
+      <c r="AU10" s="26" t="n"/>
+      <c r="AV10" s="26" t="n"/>
+      <c r="AW10" s="22">
+        <f>IF(OR(O10="",AV10=""),"",O10*AV10)</f>
+        <v/>
+      </c>
+      <c r="AX10" s="20" t="n"/>
+      <c r="AY10" s="20" t="n"/>
+      <c r="AZ10" s="20" t="n"/>
+      <c r="BA10" s="20" t="n"/>
+      <c r="BB10" s="20" t="n"/>
+      <c r="BC10" s="22" t="n"/>
+      <c r="BD10" s="20" t="n"/>
+      <c r="BE10" s="20">
+        <f>IF(C10="","",IF(AND(ISNUMBER(P10),P10&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB10),AB10&lt;=2),"Quality risk",IF(AND(ISNUMBER(U10),U10&lt;=2),"Aesthetic mismatch",IF(AY10="High","Too fragile",IF(AND(ISNUMBER(R10),R10&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT10),AT10&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD10="Maybe",AD10="Price Review"),"Needs partner review",IF(AD10="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF10" s="20" t="n"/>
+      <c r="BG10" s="20" t="n"/>
+      <c r="BH10" s="20" t="n"/>
+      <c r="BI10" s="20" t="n"/>
+      <c r="BJ10" s="20" t="n"/>
+      <c r="BK10" s="20" t="n"/>
+      <c r="BL10" s="20">
+        <f>IF(C10="","",IF(AND(BG10="Yes",BH10="Yes",BI10="Yes",BJ10="Yes",BK10="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="13">
         <f>IF(C11="","","AYN-"&amp;UPPER(LEFT(E11,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="11">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="15">
         <f>IF(I11="","",IF(J11="BDT",I11,IF(J11="USD",I11*USD_BDT,IF(J11="RMB",I11*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11">
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="15" t="n"/>
+      <c r="O11" s="15">
         <f>IF(K11="","",K11+IFERROR(L11,0)+(K11*IF(M11="",CUSTOMS_PCT,M11))+IF(N11="",MISC_FEE,N11))</f>
         <v/>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="15">
         <f>IF(O11="","",ROUND(O11*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="15">
         <f>IF(P11="","",P11-O11)</f>
         <v/>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="16">
         <f>IF(OR(P11="",P11=0),"",Q11/P11)</f>
         <v/>
       </c>
-      <c r="S11" s="9" t="n"/>
-      <c r="T11" s="9" t="n"/>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="9" t="n"/>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="13">
+      <c r="S11" s="13" t="n"/>
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="13" t="n"/>
+      <c r="V11" s="13" t="n"/>
+      <c r="W11" s="13" t="n"/>
+      <c r="X11" s="13" t="n"/>
+      <c r="Y11" s="13" t="n"/>
+      <c r="Z11" s="13" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="13" t="n"/>
+      <c r="AC11" s="17">
         <f>IF(COUNT(S11:AB11)&lt;10,"",(S11*W_FEMININE+T11*W_TREND+U11*W_AESTHETIC+V11*W_STYLE+W11*W_LIGHT+X11*W_REELS+Y11*W_GIFT+Z11*W_PRICEFIT+AA11*W_DEMAND+AB11*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD11" s="9">
+      <c r="AD11" s="13">
         <f>IF(P11="","",IF(P11&gt;HARD_REJECT_PRICE,"Reject",IF(P11&gt;MAX_PRICE,"Price Review",IF(AC11="","",IF(AND(AC11&gt;=BUY_THRESHOLD,OR(AB11&lt;=2,U11&lt;=2)),"Maybe",IF(AC11&gt;=BUY_THRESHOLD,"Buy",IF(AC11&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="9" t="n"/>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="10" t="n"/>
+      <c r="AE11" s="13" t="n"/>
+      <c r="AF11" s="13" t="n"/>
+      <c r="AG11" s="13" t="n"/>
+      <c r="AH11" s="13" t="n"/>
+      <c r="AI11" s="14" t="n"/>
       <c r="AJ11">
         <f>IF(AC11="",-9999-ROW()*0.0000001,AC11-ROW()*0.0000001)</f>
         <v/>
@@ -2039,67 +2757,100 @@
         <f>IF(AND(OR(AD11="Maybe",AD11="Price Review"),AG11&lt;&gt;"Approved",AG11&lt;&gt;"Rejected"),IF(AC11="",0,AC11)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO11" s="18" t="n"/>
+      <c r="AP11" s="18" t="n"/>
+      <c r="AQ11" s="19" t="n"/>
+      <c r="AR11" s="19" t="n"/>
+      <c r="AS11" s="13" t="n"/>
+      <c r="AT11" s="19" t="n"/>
+      <c r="AU11" s="19" t="n"/>
+      <c r="AV11" s="19" t="n"/>
+      <c r="AW11" s="15">
+        <f>IF(OR(O11="",AV11=""),"",O11*AV11)</f>
+        <v/>
+      </c>
+      <c r="AX11" s="13" t="n"/>
+      <c r="AY11" s="13" t="n"/>
+      <c r="AZ11" s="13" t="n"/>
+      <c r="BA11" s="13" t="n"/>
+      <c r="BB11" s="13" t="n"/>
+      <c r="BC11" s="15" t="n"/>
+      <c r="BD11" s="13" t="n"/>
+      <c r="BE11" s="13">
+        <f>IF(C11="","",IF(AND(ISNUMBER(P11),P11&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB11),AB11&lt;=2),"Quality risk",IF(AND(ISNUMBER(U11),U11&lt;=2),"Aesthetic mismatch",IF(AY11="High","Too fragile",IF(AND(ISNUMBER(R11),R11&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT11),AT11&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD11="Maybe",AD11="Price Review"),"Needs partner review",IF(AD11="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF11" s="13" t="n"/>
+      <c r="BG11" s="13" t="n"/>
+      <c r="BH11" s="13" t="n"/>
+      <c r="BI11" s="13" t="n"/>
+      <c r="BJ11" s="13" t="n"/>
+      <c r="BK11" s="13" t="n"/>
+      <c r="BL11" s="13">
+        <f>IF(C11="","",IF(AND(BG11="Yes",BH11="Yes",BI11="Yes",BJ11="Yes",BK11="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="14">
+      <c r="A12" s="20">
         <f>IF(C12="","","AYN-"&amp;UPPER(LEFT(E12,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="16">
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="22">
         <f>IF(I12="","",IF(J12="BDT",I12,IF(J12="USD",I12*USD_BDT,IF(J12="RMB",I12*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16">
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22">
         <f>IF(K12="","",K12+IFERROR(L12,0)+(K12*IF(M12="",CUSTOMS_PCT,M12))+IF(N12="",MISC_FEE,N12))</f>
         <v/>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="22">
         <f>IF(O12="","",ROUND(O12*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="22">
         <f>IF(P12="","",P12-O12)</f>
         <v/>
       </c>
-      <c r="R12" s="17">
+      <c r="R12" s="23">
         <f>IF(OR(P12="",P12=0),"",Q12/P12)</f>
         <v/>
       </c>
-      <c r="S12" s="14" t="n"/>
-      <c r="T12" s="14" t="n"/>
-      <c r="U12" s="14" t="n"/>
-      <c r="V12" s="14" t="n"/>
-      <c r="W12" s="14" t="n"/>
-      <c r="X12" s="14" t="n"/>
-      <c r="Y12" s="14" t="n"/>
-      <c r="Z12" s="14" t="n"/>
-      <c r="AA12" s="14" t="n"/>
-      <c r="AB12" s="14" t="n"/>
-      <c r="AC12" s="18">
+      <c r="S12" s="20" t="n"/>
+      <c r="T12" s="20" t="n"/>
+      <c r="U12" s="20" t="n"/>
+      <c r="V12" s="20" t="n"/>
+      <c r="W12" s="20" t="n"/>
+      <c r="X12" s="20" t="n"/>
+      <c r="Y12" s="20" t="n"/>
+      <c r="Z12" s="20" t="n"/>
+      <c r="AA12" s="20" t="n"/>
+      <c r="AB12" s="20" t="n"/>
+      <c r="AC12" s="24">
         <f>IF(COUNT(S12:AB12)&lt;10,"",(S12*W_FEMININE+T12*W_TREND+U12*W_AESTHETIC+V12*W_STYLE+W12*W_LIGHT+X12*W_REELS+Y12*W_GIFT+Z12*W_PRICEFIT+AA12*W_DEMAND+AB12*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD12" s="14">
+      <c r="AD12" s="20">
         <f>IF(P12="","",IF(P12&gt;HARD_REJECT_PRICE,"Reject",IF(P12&gt;MAX_PRICE,"Price Review",IF(AC12="","",IF(AND(AC12&gt;=BUY_THRESHOLD,OR(AB12&lt;=2,U12&lt;=2)),"Maybe",IF(AC12&gt;=BUY_THRESHOLD,"Buy",IF(AC12&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE12" s="14" t="n"/>
-      <c r="AF12" s="14" t="n"/>
-      <c r="AG12" s="14" t="n"/>
-      <c r="AH12" s="14" t="n"/>
-      <c r="AI12" s="15" t="n"/>
+      <c r="AE12" s="20" t="n"/>
+      <c r="AF12" s="20" t="n"/>
+      <c r="AG12" s="20" t="n"/>
+      <c r="AH12" s="20" t="n"/>
+      <c r="AI12" s="21" t="n"/>
       <c r="AJ12">
         <f>IF(AC12="",-9999-ROW()*0.0000001,AC12-ROW()*0.0000001)</f>
         <v/>
@@ -2120,67 +2871,100 @@
         <f>IF(AND(OR(AD12="Maybe",AD12="Price Review"),AG12&lt;&gt;"Approved",AG12&lt;&gt;"Rejected"),IF(AC12="",0,AC12)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO12" s="25" t="n"/>
+      <c r="AP12" s="25" t="n"/>
+      <c r="AQ12" s="26" t="n"/>
+      <c r="AR12" s="26" t="n"/>
+      <c r="AS12" s="20" t="n"/>
+      <c r="AT12" s="26" t="n"/>
+      <c r="AU12" s="26" t="n"/>
+      <c r="AV12" s="26" t="n"/>
+      <c r="AW12" s="22">
+        <f>IF(OR(O12="",AV12=""),"",O12*AV12)</f>
+        <v/>
+      </c>
+      <c r="AX12" s="20" t="n"/>
+      <c r="AY12" s="20" t="n"/>
+      <c r="AZ12" s="20" t="n"/>
+      <c r="BA12" s="20" t="n"/>
+      <c r="BB12" s="20" t="n"/>
+      <c r="BC12" s="22" t="n"/>
+      <c r="BD12" s="20" t="n"/>
+      <c r="BE12" s="20">
+        <f>IF(C12="","",IF(AND(ISNUMBER(P12),P12&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB12),AB12&lt;=2),"Quality risk",IF(AND(ISNUMBER(U12),U12&lt;=2),"Aesthetic mismatch",IF(AY12="High","Too fragile",IF(AND(ISNUMBER(R12),R12&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT12),AT12&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD12="Maybe",AD12="Price Review"),"Needs partner review",IF(AD12="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF12" s="20" t="n"/>
+      <c r="BG12" s="20" t="n"/>
+      <c r="BH12" s="20" t="n"/>
+      <c r="BI12" s="20" t="n"/>
+      <c r="BJ12" s="20" t="n"/>
+      <c r="BK12" s="20" t="n"/>
+      <c r="BL12" s="20">
+        <f>IF(C12="","",IF(AND(BG12="Yes",BH12="Yes",BI12="Yes",BJ12="Yes",BK12="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="13">
         <f>IF(C13="","","AYN-"&amp;UPPER(LEFT(E13,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="11">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="15">
         <f>IF(I13="","",IF(J13="BDT",I13,IF(J13="USD",I13*USD_BDT,IF(J13="RMB",I13*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11">
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15">
         <f>IF(K13="","",K13+IFERROR(L13,0)+(K13*IF(M13="",CUSTOMS_PCT,M13))+IF(N13="",MISC_FEE,N13))</f>
         <v/>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="15">
         <f>IF(O13="","",ROUND(O13*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="15">
         <f>IF(P13="","",P13-O13)</f>
         <v/>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="16">
         <f>IF(OR(P13="",P13=0),"",Q13/P13)</f>
         <v/>
       </c>
-      <c r="S13" s="9" t="n"/>
-      <c r="T13" s="9" t="n"/>
-      <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
-      <c r="W13" s="9" t="n"/>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="9" t="n"/>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="13">
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="13" t="n"/>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="13" t="n"/>
+      <c r="Y13" s="13" t="n"/>
+      <c r="Z13" s="13" t="n"/>
+      <c r="AA13" s="13" t="n"/>
+      <c r="AB13" s="13" t="n"/>
+      <c r="AC13" s="17">
         <f>IF(COUNT(S13:AB13)&lt;10,"",(S13*W_FEMININE+T13*W_TREND+U13*W_AESTHETIC+V13*W_STYLE+W13*W_LIGHT+X13*W_REELS+Y13*W_GIFT+Z13*W_PRICEFIT+AA13*W_DEMAND+AB13*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD13" s="9">
+      <c r="AD13" s="13">
         <f>IF(P13="","",IF(P13&gt;HARD_REJECT_PRICE,"Reject",IF(P13&gt;MAX_PRICE,"Price Review",IF(AC13="","",IF(AND(AC13&gt;=BUY_THRESHOLD,OR(AB13&lt;=2,U13&lt;=2)),"Maybe",IF(AC13&gt;=BUY_THRESHOLD,"Buy",IF(AC13&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE13" s="9" t="n"/>
-      <c r="AF13" s="9" t="n"/>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="10" t="n"/>
+      <c r="AE13" s="13" t="n"/>
+      <c r="AF13" s="13" t="n"/>
+      <c r="AG13" s="13" t="n"/>
+      <c r="AH13" s="13" t="n"/>
+      <c r="AI13" s="14" t="n"/>
       <c r="AJ13">
         <f>IF(AC13="",-9999-ROW()*0.0000001,AC13-ROW()*0.0000001)</f>
         <v/>
@@ -2201,67 +2985,100 @@
         <f>IF(AND(OR(AD13="Maybe",AD13="Price Review"),AG13&lt;&gt;"Approved",AG13&lt;&gt;"Rejected"),IF(AC13="",0,AC13)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO13" s="18" t="n"/>
+      <c r="AP13" s="18" t="n"/>
+      <c r="AQ13" s="19" t="n"/>
+      <c r="AR13" s="19" t="n"/>
+      <c r="AS13" s="13" t="n"/>
+      <c r="AT13" s="19" t="n"/>
+      <c r="AU13" s="19" t="n"/>
+      <c r="AV13" s="19" t="n"/>
+      <c r="AW13" s="15">
+        <f>IF(OR(O13="",AV13=""),"",O13*AV13)</f>
+        <v/>
+      </c>
+      <c r="AX13" s="13" t="n"/>
+      <c r="AY13" s="13" t="n"/>
+      <c r="AZ13" s="13" t="n"/>
+      <c r="BA13" s="13" t="n"/>
+      <c r="BB13" s="13" t="n"/>
+      <c r="BC13" s="15" t="n"/>
+      <c r="BD13" s="13" t="n"/>
+      <c r="BE13" s="13">
+        <f>IF(C13="","",IF(AND(ISNUMBER(P13),P13&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB13),AB13&lt;=2),"Quality risk",IF(AND(ISNUMBER(U13),U13&lt;=2),"Aesthetic mismatch",IF(AY13="High","Too fragile",IF(AND(ISNUMBER(R13),R13&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT13),AT13&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD13="Maybe",AD13="Price Review"),"Needs partner review",IF(AD13="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF13" s="13" t="n"/>
+      <c r="BG13" s="13" t="n"/>
+      <c r="BH13" s="13" t="n"/>
+      <c r="BI13" s="13" t="n"/>
+      <c r="BJ13" s="13" t="n"/>
+      <c r="BK13" s="13" t="n"/>
+      <c r="BL13" s="13">
+        <f>IF(C13="","",IF(AND(BG13="Yes",BH13="Yes",BI13="Yes",BJ13="Yes",BK13="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="14">
+      <c r="A14" s="20">
         <f>IF(C14="","","AYN-"&amp;UPPER(LEFT(E14,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="16">
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="22">
         <f>IF(I14="","",IF(J14="BDT",I14,IF(J14="USD",I14*USD_BDT,IF(J14="RMB",I14*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16">
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22">
         <f>IF(K14="","",K14+IFERROR(L14,0)+(K14*IF(M14="",CUSTOMS_PCT,M14))+IF(N14="",MISC_FEE,N14))</f>
         <v/>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="22">
         <f>IF(O14="","",ROUND(O14*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="22">
         <f>IF(P14="","",P14-O14)</f>
         <v/>
       </c>
-      <c r="R14" s="17">
+      <c r="R14" s="23">
         <f>IF(OR(P14="",P14=0),"",Q14/P14)</f>
         <v/>
       </c>
-      <c r="S14" s="14" t="n"/>
-      <c r="T14" s="14" t="n"/>
-      <c r="U14" s="14" t="n"/>
-      <c r="V14" s="14" t="n"/>
-      <c r="W14" s="14" t="n"/>
-      <c r="X14" s="14" t="n"/>
-      <c r="Y14" s="14" t="n"/>
-      <c r="Z14" s="14" t="n"/>
-      <c r="AA14" s="14" t="n"/>
-      <c r="AB14" s="14" t="n"/>
-      <c r="AC14" s="18">
+      <c r="S14" s="20" t="n"/>
+      <c r="T14" s="20" t="n"/>
+      <c r="U14" s="20" t="n"/>
+      <c r="V14" s="20" t="n"/>
+      <c r="W14" s="20" t="n"/>
+      <c r="X14" s="20" t="n"/>
+      <c r="Y14" s="20" t="n"/>
+      <c r="Z14" s="20" t="n"/>
+      <c r="AA14" s="20" t="n"/>
+      <c r="AB14" s="20" t="n"/>
+      <c r="AC14" s="24">
         <f>IF(COUNT(S14:AB14)&lt;10,"",(S14*W_FEMININE+T14*W_TREND+U14*W_AESTHETIC+V14*W_STYLE+W14*W_LIGHT+X14*W_REELS+Y14*W_GIFT+Z14*W_PRICEFIT+AA14*W_DEMAND+AB14*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD14" s="14">
+      <c r="AD14" s="20">
         <f>IF(P14="","",IF(P14&gt;HARD_REJECT_PRICE,"Reject",IF(P14&gt;MAX_PRICE,"Price Review",IF(AC14="","",IF(AND(AC14&gt;=BUY_THRESHOLD,OR(AB14&lt;=2,U14&lt;=2)),"Maybe",IF(AC14&gt;=BUY_THRESHOLD,"Buy",IF(AC14&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE14" s="14" t="n"/>
-      <c r="AF14" s="14" t="n"/>
-      <c r="AG14" s="14" t="n"/>
-      <c r="AH14" s="14" t="n"/>
-      <c r="AI14" s="15" t="n"/>
+      <c r="AE14" s="20" t="n"/>
+      <c r="AF14" s="20" t="n"/>
+      <c r="AG14" s="20" t="n"/>
+      <c r="AH14" s="20" t="n"/>
+      <c r="AI14" s="21" t="n"/>
       <c r="AJ14">
         <f>IF(AC14="",-9999-ROW()*0.0000001,AC14-ROW()*0.0000001)</f>
         <v/>
@@ -2282,67 +3099,100 @@
         <f>IF(AND(OR(AD14="Maybe",AD14="Price Review"),AG14&lt;&gt;"Approved",AG14&lt;&gt;"Rejected"),IF(AC14="",0,AC14)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO14" s="25" t="n"/>
+      <c r="AP14" s="25" t="n"/>
+      <c r="AQ14" s="26" t="n"/>
+      <c r="AR14" s="26" t="n"/>
+      <c r="AS14" s="20" t="n"/>
+      <c r="AT14" s="26" t="n"/>
+      <c r="AU14" s="26" t="n"/>
+      <c r="AV14" s="26" t="n"/>
+      <c r="AW14" s="22">
+        <f>IF(OR(O14="",AV14=""),"",O14*AV14)</f>
+        <v/>
+      </c>
+      <c r="AX14" s="20" t="n"/>
+      <c r="AY14" s="20" t="n"/>
+      <c r="AZ14" s="20" t="n"/>
+      <c r="BA14" s="20" t="n"/>
+      <c r="BB14" s="20" t="n"/>
+      <c r="BC14" s="22" t="n"/>
+      <c r="BD14" s="20" t="n"/>
+      <c r="BE14" s="20">
+        <f>IF(C14="","",IF(AND(ISNUMBER(P14),P14&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB14),AB14&lt;=2),"Quality risk",IF(AND(ISNUMBER(U14),U14&lt;=2),"Aesthetic mismatch",IF(AY14="High","Too fragile",IF(AND(ISNUMBER(R14),R14&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT14),AT14&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD14="Maybe",AD14="Price Review"),"Needs partner review",IF(AD14="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF14" s="20" t="n"/>
+      <c r="BG14" s="20" t="n"/>
+      <c r="BH14" s="20" t="n"/>
+      <c r="BI14" s="20" t="n"/>
+      <c r="BJ14" s="20" t="n"/>
+      <c r="BK14" s="20" t="n"/>
+      <c r="BL14" s="20">
+        <f>IF(C14="","",IF(AND(BG14="Yes",BH14="Yes",BI14="Yes",BJ14="Yes",BK14="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="13">
         <f>IF(C15="","","AYN-"&amp;UPPER(LEFT(E15,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="11">
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="15">
         <f>IF(I15="","",IF(J15="BDT",I15,IF(J15="USD",I15*USD_BDT,IF(J15="RMB",I15*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11">
+      <c r="L15" s="15" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15">
         <f>IF(K15="","",K15+IFERROR(L15,0)+(K15*IF(M15="",CUSTOMS_PCT,M15))+IF(N15="",MISC_FEE,N15))</f>
         <v/>
       </c>
-      <c r="P15" s="11">
+      <c r="P15" s="15">
         <f>IF(O15="","",ROUND(O15*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q15" s="11">
+      <c r="Q15" s="15">
         <f>IF(P15="","",P15-O15)</f>
         <v/>
       </c>
-      <c r="R15" s="12">
+      <c r="R15" s="16">
         <f>IF(OR(P15="",P15=0),"",Q15/P15)</f>
         <v/>
       </c>
-      <c r="S15" s="9" t="n"/>
-      <c r="T15" s="9" t="n"/>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="9" t="n"/>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="9" t="n"/>
-      <c r="Z15" s="9" t="n"/>
-      <c r="AA15" s="9" t="n"/>
-      <c r="AB15" s="9" t="n"/>
-      <c r="AC15" s="13">
+      <c r="S15" s="13" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="13" t="n"/>
+      <c r="W15" s="13" t="n"/>
+      <c r="X15" s="13" t="n"/>
+      <c r="Y15" s="13" t="n"/>
+      <c r="Z15" s="13" t="n"/>
+      <c r="AA15" s="13" t="n"/>
+      <c r="AB15" s="13" t="n"/>
+      <c r="AC15" s="17">
         <f>IF(COUNT(S15:AB15)&lt;10,"",(S15*W_FEMININE+T15*W_TREND+U15*W_AESTHETIC+V15*W_STYLE+W15*W_LIGHT+X15*W_REELS+Y15*W_GIFT+Z15*W_PRICEFIT+AA15*W_DEMAND+AB15*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD15" s="9">
+      <c r="AD15" s="13">
         <f>IF(P15="","",IF(P15&gt;HARD_REJECT_PRICE,"Reject",IF(P15&gt;MAX_PRICE,"Price Review",IF(AC15="","",IF(AND(AC15&gt;=BUY_THRESHOLD,OR(AB15&lt;=2,U15&lt;=2)),"Maybe",IF(AC15&gt;=BUY_THRESHOLD,"Buy",IF(AC15&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE15" s="9" t="n"/>
-      <c r="AF15" s="9" t="n"/>
-      <c r="AG15" s="9" t="n"/>
-      <c r="AH15" s="9" t="n"/>
-      <c r="AI15" s="10" t="n"/>
+      <c r="AE15" s="13" t="n"/>
+      <c r="AF15" s="13" t="n"/>
+      <c r="AG15" s="13" t="n"/>
+      <c r="AH15" s="13" t="n"/>
+      <c r="AI15" s="14" t="n"/>
       <c r="AJ15">
         <f>IF(AC15="",-9999-ROW()*0.0000001,AC15-ROW()*0.0000001)</f>
         <v/>
@@ -2363,67 +3213,100 @@
         <f>IF(AND(OR(AD15="Maybe",AD15="Price Review"),AG15&lt;&gt;"Approved",AG15&lt;&gt;"Rejected"),IF(AC15="",0,AC15)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO15" s="18" t="n"/>
+      <c r="AP15" s="18" t="n"/>
+      <c r="AQ15" s="19" t="n"/>
+      <c r="AR15" s="19" t="n"/>
+      <c r="AS15" s="13" t="n"/>
+      <c r="AT15" s="19" t="n"/>
+      <c r="AU15" s="19" t="n"/>
+      <c r="AV15" s="19" t="n"/>
+      <c r="AW15" s="15">
+        <f>IF(OR(O15="",AV15=""),"",O15*AV15)</f>
+        <v/>
+      </c>
+      <c r="AX15" s="13" t="n"/>
+      <c r="AY15" s="13" t="n"/>
+      <c r="AZ15" s="13" t="n"/>
+      <c r="BA15" s="13" t="n"/>
+      <c r="BB15" s="13" t="n"/>
+      <c r="BC15" s="15" t="n"/>
+      <c r="BD15" s="13" t="n"/>
+      <c r="BE15" s="13">
+        <f>IF(C15="","",IF(AND(ISNUMBER(P15),P15&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB15),AB15&lt;=2),"Quality risk",IF(AND(ISNUMBER(U15),U15&lt;=2),"Aesthetic mismatch",IF(AY15="High","Too fragile",IF(AND(ISNUMBER(R15),R15&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT15),AT15&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD15="Maybe",AD15="Price Review"),"Needs partner review",IF(AD15="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF15" s="13" t="n"/>
+      <c r="BG15" s="13" t="n"/>
+      <c r="BH15" s="13" t="n"/>
+      <c r="BI15" s="13" t="n"/>
+      <c r="BJ15" s="13" t="n"/>
+      <c r="BK15" s="13" t="n"/>
+      <c r="BL15" s="13">
+        <f>IF(C15="","",IF(AND(BG15="Yes",BH15="Yes",BI15="Yes",BJ15="Yes",BK15="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="14">
+      <c r="A16" s="20">
         <f>IF(C16="","","AYN-"&amp;UPPER(LEFT(E16,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="16">
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="22">
         <f>IF(I16="","",IF(J16="BDT",I16,IF(J16="USD",I16*USD_BDT,IF(J16="RMB",I16*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16">
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="23" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22">
         <f>IF(K16="","",K16+IFERROR(L16,0)+(K16*IF(M16="",CUSTOMS_PCT,M16))+IF(N16="",MISC_FEE,N16))</f>
         <v/>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="22">
         <f>IF(O16="","",ROUND(O16*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="22">
         <f>IF(P16="","",P16-O16)</f>
         <v/>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="23">
         <f>IF(OR(P16="",P16=0),"",Q16/P16)</f>
         <v/>
       </c>
-      <c r="S16" s="14" t="n"/>
-      <c r="T16" s="14" t="n"/>
-      <c r="U16" s="14" t="n"/>
-      <c r="V16" s="14" t="n"/>
-      <c r="W16" s="14" t="n"/>
-      <c r="X16" s="14" t="n"/>
-      <c r="Y16" s="14" t="n"/>
-      <c r="Z16" s="14" t="n"/>
-      <c r="AA16" s="14" t="n"/>
-      <c r="AB16" s="14" t="n"/>
-      <c r="AC16" s="18">
+      <c r="S16" s="20" t="n"/>
+      <c r="T16" s="20" t="n"/>
+      <c r="U16" s="20" t="n"/>
+      <c r="V16" s="20" t="n"/>
+      <c r="W16" s="20" t="n"/>
+      <c r="X16" s="20" t="n"/>
+      <c r="Y16" s="20" t="n"/>
+      <c r="Z16" s="20" t="n"/>
+      <c r="AA16" s="20" t="n"/>
+      <c r="AB16" s="20" t="n"/>
+      <c r="AC16" s="24">
         <f>IF(COUNT(S16:AB16)&lt;10,"",(S16*W_FEMININE+T16*W_TREND+U16*W_AESTHETIC+V16*W_STYLE+W16*W_LIGHT+X16*W_REELS+Y16*W_GIFT+Z16*W_PRICEFIT+AA16*W_DEMAND+AB16*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD16" s="14">
+      <c r="AD16" s="20">
         <f>IF(P16="","",IF(P16&gt;HARD_REJECT_PRICE,"Reject",IF(P16&gt;MAX_PRICE,"Price Review",IF(AC16="","",IF(AND(AC16&gt;=BUY_THRESHOLD,OR(AB16&lt;=2,U16&lt;=2)),"Maybe",IF(AC16&gt;=BUY_THRESHOLD,"Buy",IF(AC16&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE16" s="14" t="n"/>
-      <c r="AF16" s="14" t="n"/>
-      <c r="AG16" s="14" t="n"/>
-      <c r="AH16" s="14" t="n"/>
-      <c r="AI16" s="15" t="n"/>
+      <c r="AE16" s="20" t="n"/>
+      <c r="AF16" s="20" t="n"/>
+      <c r="AG16" s="20" t="n"/>
+      <c r="AH16" s="20" t="n"/>
+      <c r="AI16" s="21" t="n"/>
       <c r="AJ16">
         <f>IF(AC16="",-9999-ROW()*0.0000001,AC16-ROW()*0.0000001)</f>
         <v/>
@@ -2444,67 +3327,100 @@
         <f>IF(AND(OR(AD16="Maybe",AD16="Price Review"),AG16&lt;&gt;"Approved",AG16&lt;&gt;"Rejected"),IF(AC16="",0,AC16)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO16" s="25" t="n"/>
+      <c r="AP16" s="25" t="n"/>
+      <c r="AQ16" s="26" t="n"/>
+      <c r="AR16" s="26" t="n"/>
+      <c r="AS16" s="20" t="n"/>
+      <c r="AT16" s="26" t="n"/>
+      <c r="AU16" s="26" t="n"/>
+      <c r="AV16" s="26" t="n"/>
+      <c r="AW16" s="22">
+        <f>IF(OR(O16="",AV16=""),"",O16*AV16)</f>
+        <v/>
+      </c>
+      <c r="AX16" s="20" t="n"/>
+      <c r="AY16" s="20" t="n"/>
+      <c r="AZ16" s="20" t="n"/>
+      <c r="BA16" s="20" t="n"/>
+      <c r="BB16" s="20" t="n"/>
+      <c r="BC16" s="22" t="n"/>
+      <c r="BD16" s="20" t="n"/>
+      <c r="BE16" s="20">
+        <f>IF(C16="","",IF(AND(ISNUMBER(P16),P16&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB16),AB16&lt;=2),"Quality risk",IF(AND(ISNUMBER(U16),U16&lt;=2),"Aesthetic mismatch",IF(AY16="High","Too fragile",IF(AND(ISNUMBER(R16),R16&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT16),AT16&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD16="Maybe",AD16="Price Review"),"Needs partner review",IF(AD16="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF16" s="20" t="n"/>
+      <c r="BG16" s="20" t="n"/>
+      <c r="BH16" s="20" t="n"/>
+      <c r="BI16" s="20" t="n"/>
+      <c r="BJ16" s="20" t="n"/>
+      <c r="BK16" s="20" t="n"/>
+      <c r="BL16" s="20">
+        <f>IF(C16="","",IF(AND(BG16="Yes",BH16="Yes",BI16="Yes",BJ16="Yes",BK16="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="13">
         <f>IF(C17="","","AYN-"&amp;UPPER(LEFT(E17,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="11">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="15">
         <f>IF(I17="","",IF(J17="BDT",I17,IF(J17="USD",I17*USD_BDT,IF(J17="RMB",I17*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11">
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15">
         <f>IF(K17="","",K17+IFERROR(L17,0)+(K17*IF(M17="",CUSTOMS_PCT,M17))+IF(N17="",MISC_FEE,N17))</f>
         <v/>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="15">
         <f>IF(O17="","",ROUND(O17*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q17" s="11">
+      <c r="Q17" s="15">
         <f>IF(P17="","",P17-O17)</f>
         <v/>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="16">
         <f>IF(OR(P17="",P17=0),"",Q17/P17)</f>
         <v/>
       </c>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="9" t="n"/>
-      <c r="U17" s="9" t="n"/>
-      <c r="V17" s="9" t="n"/>
-      <c r="W17" s="9" t="n"/>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="9" t="n"/>
-      <c r="Z17" s="9" t="n"/>
-      <c r="AA17" s="9" t="n"/>
-      <c r="AB17" s="9" t="n"/>
-      <c r="AC17" s="13">
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="13" t="n"/>
+      <c r="W17" s="13" t="n"/>
+      <c r="X17" s="13" t="n"/>
+      <c r="Y17" s="13" t="n"/>
+      <c r="Z17" s="13" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="13" t="n"/>
+      <c r="AC17" s="17">
         <f>IF(COUNT(S17:AB17)&lt;10,"",(S17*W_FEMININE+T17*W_TREND+U17*W_AESTHETIC+V17*W_STYLE+W17*W_LIGHT+X17*W_REELS+Y17*W_GIFT+Z17*W_PRICEFIT+AA17*W_DEMAND+AB17*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD17" s="9">
+      <c r="AD17" s="13">
         <f>IF(P17="","",IF(P17&gt;HARD_REJECT_PRICE,"Reject",IF(P17&gt;MAX_PRICE,"Price Review",IF(AC17="","",IF(AND(AC17&gt;=BUY_THRESHOLD,OR(AB17&lt;=2,U17&lt;=2)),"Maybe",IF(AC17&gt;=BUY_THRESHOLD,"Buy",IF(AC17&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE17" s="9" t="n"/>
-      <c r="AF17" s="9" t="n"/>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="10" t="n"/>
+      <c r="AE17" s="13" t="n"/>
+      <c r="AF17" s="13" t="n"/>
+      <c r="AG17" s="13" t="n"/>
+      <c r="AH17" s="13" t="n"/>
+      <c r="AI17" s="14" t="n"/>
       <c r="AJ17">
         <f>IF(AC17="",-9999-ROW()*0.0000001,AC17-ROW()*0.0000001)</f>
         <v/>
@@ -2525,67 +3441,100 @@
         <f>IF(AND(OR(AD17="Maybe",AD17="Price Review"),AG17&lt;&gt;"Approved",AG17&lt;&gt;"Rejected"),IF(AC17="",0,AC17)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO17" s="18" t="n"/>
+      <c r="AP17" s="18" t="n"/>
+      <c r="AQ17" s="19" t="n"/>
+      <c r="AR17" s="19" t="n"/>
+      <c r="AS17" s="13" t="n"/>
+      <c r="AT17" s="19" t="n"/>
+      <c r="AU17" s="19" t="n"/>
+      <c r="AV17" s="19" t="n"/>
+      <c r="AW17" s="15">
+        <f>IF(OR(O17="",AV17=""),"",O17*AV17)</f>
+        <v/>
+      </c>
+      <c r="AX17" s="13" t="n"/>
+      <c r="AY17" s="13" t="n"/>
+      <c r="AZ17" s="13" t="n"/>
+      <c r="BA17" s="13" t="n"/>
+      <c r="BB17" s="13" t="n"/>
+      <c r="BC17" s="15" t="n"/>
+      <c r="BD17" s="13" t="n"/>
+      <c r="BE17" s="13">
+        <f>IF(C17="","",IF(AND(ISNUMBER(P17),P17&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB17),AB17&lt;=2),"Quality risk",IF(AND(ISNUMBER(U17),U17&lt;=2),"Aesthetic mismatch",IF(AY17="High","Too fragile",IF(AND(ISNUMBER(R17),R17&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT17),AT17&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD17="Maybe",AD17="Price Review"),"Needs partner review",IF(AD17="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF17" s="13" t="n"/>
+      <c r="BG17" s="13" t="n"/>
+      <c r="BH17" s="13" t="n"/>
+      <c r="BI17" s="13" t="n"/>
+      <c r="BJ17" s="13" t="n"/>
+      <c r="BK17" s="13" t="n"/>
+      <c r="BL17" s="13">
+        <f>IF(C17="","",IF(AND(BG17="Yes",BH17="Yes",BI17="Yes",BJ17="Yes",BK17="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="14">
+      <c r="A18" s="20">
         <f>IF(C18="","","AYN-"&amp;UPPER(LEFT(E18,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="16">
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="22">
         <f>IF(I18="","",IF(J18="BDT",I18,IF(J18="USD",I18*USD_BDT,IF(J18="RMB",I18*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="17" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16">
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="23" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22">
         <f>IF(K18="","",K18+IFERROR(L18,0)+(K18*IF(M18="",CUSTOMS_PCT,M18))+IF(N18="",MISC_FEE,N18))</f>
         <v/>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="22">
         <f>IF(O18="","",ROUND(O18*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="22">
         <f>IF(P18="","",P18-O18)</f>
         <v/>
       </c>
-      <c r="R18" s="17">
+      <c r="R18" s="23">
         <f>IF(OR(P18="",P18=0),"",Q18/P18)</f>
         <v/>
       </c>
-      <c r="S18" s="14" t="n"/>
-      <c r="T18" s="14" t="n"/>
-      <c r="U18" s="14" t="n"/>
-      <c r="V18" s="14" t="n"/>
-      <c r="W18" s="14" t="n"/>
-      <c r="X18" s="14" t="n"/>
-      <c r="Y18" s="14" t="n"/>
-      <c r="Z18" s="14" t="n"/>
-      <c r="AA18" s="14" t="n"/>
-      <c r="AB18" s="14" t="n"/>
-      <c r="AC18" s="18">
+      <c r="S18" s="20" t="n"/>
+      <c r="T18" s="20" t="n"/>
+      <c r="U18" s="20" t="n"/>
+      <c r="V18" s="20" t="n"/>
+      <c r="W18" s="20" t="n"/>
+      <c r="X18" s="20" t="n"/>
+      <c r="Y18" s="20" t="n"/>
+      <c r="Z18" s="20" t="n"/>
+      <c r="AA18" s="20" t="n"/>
+      <c r="AB18" s="20" t="n"/>
+      <c r="AC18" s="24">
         <f>IF(COUNT(S18:AB18)&lt;10,"",(S18*W_FEMININE+T18*W_TREND+U18*W_AESTHETIC+V18*W_STYLE+W18*W_LIGHT+X18*W_REELS+Y18*W_GIFT+Z18*W_PRICEFIT+AA18*W_DEMAND+AB18*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD18" s="14">
+      <c r="AD18" s="20">
         <f>IF(P18="","",IF(P18&gt;HARD_REJECT_PRICE,"Reject",IF(P18&gt;MAX_PRICE,"Price Review",IF(AC18="","",IF(AND(AC18&gt;=BUY_THRESHOLD,OR(AB18&lt;=2,U18&lt;=2)),"Maybe",IF(AC18&gt;=BUY_THRESHOLD,"Buy",IF(AC18&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE18" s="14" t="n"/>
-      <c r="AF18" s="14" t="n"/>
-      <c r="AG18" s="14" t="n"/>
-      <c r="AH18" s="14" t="n"/>
-      <c r="AI18" s="15" t="n"/>
+      <c r="AE18" s="20" t="n"/>
+      <c r="AF18" s="20" t="n"/>
+      <c r="AG18" s="20" t="n"/>
+      <c r="AH18" s="20" t="n"/>
+      <c r="AI18" s="21" t="n"/>
       <c r="AJ18">
         <f>IF(AC18="",-9999-ROW()*0.0000001,AC18-ROW()*0.0000001)</f>
         <v/>
@@ -2606,67 +3555,100 @@
         <f>IF(AND(OR(AD18="Maybe",AD18="Price Review"),AG18&lt;&gt;"Approved",AG18&lt;&gt;"Rejected"),IF(AC18="",0,AC18)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO18" s="25" t="n"/>
+      <c r="AP18" s="25" t="n"/>
+      <c r="AQ18" s="26" t="n"/>
+      <c r="AR18" s="26" t="n"/>
+      <c r="AS18" s="20" t="n"/>
+      <c r="AT18" s="26" t="n"/>
+      <c r="AU18" s="26" t="n"/>
+      <c r="AV18" s="26" t="n"/>
+      <c r="AW18" s="22">
+        <f>IF(OR(O18="",AV18=""),"",O18*AV18)</f>
+        <v/>
+      </c>
+      <c r="AX18" s="20" t="n"/>
+      <c r="AY18" s="20" t="n"/>
+      <c r="AZ18" s="20" t="n"/>
+      <c r="BA18" s="20" t="n"/>
+      <c r="BB18" s="20" t="n"/>
+      <c r="BC18" s="22" t="n"/>
+      <c r="BD18" s="20" t="n"/>
+      <c r="BE18" s="20">
+        <f>IF(C18="","",IF(AND(ISNUMBER(P18),P18&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB18),AB18&lt;=2),"Quality risk",IF(AND(ISNUMBER(U18),U18&lt;=2),"Aesthetic mismatch",IF(AY18="High","Too fragile",IF(AND(ISNUMBER(R18),R18&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT18),AT18&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD18="Maybe",AD18="Price Review"),"Needs partner review",IF(AD18="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF18" s="20" t="n"/>
+      <c r="BG18" s="20" t="n"/>
+      <c r="BH18" s="20" t="n"/>
+      <c r="BI18" s="20" t="n"/>
+      <c r="BJ18" s="20" t="n"/>
+      <c r="BK18" s="20" t="n"/>
+      <c r="BL18" s="20">
+        <f>IF(C18="","",IF(AND(BG18="Yes",BH18="Yes",BI18="Yes",BJ18="Yes",BK18="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="13">
         <f>IF(C19="","","AYN-"&amp;UPPER(LEFT(E19,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="11">
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="15">
         <f>IF(I19="","",IF(J19="BDT",I19,IF(J19="USD",I19*USD_BDT,IF(J19="RMB",I19*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11">
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15">
         <f>IF(K19="","",K19+IFERROR(L19,0)+(K19*IF(M19="",CUSTOMS_PCT,M19))+IF(N19="",MISC_FEE,N19))</f>
         <v/>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="15">
         <f>IF(O19="","",ROUND(O19*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q19" s="11">
+      <c r="Q19" s="15">
         <f>IF(P19="","",P19-O19)</f>
         <v/>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="16">
         <f>IF(OR(P19="",P19=0),"",Q19/P19)</f>
         <v/>
       </c>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="9" t="n"/>
-      <c r="U19" s="9" t="n"/>
-      <c r="V19" s="9" t="n"/>
-      <c r="W19" s="9" t="n"/>
-      <c r="X19" s="9" t="n"/>
-      <c r="Y19" s="9" t="n"/>
-      <c r="Z19" s="9" t="n"/>
-      <c r="AA19" s="9" t="n"/>
-      <c r="AB19" s="9" t="n"/>
-      <c r="AC19" s="13">
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="13" t="n"/>
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="13" t="n"/>
+      <c r="Y19" s="13" t="n"/>
+      <c r="Z19" s="13" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="13" t="n"/>
+      <c r="AC19" s="17">
         <f>IF(COUNT(S19:AB19)&lt;10,"",(S19*W_FEMININE+T19*W_TREND+U19*W_AESTHETIC+V19*W_STYLE+W19*W_LIGHT+X19*W_REELS+Y19*W_GIFT+Z19*W_PRICEFIT+AA19*W_DEMAND+AB19*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD19" s="9">
+      <c r="AD19" s="13">
         <f>IF(P19="","",IF(P19&gt;HARD_REJECT_PRICE,"Reject",IF(P19&gt;MAX_PRICE,"Price Review",IF(AC19="","",IF(AND(AC19&gt;=BUY_THRESHOLD,OR(AB19&lt;=2,U19&lt;=2)),"Maybe",IF(AC19&gt;=BUY_THRESHOLD,"Buy",IF(AC19&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE19" s="9" t="n"/>
-      <c r="AF19" s="9" t="n"/>
-      <c r="AG19" s="9" t="n"/>
-      <c r="AH19" s="9" t="n"/>
-      <c r="AI19" s="10" t="n"/>
+      <c r="AE19" s="13" t="n"/>
+      <c r="AF19" s="13" t="n"/>
+      <c r="AG19" s="13" t="n"/>
+      <c r="AH19" s="13" t="n"/>
+      <c r="AI19" s="14" t="n"/>
       <c r="AJ19">
         <f>IF(AC19="",-9999-ROW()*0.0000001,AC19-ROW()*0.0000001)</f>
         <v/>
@@ -2687,67 +3669,100 @@
         <f>IF(AND(OR(AD19="Maybe",AD19="Price Review"),AG19&lt;&gt;"Approved",AG19&lt;&gt;"Rejected"),IF(AC19="",0,AC19)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO19" s="18" t="n"/>
+      <c r="AP19" s="18" t="n"/>
+      <c r="AQ19" s="19" t="n"/>
+      <c r="AR19" s="19" t="n"/>
+      <c r="AS19" s="13" t="n"/>
+      <c r="AT19" s="19" t="n"/>
+      <c r="AU19" s="19" t="n"/>
+      <c r="AV19" s="19" t="n"/>
+      <c r="AW19" s="15">
+        <f>IF(OR(O19="",AV19=""),"",O19*AV19)</f>
+        <v/>
+      </c>
+      <c r="AX19" s="13" t="n"/>
+      <c r="AY19" s="13" t="n"/>
+      <c r="AZ19" s="13" t="n"/>
+      <c r="BA19" s="13" t="n"/>
+      <c r="BB19" s="13" t="n"/>
+      <c r="BC19" s="15" t="n"/>
+      <c r="BD19" s="13" t="n"/>
+      <c r="BE19" s="13">
+        <f>IF(C19="","",IF(AND(ISNUMBER(P19),P19&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB19),AB19&lt;=2),"Quality risk",IF(AND(ISNUMBER(U19),U19&lt;=2),"Aesthetic mismatch",IF(AY19="High","Too fragile",IF(AND(ISNUMBER(R19),R19&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT19),AT19&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD19="Maybe",AD19="Price Review"),"Needs partner review",IF(AD19="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF19" s="13" t="n"/>
+      <c r="BG19" s="13" t="n"/>
+      <c r="BH19" s="13" t="n"/>
+      <c r="BI19" s="13" t="n"/>
+      <c r="BJ19" s="13" t="n"/>
+      <c r="BK19" s="13" t="n"/>
+      <c r="BL19" s="13">
+        <f>IF(C19="","",IF(AND(BG19="Yes",BH19="Yes",BI19="Yes",BJ19="Yes",BK19="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="14">
+      <c r="A20" s="20">
         <f>IF(C20="","","AYN-"&amp;UPPER(LEFT(E20,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="16">
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="22">
         <f>IF(I20="","",IF(J20="BDT",I20,IF(J20="USD",I20*USD_BDT,IF(J20="RMB",I20*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16">
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22">
         <f>IF(K20="","",K20+IFERROR(L20,0)+(K20*IF(M20="",CUSTOMS_PCT,M20))+IF(N20="",MISC_FEE,N20))</f>
         <v/>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="22">
         <f>IF(O20="","",ROUND(O20*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="22">
         <f>IF(P20="","",P20-O20)</f>
         <v/>
       </c>
-      <c r="R20" s="17">
+      <c r="R20" s="23">
         <f>IF(OR(P20="",P20=0),"",Q20/P20)</f>
         <v/>
       </c>
-      <c r="S20" s="14" t="n"/>
-      <c r="T20" s="14" t="n"/>
-      <c r="U20" s="14" t="n"/>
-      <c r="V20" s="14" t="n"/>
-      <c r="W20" s="14" t="n"/>
-      <c r="X20" s="14" t="n"/>
-      <c r="Y20" s="14" t="n"/>
-      <c r="Z20" s="14" t="n"/>
-      <c r="AA20" s="14" t="n"/>
-      <c r="AB20" s="14" t="n"/>
-      <c r="AC20" s="18">
+      <c r="S20" s="20" t="n"/>
+      <c r="T20" s="20" t="n"/>
+      <c r="U20" s="20" t="n"/>
+      <c r="V20" s="20" t="n"/>
+      <c r="W20" s="20" t="n"/>
+      <c r="X20" s="20" t="n"/>
+      <c r="Y20" s="20" t="n"/>
+      <c r="Z20" s="20" t="n"/>
+      <c r="AA20" s="20" t="n"/>
+      <c r="AB20" s="20" t="n"/>
+      <c r="AC20" s="24">
         <f>IF(COUNT(S20:AB20)&lt;10,"",(S20*W_FEMININE+T20*W_TREND+U20*W_AESTHETIC+V20*W_STYLE+W20*W_LIGHT+X20*W_REELS+Y20*W_GIFT+Z20*W_PRICEFIT+AA20*W_DEMAND+AB20*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD20" s="14">
+      <c r="AD20" s="20">
         <f>IF(P20="","",IF(P20&gt;HARD_REJECT_PRICE,"Reject",IF(P20&gt;MAX_PRICE,"Price Review",IF(AC20="","",IF(AND(AC20&gt;=BUY_THRESHOLD,OR(AB20&lt;=2,U20&lt;=2)),"Maybe",IF(AC20&gt;=BUY_THRESHOLD,"Buy",IF(AC20&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE20" s="14" t="n"/>
-      <c r="AF20" s="14" t="n"/>
-      <c r="AG20" s="14" t="n"/>
-      <c r="AH20" s="14" t="n"/>
-      <c r="AI20" s="15" t="n"/>
+      <c r="AE20" s="20" t="n"/>
+      <c r="AF20" s="20" t="n"/>
+      <c r="AG20" s="20" t="n"/>
+      <c r="AH20" s="20" t="n"/>
+      <c r="AI20" s="21" t="n"/>
       <c r="AJ20">
         <f>IF(AC20="",-9999-ROW()*0.0000001,AC20-ROW()*0.0000001)</f>
         <v/>
@@ -2768,67 +3783,100 @@
         <f>IF(AND(OR(AD20="Maybe",AD20="Price Review"),AG20&lt;&gt;"Approved",AG20&lt;&gt;"Rejected"),IF(AC20="",0,AC20)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO20" s="25" t="n"/>
+      <c r="AP20" s="25" t="n"/>
+      <c r="AQ20" s="26" t="n"/>
+      <c r="AR20" s="26" t="n"/>
+      <c r="AS20" s="20" t="n"/>
+      <c r="AT20" s="26" t="n"/>
+      <c r="AU20" s="26" t="n"/>
+      <c r="AV20" s="26" t="n"/>
+      <c r="AW20" s="22">
+        <f>IF(OR(O20="",AV20=""),"",O20*AV20)</f>
+        <v/>
+      </c>
+      <c r="AX20" s="20" t="n"/>
+      <c r="AY20" s="20" t="n"/>
+      <c r="AZ20" s="20" t="n"/>
+      <c r="BA20" s="20" t="n"/>
+      <c r="BB20" s="20" t="n"/>
+      <c r="BC20" s="22" t="n"/>
+      <c r="BD20" s="20" t="n"/>
+      <c r="BE20" s="20">
+        <f>IF(C20="","",IF(AND(ISNUMBER(P20),P20&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB20),AB20&lt;=2),"Quality risk",IF(AND(ISNUMBER(U20),U20&lt;=2),"Aesthetic mismatch",IF(AY20="High","Too fragile",IF(AND(ISNUMBER(R20),R20&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT20),AT20&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD20="Maybe",AD20="Price Review"),"Needs partner review",IF(AD20="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF20" s="20" t="n"/>
+      <c r="BG20" s="20" t="n"/>
+      <c r="BH20" s="20" t="n"/>
+      <c r="BI20" s="20" t="n"/>
+      <c r="BJ20" s="20" t="n"/>
+      <c r="BK20" s="20" t="n"/>
+      <c r="BL20" s="20">
+        <f>IF(C20="","",IF(AND(BG20="Yes",BH20="Yes",BI20="Yes",BJ20="Yes",BK20="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="13">
         <f>IF(C21="","","AYN-"&amp;UPPER(LEFT(E21,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="11">
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="15">
         <f>IF(I21="","",IF(J21="BDT",I21,IF(J21="USD",I21*USD_BDT,IF(J21="RMB",I21*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11">
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15">
         <f>IF(K21="","",K21+IFERROR(L21,0)+(K21*IF(M21="",CUSTOMS_PCT,M21))+IF(N21="",MISC_FEE,N21))</f>
         <v/>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="15">
         <f>IF(O21="","",ROUND(O21*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="15">
         <f>IF(P21="","",P21-O21)</f>
         <v/>
       </c>
-      <c r="R21" s="12">
+      <c r="R21" s="16">
         <f>IF(OR(P21="",P21=0),"",Q21/P21)</f>
         <v/>
       </c>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="9" t="n"/>
-      <c r="U21" s="9" t="n"/>
-      <c r="V21" s="9" t="n"/>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="9" t="n"/>
-      <c r="Y21" s="9" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="9" t="n"/>
-      <c r="AB21" s="9" t="n"/>
-      <c r="AC21" s="13">
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="13" t="n"/>
+      <c r="W21" s="13" t="n"/>
+      <c r="X21" s="13" t="n"/>
+      <c r="Y21" s="13" t="n"/>
+      <c r="Z21" s="13" t="n"/>
+      <c r="AA21" s="13" t="n"/>
+      <c r="AB21" s="13" t="n"/>
+      <c r="AC21" s="17">
         <f>IF(COUNT(S21:AB21)&lt;10,"",(S21*W_FEMININE+T21*W_TREND+U21*W_AESTHETIC+V21*W_STYLE+W21*W_LIGHT+X21*W_REELS+Y21*W_GIFT+Z21*W_PRICEFIT+AA21*W_DEMAND+AB21*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD21" s="9">
+      <c r="AD21" s="13">
         <f>IF(P21="","",IF(P21&gt;HARD_REJECT_PRICE,"Reject",IF(P21&gt;MAX_PRICE,"Price Review",IF(AC21="","",IF(AND(AC21&gt;=BUY_THRESHOLD,OR(AB21&lt;=2,U21&lt;=2)),"Maybe",IF(AC21&gt;=BUY_THRESHOLD,"Buy",IF(AC21&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE21" s="9" t="n"/>
-      <c r="AF21" s="9" t="n"/>
-      <c r="AG21" s="9" t="n"/>
-      <c r="AH21" s="9" t="n"/>
-      <c r="AI21" s="10" t="n"/>
+      <c r="AE21" s="13" t="n"/>
+      <c r="AF21" s="13" t="n"/>
+      <c r="AG21" s="13" t="n"/>
+      <c r="AH21" s="13" t="n"/>
+      <c r="AI21" s="14" t="n"/>
       <c r="AJ21">
         <f>IF(AC21="",-9999-ROW()*0.0000001,AC21-ROW()*0.0000001)</f>
         <v/>
@@ -2849,67 +3897,100 @@
         <f>IF(AND(OR(AD21="Maybe",AD21="Price Review"),AG21&lt;&gt;"Approved",AG21&lt;&gt;"Rejected"),IF(AC21="",0,AC21)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO21" s="18" t="n"/>
+      <c r="AP21" s="18" t="n"/>
+      <c r="AQ21" s="19" t="n"/>
+      <c r="AR21" s="19" t="n"/>
+      <c r="AS21" s="13" t="n"/>
+      <c r="AT21" s="19" t="n"/>
+      <c r="AU21" s="19" t="n"/>
+      <c r="AV21" s="19" t="n"/>
+      <c r="AW21" s="15">
+        <f>IF(OR(O21="",AV21=""),"",O21*AV21)</f>
+        <v/>
+      </c>
+      <c r="AX21" s="13" t="n"/>
+      <c r="AY21" s="13" t="n"/>
+      <c r="AZ21" s="13" t="n"/>
+      <c r="BA21" s="13" t="n"/>
+      <c r="BB21" s="13" t="n"/>
+      <c r="BC21" s="15" t="n"/>
+      <c r="BD21" s="13" t="n"/>
+      <c r="BE21" s="13">
+        <f>IF(C21="","",IF(AND(ISNUMBER(P21),P21&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB21),AB21&lt;=2),"Quality risk",IF(AND(ISNUMBER(U21),U21&lt;=2),"Aesthetic mismatch",IF(AY21="High","Too fragile",IF(AND(ISNUMBER(R21),R21&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT21),AT21&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD21="Maybe",AD21="Price Review"),"Needs partner review",IF(AD21="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF21" s="13" t="n"/>
+      <c r="BG21" s="13" t="n"/>
+      <c r="BH21" s="13" t="n"/>
+      <c r="BI21" s="13" t="n"/>
+      <c r="BJ21" s="13" t="n"/>
+      <c r="BK21" s="13" t="n"/>
+      <c r="BL21" s="13">
+        <f>IF(C21="","",IF(AND(BG21="Yes",BH21="Yes",BI21="Yes",BJ21="Yes",BK21="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="14">
+      <c r="A22" s="20">
         <f>IF(C22="","","AYN-"&amp;UPPER(LEFT(E22,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="14" t="n"/>
-      <c r="I22" s="14" t="n"/>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="16">
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="22">
         <f>IF(I22="","",IF(J22="BDT",I22,IF(J22="USD",I22*USD_BDT,IF(J22="RMB",I22*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
-      <c r="M22" s="17" t="n"/>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16">
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22">
         <f>IF(K22="","",K22+IFERROR(L22,0)+(K22*IF(M22="",CUSTOMS_PCT,M22))+IF(N22="",MISC_FEE,N22))</f>
         <v/>
       </c>
-      <c r="P22" s="16">
+      <c r="P22" s="22">
         <f>IF(O22="","",ROUND(O22*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q22" s="16">
+      <c r="Q22" s="22">
         <f>IF(P22="","",P22-O22)</f>
         <v/>
       </c>
-      <c r="R22" s="17">
+      <c r="R22" s="23">
         <f>IF(OR(P22="",P22=0),"",Q22/P22)</f>
         <v/>
       </c>
-      <c r="S22" s="14" t="n"/>
-      <c r="T22" s="14" t="n"/>
-      <c r="U22" s="14" t="n"/>
-      <c r="V22" s="14" t="n"/>
-      <c r="W22" s="14" t="n"/>
-      <c r="X22" s="14" t="n"/>
-      <c r="Y22" s="14" t="n"/>
-      <c r="Z22" s="14" t="n"/>
-      <c r="AA22" s="14" t="n"/>
-      <c r="AB22" s="14" t="n"/>
-      <c r="AC22" s="18">
+      <c r="S22" s="20" t="n"/>
+      <c r="T22" s="20" t="n"/>
+      <c r="U22" s="20" t="n"/>
+      <c r="V22" s="20" t="n"/>
+      <c r="W22" s="20" t="n"/>
+      <c r="X22" s="20" t="n"/>
+      <c r="Y22" s="20" t="n"/>
+      <c r="Z22" s="20" t="n"/>
+      <c r="AA22" s="20" t="n"/>
+      <c r="AB22" s="20" t="n"/>
+      <c r="AC22" s="24">
         <f>IF(COUNT(S22:AB22)&lt;10,"",(S22*W_FEMININE+T22*W_TREND+U22*W_AESTHETIC+V22*W_STYLE+W22*W_LIGHT+X22*W_REELS+Y22*W_GIFT+Z22*W_PRICEFIT+AA22*W_DEMAND+AB22*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD22" s="14">
+      <c r="AD22" s="20">
         <f>IF(P22="","",IF(P22&gt;HARD_REJECT_PRICE,"Reject",IF(P22&gt;MAX_PRICE,"Price Review",IF(AC22="","",IF(AND(AC22&gt;=BUY_THRESHOLD,OR(AB22&lt;=2,U22&lt;=2)),"Maybe",IF(AC22&gt;=BUY_THRESHOLD,"Buy",IF(AC22&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE22" s="14" t="n"/>
-      <c r="AF22" s="14" t="n"/>
-      <c r="AG22" s="14" t="n"/>
-      <c r="AH22" s="14" t="n"/>
-      <c r="AI22" s="15" t="n"/>
+      <c r="AE22" s="20" t="n"/>
+      <c r="AF22" s="20" t="n"/>
+      <c r="AG22" s="20" t="n"/>
+      <c r="AH22" s="20" t="n"/>
+      <c r="AI22" s="21" t="n"/>
       <c r="AJ22">
         <f>IF(AC22="",-9999-ROW()*0.0000001,AC22-ROW()*0.0000001)</f>
         <v/>
@@ -2930,67 +4011,100 @@
         <f>IF(AND(OR(AD22="Maybe",AD22="Price Review"),AG22&lt;&gt;"Approved",AG22&lt;&gt;"Rejected"),IF(AC22="",0,AC22)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO22" s="25" t="n"/>
+      <c r="AP22" s="25" t="n"/>
+      <c r="AQ22" s="26" t="n"/>
+      <c r="AR22" s="26" t="n"/>
+      <c r="AS22" s="20" t="n"/>
+      <c r="AT22" s="26" t="n"/>
+      <c r="AU22" s="26" t="n"/>
+      <c r="AV22" s="26" t="n"/>
+      <c r="AW22" s="22">
+        <f>IF(OR(O22="",AV22=""),"",O22*AV22)</f>
+        <v/>
+      </c>
+      <c r="AX22" s="20" t="n"/>
+      <c r="AY22" s="20" t="n"/>
+      <c r="AZ22" s="20" t="n"/>
+      <c r="BA22" s="20" t="n"/>
+      <c r="BB22" s="20" t="n"/>
+      <c r="BC22" s="22" t="n"/>
+      <c r="BD22" s="20" t="n"/>
+      <c r="BE22" s="20">
+        <f>IF(C22="","",IF(AND(ISNUMBER(P22),P22&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB22),AB22&lt;=2),"Quality risk",IF(AND(ISNUMBER(U22),U22&lt;=2),"Aesthetic mismatch",IF(AY22="High","Too fragile",IF(AND(ISNUMBER(R22),R22&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT22),AT22&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD22="Maybe",AD22="Price Review"),"Needs partner review",IF(AD22="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF22" s="20" t="n"/>
+      <c r="BG22" s="20" t="n"/>
+      <c r="BH22" s="20" t="n"/>
+      <c r="BI22" s="20" t="n"/>
+      <c r="BJ22" s="20" t="n"/>
+      <c r="BK22" s="20" t="n"/>
+      <c r="BL22" s="20">
+        <f>IF(C22="","",IF(AND(BG22="Yes",BH22="Yes",BI22="Yes",BJ22="Yes",BK22="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="13">
         <f>IF(C23="","","AYN-"&amp;UPPER(LEFT(E23,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="11">
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="15">
         <f>IF(I23="","",IF(J23="BDT",I23,IF(J23="USD",I23*USD_BDT,IF(J23="RMB",I23*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11">
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15">
         <f>IF(K23="","",K23+IFERROR(L23,0)+(K23*IF(M23="",CUSTOMS_PCT,M23))+IF(N23="",MISC_FEE,N23))</f>
         <v/>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="15">
         <f>IF(O23="","",ROUND(O23*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q23" s="11">
+      <c r="Q23" s="15">
         <f>IF(P23="","",P23-O23)</f>
         <v/>
       </c>
-      <c r="R23" s="12">
+      <c r="R23" s="16">
         <f>IF(OR(P23="",P23=0),"",Q23/P23)</f>
         <v/>
       </c>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="9" t="n"/>
-      <c r="U23" s="9" t="n"/>
-      <c r="V23" s="9" t="n"/>
-      <c r="W23" s="9" t="n"/>
-      <c r="X23" s="9" t="n"/>
-      <c r="Y23" s="9" t="n"/>
-      <c r="Z23" s="9" t="n"/>
-      <c r="AA23" s="9" t="n"/>
-      <c r="AB23" s="9" t="n"/>
-      <c r="AC23" s="13">
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="13" t="n"/>
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="13" t="n"/>
+      <c r="Y23" s="13" t="n"/>
+      <c r="Z23" s="13" t="n"/>
+      <c r="AA23" s="13" t="n"/>
+      <c r="AB23" s="13" t="n"/>
+      <c r="AC23" s="17">
         <f>IF(COUNT(S23:AB23)&lt;10,"",(S23*W_FEMININE+T23*W_TREND+U23*W_AESTHETIC+V23*W_STYLE+W23*W_LIGHT+X23*W_REELS+Y23*W_GIFT+Z23*W_PRICEFIT+AA23*W_DEMAND+AB23*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD23" s="9">
+      <c r="AD23" s="13">
         <f>IF(P23="","",IF(P23&gt;HARD_REJECT_PRICE,"Reject",IF(P23&gt;MAX_PRICE,"Price Review",IF(AC23="","",IF(AND(AC23&gt;=BUY_THRESHOLD,OR(AB23&lt;=2,U23&lt;=2)),"Maybe",IF(AC23&gt;=BUY_THRESHOLD,"Buy",IF(AC23&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE23" s="9" t="n"/>
-      <c r="AF23" s="9" t="n"/>
-      <c r="AG23" s="9" t="n"/>
-      <c r="AH23" s="9" t="n"/>
-      <c r="AI23" s="10" t="n"/>
+      <c r="AE23" s="13" t="n"/>
+      <c r="AF23" s="13" t="n"/>
+      <c r="AG23" s="13" t="n"/>
+      <c r="AH23" s="13" t="n"/>
+      <c r="AI23" s="14" t="n"/>
       <c r="AJ23">
         <f>IF(AC23="",-9999-ROW()*0.0000001,AC23-ROW()*0.0000001)</f>
         <v/>
@@ -3011,67 +4125,100 @@
         <f>IF(AND(OR(AD23="Maybe",AD23="Price Review"),AG23&lt;&gt;"Approved",AG23&lt;&gt;"Rejected"),IF(AC23="",0,AC23)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO23" s="18" t="n"/>
+      <c r="AP23" s="18" t="n"/>
+      <c r="AQ23" s="19" t="n"/>
+      <c r="AR23" s="19" t="n"/>
+      <c r="AS23" s="13" t="n"/>
+      <c r="AT23" s="19" t="n"/>
+      <c r="AU23" s="19" t="n"/>
+      <c r="AV23" s="19" t="n"/>
+      <c r="AW23" s="15">
+        <f>IF(OR(O23="",AV23=""),"",O23*AV23)</f>
+        <v/>
+      </c>
+      <c r="AX23" s="13" t="n"/>
+      <c r="AY23" s="13" t="n"/>
+      <c r="AZ23" s="13" t="n"/>
+      <c r="BA23" s="13" t="n"/>
+      <c r="BB23" s="13" t="n"/>
+      <c r="BC23" s="15" t="n"/>
+      <c r="BD23" s="13" t="n"/>
+      <c r="BE23" s="13">
+        <f>IF(C23="","",IF(AND(ISNUMBER(P23),P23&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB23),AB23&lt;=2),"Quality risk",IF(AND(ISNUMBER(U23),U23&lt;=2),"Aesthetic mismatch",IF(AY23="High","Too fragile",IF(AND(ISNUMBER(R23),R23&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT23),AT23&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD23="Maybe",AD23="Price Review"),"Needs partner review",IF(AD23="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF23" s="13" t="n"/>
+      <c r="BG23" s="13" t="n"/>
+      <c r="BH23" s="13" t="n"/>
+      <c r="BI23" s="13" t="n"/>
+      <c r="BJ23" s="13" t="n"/>
+      <c r="BK23" s="13" t="n"/>
+      <c r="BL23" s="13">
+        <f>IF(C23="","",IF(AND(BG23="Yes",BH23="Yes",BI23="Yes",BJ23="Yes",BK23="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="14">
+      <c r="A24" s="20">
         <f>IF(C24="","","AYN-"&amp;UPPER(LEFT(E24,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="16">
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="22">
         <f>IF(I24="","",IF(J24="BDT",I24,IF(J24="USD",I24*USD_BDT,IF(J24="RMB",I24*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="17" t="n"/>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="16">
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22">
         <f>IF(K24="","",K24+IFERROR(L24,0)+(K24*IF(M24="",CUSTOMS_PCT,M24))+IF(N24="",MISC_FEE,N24))</f>
         <v/>
       </c>
-      <c r="P24" s="16">
+      <c r="P24" s="22">
         <f>IF(O24="","",ROUND(O24*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q24" s="16">
+      <c r="Q24" s="22">
         <f>IF(P24="","",P24-O24)</f>
         <v/>
       </c>
-      <c r="R24" s="17">
+      <c r="R24" s="23">
         <f>IF(OR(P24="",P24=0),"",Q24/P24)</f>
         <v/>
       </c>
-      <c r="S24" s="14" t="n"/>
-      <c r="T24" s="14" t="n"/>
-      <c r="U24" s="14" t="n"/>
-      <c r="V24" s="14" t="n"/>
-      <c r="W24" s="14" t="n"/>
-      <c r="X24" s="14" t="n"/>
-      <c r="Y24" s="14" t="n"/>
-      <c r="Z24" s="14" t="n"/>
-      <c r="AA24" s="14" t="n"/>
-      <c r="AB24" s="14" t="n"/>
-      <c r="AC24" s="18">
+      <c r="S24" s="20" t="n"/>
+      <c r="T24" s="20" t="n"/>
+      <c r="U24" s="20" t="n"/>
+      <c r="V24" s="20" t="n"/>
+      <c r="W24" s="20" t="n"/>
+      <c r="X24" s="20" t="n"/>
+      <c r="Y24" s="20" t="n"/>
+      <c r="Z24" s="20" t="n"/>
+      <c r="AA24" s="20" t="n"/>
+      <c r="AB24" s="20" t="n"/>
+      <c r="AC24" s="24">
         <f>IF(COUNT(S24:AB24)&lt;10,"",(S24*W_FEMININE+T24*W_TREND+U24*W_AESTHETIC+V24*W_STYLE+W24*W_LIGHT+X24*W_REELS+Y24*W_GIFT+Z24*W_PRICEFIT+AA24*W_DEMAND+AB24*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD24" s="14">
+      <c r="AD24" s="20">
         <f>IF(P24="","",IF(P24&gt;HARD_REJECT_PRICE,"Reject",IF(P24&gt;MAX_PRICE,"Price Review",IF(AC24="","",IF(AND(AC24&gt;=BUY_THRESHOLD,OR(AB24&lt;=2,U24&lt;=2)),"Maybe",IF(AC24&gt;=BUY_THRESHOLD,"Buy",IF(AC24&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE24" s="14" t="n"/>
-      <c r="AF24" s="14" t="n"/>
-      <c r="AG24" s="14" t="n"/>
-      <c r="AH24" s="14" t="n"/>
-      <c r="AI24" s="15" t="n"/>
+      <c r="AE24" s="20" t="n"/>
+      <c r="AF24" s="20" t="n"/>
+      <c r="AG24" s="20" t="n"/>
+      <c r="AH24" s="20" t="n"/>
+      <c r="AI24" s="21" t="n"/>
       <c r="AJ24">
         <f>IF(AC24="",-9999-ROW()*0.0000001,AC24-ROW()*0.0000001)</f>
         <v/>
@@ -3092,67 +4239,100 @@
         <f>IF(AND(OR(AD24="Maybe",AD24="Price Review"),AG24&lt;&gt;"Approved",AG24&lt;&gt;"Rejected"),IF(AC24="",0,AC24)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO24" s="25" t="n"/>
+      <c r="AP24" s="25" t="n"/>
+      <c r="AQ24" s="26" t="n"/>
+      <c r="AR24" s="26" t="n"/>
+      <c r="AS24" s="20" t="n"/>
+      <c r="AT24" s="26" t="n"/>
+      <c r="AU24" s="26" t="n"/>
+      <c r="AV24" s="26" t="n"/>
+      <c r="AW24" s="22">
+        <f>IF(OR(O24="",AV24=""),"",O24*AV24)</f>
+        <v/>
+      </c>
+      <c r="AX24" s="20" t="n"/>
+      <c r="AY24" s="20" t="n"/>
+      <c r="AZ24" s="20" t="n"/>
+      <c r="BA24" s="20" t="n"/>
+      <c r="BB24" s="20" t="n"/>
+      <c r="BC24" s="22" t="n"/>
+      <c r="BD24" s="20" t="n"/>
+      <c r="BE24" s="20">
+        <f>IF(C24="","",IF(AND(ISNUMBER(P24),P24&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB24),AB24&lt;=2),"Quality risk",IF(AND(ISNUMBER(U24),U24&lt;=2),"Aesthetic mismatch",IF(AY24="High","Too fragile",IF(AND(ISNUMBER(R24),R24&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT24),AT24&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD24="Maybe",AD24="Price Review"),"Needs partner review",IF(AD24="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF24" s="20" t="n"/>
+      <c r="BG24" s="20" t="n"/>
+      <c r="BH24" s="20" t="n"/>
+      <c r="BI24" s="20" t="n"/>
+      <c r="BJ24" s="20" t="n"/>
+      <c r="BK24" s="20" t="n"/>
+      <c r="BL24" s="20">
+        <f>IF(C24="","",IF(AND(BG24="Yes",BH24="Yes",BI24="Yes",BJ24="Yes",BK24="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="13">
         <f>IF(C25="","","AYN-"&amp;UPPER(LEFT(E25,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="11">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="15">
         <f>IF(I25="","",IF(J25="BDT",I25,IF(J25="USD",I25*USD_BDT,IF(J25="RMB",I25*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="11">
+      <c r="L25" s="15" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="15" t="n"/>
+      <c r="O25" s="15">
         <f>IF(K25="","",K25+IFERROR(L25,0)+(K25*IF(M25="",CUSTOMS_PCT,M25))+IF(N25="",MISC_FEE,N25))</f>
         <v/>
       </c>
-      <c r="P25" s="11">
+      <c r="P25" s="15">
         <f>IF(O25="","",ROUND(O25*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q25" s="11">
+      <c r="Q25" s="15">
         <f>IF(P25="","",P25-O25)</f>
         <v/>
       </c>
-      <c r="R25" s="12">
+      <c r="R25" s="16">
         <f>IF(OR(P25="",P25=0),"",Q25/P25)</f>
         <v/>
       </c>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="9" t="n"/>
-      <c r="U25" s="9" t="n"/>
-      <c r="V25" s="9" t="n"/>
-      <c r="W25" s="9" t="n"/>
-      <c r="X25" s="9" t="n"/>
-      <c r="Y25" s="9" t="n"/>
-      <c r="Z25" s="9" t="n"/>
-      <c r="AA25" s="9" t="n"/>
-      <c r="AB25" s="9" t="n"/>
-      <c r="AC25" s="13">
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="13" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="13" t="n"/>
+      <c r="Y25" s="13" t="n"/>
+      <c r="Z25" s="13" t="n"/>
+      <c r="AA25" s="13" t="n"/>
+      <c r="AB25" s="13" t="n"/>
+      <c r="AC25" s="17">
         <f>IF(COUNT(S25:AB25)&lt;10,"",(S25*W_FEMININE+T25*W_TREND+U25*W_AESTHETIC+V25*W_STYLE+W25*W_LIGHT+X25*W_REELS+Y25*W_GIFT+Z25*W_PRICEFIT+AA25*W_DEMAND+AB25*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD25" s="9">
+      <c r="AD25" s="13">
         <f>IF(P25="","",IF(P25&gt;HARD_REJECT_PRICE,"Reject",IF(P25&gt;MAX_PRICE,"Price Review",IF(AC25="","",IF(AND(AC25&gt;=BUY_THRESHOLD,OR(AB25&lt;=2,U25&lt;=2)),"Maybe",IF(AC25&gt;=BUY_THRESHOLD,"Buy",IF(AC25&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE25" s="9" t="n"/>
-      <c r="AF25" s="9" t="n"/>
-      <c r="AG25" s="9" t="n"/>
-      <c r="AH25" s="9" t="n"/>
-      <c r="AI25" s="10" t="n"/>
+      <c r="AE25" s="13" t="n"/>
+      <c r="AF25" s="13" t="n"/>
+      <c r="AG25" s="13" t="n"/>
+      <c r="AH25" s="13" t="n"/>
+      <c r="AI25" s="14" t="n"/>
       <c r="AJ25">
         <f>IF(AC25="",-9999-ROW()*0.0000001,AC25-ROW()*0.0000001)</f>
         <v/>
@@ -3173,67 +4353,100 @@
         <f>IF(AND(OR(AD25="Maybe",AD25="Price Review"),AG25&lt;&gt;"Approved",AG25&lt;&gt;"Rejected"),IF(AC25="",0,AC25)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO25" s="18" t="n"/>
+      <c r="AP25" s="18" t="n"/>
+      <c r="AQ25" s="19" t="n"/>
+      <c r="AR25" s="19" t="n"/>
+      <c r="AS25" s="13" t="n"/>
+      <c r="AT25" s="19" t="n"/>
+      <c r="AU25" s="19" t="n"/>
+      <c r="AV25" s="19" t="n"/>
+      <c r="AW25" s="15">
+        <f>IF(OR(O25="",AV25=""),"",O25*AV25)</f>
+        <v/>
+      </c>
+      <c r="AX25" s="13" t="n"/>
+      <c r="AY25" s="13" t="n"/>
+      <c r="AZ25" s="13" t="n"/>
+      <c r="BA25" s="13" t="n"/>
+      <c r="BB25" s="13" t="n"/>
+      <c r="BC25" s="15" t="n"/>
+      <c r="BD25" s="13" t="n"/>
+      <c r="BE25" s="13">
+        <f>IF(C25="","",IF(AND(ISNUMBER(P25),P25&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB25),AB25&lt;=2),"Quality risk",IF(AND(ISNUMBER(U25),U25&lt;=2),"Aesthetic mismatch",IF(AY25="High","Too fragile",IF(AND(ISNUMBER(R25),R25&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT25),AT25&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD25="Maybe",AD25="Price Review"),"Needs partner review",IF(AD25="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF25" s="13" t="n"/>
+      <c r="BG25" s="13" t="n"/>
+      <c r="BH25" s="13" t="n"/>
+      <c r="BI25" s="13" t="n"/>
+      <c r="BJ25" s="13" t="n"/>
+      <c r="BK25" s="13" t="n"/>
+      <c r="BL25" s="13">
+        <f>IF(C25="","",IF(AND(BG25="Yes",BH25="Yes",BI25="Yes",BJ25="Yes",BK25="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="14">
+      <c r="A26" s="20">
         <f>IF(C26="","","AYN-"&amp;UPPER(LEFT(E26,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="16">
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="20" t="n"/>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="20" t="n"/>
+      <c r="J26" s="20" t="n"/>
+      <c r="K26" s="22">
         <f>IF(I26="","",IF(J26="BDT",I26,IF(J26="USD",I26*USD_BDT,IF(J26="RMB",I26*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L26" s="16" t="n"/>
-      <c r="M26" s="17" t="n"/>
-      <c r="N26" s="16" t="n"/>
-      <c r="O26" s="16">
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="23" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22">
         <f>IF(K26="","",K26+IFERROR(L26,0)+(K26*IF(M26="",CUSTOMS_PCT,M26))+IF(N26="",MISC_FEE,N26))</f>
         <v/>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="22">
         <f>IF(O26="","",ROUND(O26*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="22">
         <f>IF(P26="","",P26-O26)</f>
         <v/>
       </c>
-      <c r="R26" s="17">
+      <c r="R26" s="23">
         <f>IF(OR(P26="",P26=0),"",Q26/P26)</f>
         <v/>
       </c>
-      <c r="S26" s="14" t="n"/>
-      <c r="T26" s="14" t="n"/>
-      <c r="U26" s="14" t="n"/>
-      <c r="V26" s="14" t="n"/>
-      <c r="W26" s="14" t="n"/>
-      <c r="X26" s="14" t="n"/>
-      <c r="Y26" s="14" t="n"/>
-      <c r="Z26" s="14" t="n"/>
-      <c r="AA26" s="14" t="n"/>
-      <c r="AB26" s="14" t="n"/>
-      <c r="AC26" s="18">
+      <c r="S26" s="20" t="n"/>
+      <c r="T26" s="20" t="n"/>
+      <c r="U26" s="20" t="n"/>
+      <c r="V26" s="20" t="n"/>
+      <c r="W26" s="20" t="n"/>
+      <c r="X26" s="20" t="n"/>
+      <c r="Y26" s="20" t="n"/>
+      <c r="Z26" s="20" t="n"/>
+      <c r="AA26" s="20" t="n"/>
+      <c r="AB26" s="20" t="n"/>
+      <c r="AC26" s="24">
         <f>IF(COUNT(S26:AB26)&lt;10,"",(S26*W_FEMININE+T26*W_TREND+U26*W_AESTHETIC+V26*W_STYLE+W26*W_LIGHT+X26*W_REELS+Y26*W_GIFT+Z26*W_PRICEFIT+AA26*W_DEMAND+AB26*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD26" s="14">
+      <c r="AD26" s="20">
         <f>IF(P26="","",IF(P26&gt;HARD_REJECT_PRICE,"Reject",IF(P26&gt;MAX_PRICE,"Price Review",IF(AC26="","",IF(AND(AC26&gt;=BUY_THRESHOLD,OR(AB26&lt;=2,U26&lt;=2)),"Maybe",IF(AC26&gt;=BUY_THRESHOLD,"Buy",IF(AC26&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE26" s="14" t="n"/>
-      <c r="AF26" s="14" t="n"/>
-      <c r="AG26" s="14" t="n"/>
-      <c r="AH26" s="14" t="n"/>
-      <c r="AI26" s="15" t="n"/>
+      <c r="AE26" s="20" t="n"/>
+      <c r="AF26" s="20" t="n"/>
+      <c r="AG26" s="20" t="n"/>
+      <c r="AH26" s="20" t="n"/>
+      <c r="AI26" s="21" t="n"/>
       <c r="AJ26">
         <f>IF(AC26="",-9999-ROW()*0.0000001,AC26-ROW()*0.0000001)</f>
         <v/>
@@ -3254,67 +4467,100 @@
         <f>IF(AND(OR(AD26="Maybe",AD26="Price Review"),AG26&lt;&gt;"Approved",AG26&lt;&gt;"Rejected"),IF(AC26="",0,AC26)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO26" s="25" t="n"/>
+      <c r="AP26" s="25" t="n"/>
+      <c r="AQ26" s="26" t="n"/>
+      <c r="AR26" s="26" t="n"/>
+      <c r="AS26" s="20" t="n"/>
+      <c r="AT26" s="26" t="n"/>
+      <c r="AU26" s="26" t="n"/>
+      <c r="AV26" s="26" t="n"/>
+      <c r="AW26" s="22">
+        <f>IF(OR(O26="",AV26=""),"",O26*AV26)</f>
+        <v/>
+      </c>
+      <c r="AX26" s="20" t="n"/>
+      <c r="AY26" s="20" t="n"/>
+      <c r="AZ26" s="20" t="n"/>
+      <c r="BA26" s="20" t="n"/>
+      <c r="BB26" s="20" t="n"/>
+      <c r="BC26" s="22" t="n"/>
+      <c r="BD26" s="20" t="n"/>
+      <c r="BE26" s="20">
+        <f>IF(C26="","",IF(AND(ISNUMBER(P26),P26&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB26),AB26&lt;=2),"Quality risk",IF(AND(ISNUMBER(U26),U26&lt;=2),"Aesthetic mismatch",IF(AY26="High","Too fragile",IF(AND(ISNUMBER(R26),R26&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT26),AT26&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD26="Maybe",AD26="Price Review"),"Needs partner review",IF(AD26="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF26" s="20" t="n"/>
+      <c r="BG26" s="20" t="n"/>
+      <c r="BH26" s="20" t="n"/>
+      <c r="BI26" s="20" t="n"/>
+      <c r="BJ26" s="20" t="n"/>
+      <c r="BK26" s="20" t="n"/>
+      <c r="BL26" s="20">
+        <f>IF(C26="","",IF(AND(BG26="Yes",BH26="Yes",BI26="Yes",BJ26="Yes",BK26="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="13">
         <f>IF(C27="","","AYN-"&amp;UPPER(LEFT(E27,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="11">
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="15">
         <f>IF(I27="","",IF(J27="BDT",I27,IF(J27="USD",I27*USD_BDT,IF(J27="RMB",I27*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11">
+      <c r="L27" s="15" t="n"/>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="15" t="n"/>
+      <c r="O27" s="15">
         <f>IF(K27="","",K27+IFERROR(L27,0)+(K27*IF(M27="",CUSTOMS_PCT,M27))+IF(N27="",MISC_FEE,N27))</f>
         <v/>
       </c>
-      <c r="P27" s="11">
+      <c r="P27" s="15">
         <f>IF(O27="","",ROUND(O27*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q27" s="11">
+      <c r="Q27" s="15">
         <f>IF(P27="","",P27-O27)</f>
         <v/>
       </c>
-      <c r="R27" s="12">
+      <c r="R27" s="16">
         <f>IF(OR(P27="",P27=0),"",Q27/P27)</f>
         <v/>
       </c>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="9" t="n"/>
-      <c r="U27" s="9" t="n"/>
-      <c r="V27" s="9" t="n"/>
-      <c r="W27" s="9" t="n"/>
-      <c r="X27" s="9" t="n"/>
-      <c r="Y27" s="9" t="n"/>
-      <c r="Z27" s="9" t="n"/>
-      <c r="AA27" s="9" t="n"/>
-      <c r="AB27" s="9" t="n"/>
-      <c r="AC27" s="13">
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="13" t="n"/>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="13" t="n"/>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="13" t="n"/>
+      <c r="Y27" s="13" t="n"/>
+      <c r="Z27" s="13" t="n"/>
+      <c r="AA27" s="13" t="n"/>
+      <c r="AB27" s="13" t="n"/>
+      <c r="AC27" s="17">
         <f>IF(COUNT(S27:AB27)&lt;10,"",(S27*W_FEMININE+T27*W_TREND+U27*W_AESTHETIC+V27*W_STYLE+W27*W_LIGHT+X27*W_REELS+Y27*W_GIFT+Z27*W_PRICEFIT+AA27*W_DEMAND+AB27*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD27" s="9">
+      <c r="AD27" s="13">
         <f>IF(P27="","",IF(P27&gt;HARD_REJECT_PRICE,"Reject",IF(P27&gt;MAX_PRICE,"Price Review",IF(AC27="","",IF(AND(AC27&gt;=BUY_THRESHOLD,OR(AB27&lt;=2,U27&lt;=2)),"Maybe",IF(AC27&gt;=BUY_THRESHOLD,"Buy",IF(AC27&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE27" s="9" t="n"/>
-      <c r="AF27" s="9" t="n"/>
-      <c r="AG27" s="9" t="n"/>
-      <c r="AH27" s="9" t="n"/>
-      <c r="AI27" s="10" t="n"/>
+      <c r="AE27" s="13" t="n"/>
+      <c r="AF27" s="13" t="n"/>
+      <c r="AG27" s="13" t="n"/>
+      <c r="AH27" s="13" t="n"/>
+      <c r="AI27" s="14" t="n"/>
       <c r="AJ27">
         <f>IF(AC27="",-9999-ROW()*0.0000001,AC27-ROW()*0.0000001)</f>
         <v/>
@@ -3335,67 +4581,100 @@
         <f>IF(AND(OR(AD27="Maybe",AD27="Price Review"),AG27&lt;&gt;"Approved",AG27&lt;&gt;"Rejected"),IF(AC27="",0,AC27)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO27" s="18" t="n"/>
+      <c r="AP27" s="18" t="n"/>
+      <c r="AQ27" s="19" t="n"/>
+      <c r="AR27" s="19" t="n"/>
+      <c r="AS27" s="13" t="n"/>
+      <c r="AT27" s="19" t="n"/>
+      <c r="AU27" s="19" t="n"/>
+      <c r="AV27" s="19" t="n"/>
+      <c r="AW27" s="15">
+        <f>IF(OR(O27="",AV27=""),"",O27*AV27)</f>
+        <v/>
+      </c>
+      <c r="AX27" s="13" t="n"/>
+      <c r="AY27" s="13" t="n"/>
+      <c r="AZ27" s="13" t="n"/>
+      <c r="BA27" s="13" t="n"/>
+      <c r="BB27" s="13" t="n"/>
+      <c r="BC27" s="15" t="n"/>
+      <c r="BD27" s="13" t="n"/>
+      <c r="BE27" s="13">
+        <f>IF(C27="","",IF(AND(ISNUMBER(P27),P27&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB27),AB27&lt;=2),"Quality risk",IF(AND(ISNUMBER(U27),U27&lt;=2),"Aesthetic mismatch",IF(AY27="High","Too fragile",IF(AND(ISNUMBER(R27),R27&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT27),AT27&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD27="Maybe",AD27="Price Review"),"Needs partner review",IF(AD27="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF27" s="13" t="n"/>
+      <c r="BG27" s="13" t="n"/>
+      <c r="BH27" s="13" t="n"/>
+      <c r="BI27" s="13" t="n"/>
+      <c r="BJ27" s="13" t="n"/>
+      <c r="BK27" s="13" t="n"/>
+      <c r="BL27" s="13">
+        <f>IF(C27="","",IF(AND(BG27="Yes",BH27="Yes",BI27="Yes",BJ27="Yes",BK27="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="14">
+      <c r="A28" s="20">
         <f>IF(C28="","","AYN-"&amp;UPPER(LEFT(E28,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="16">
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="22">
         <f>IF(I28="","",IF(J28="BDT",I28,IF(J28="USD",I28*USD_BDT,IF(J28="RMB",I28*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L28" s="16" t="n"/>
-      <c r="M28" s="17" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16">
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22">
         <f>IF(K28="","",K28+IFERROR(L28,0)+(K28*IF(M28="",CUSTOMS_PCT,M28))+IF(N28="",MISC_FEE,N28))</f>
         <v/>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="22">
         <f>IF(O28="","",ROUND(O28*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="22">
         <f>IF(P28="","",P28-O28)</f>
         <v/>
       </c>
-      <c r="R28" s="17">
+      <c r="R28" s="23">
         <f>IF(OR(P28="",P28=0),"",Q28/P28)</f>
         <v/>
       </c>
-      <c r="S28" s="14" t="n"/>
-      <c r="T28" s="14" t="n"/>
-      <c r="U28" s="14" t="n"/>
-      <c r="V28" s="14" t="n"/>
-      <c r="W28" s="14" t="n"/>
-      <c r="X28" s="14" t="n"/>
-      <c r="Y28" s="14" t="n"/>
-      <c r="Z28" s="14" t="n"/>
-      <c r="AA28" s="14" t="n"/>
-      <c r="AB28" s="14" t="n"/>
-      <c r="AC28" s="18">
+      <c r="S28" s="20" t="n"/>
+      <c r="T28" s="20" t="n"/>
+      <c r="U28" s="20" t="n"/>
+      <c r="V28" s="20" t="n"/>
+      <c r="W28" s="20" t="n"/>
+      <c r="X28" s="20" t="n"/>
+      <c r="Y28" s="20" t="n"/>
+      <c r="Z28" s="20" t="n"/>
+      <c r="AA28" s="20" t="n"/>
+      <c r="AB28" s="20" t="n"/>
+      <c r="AC28" s="24">
         <f>IF(COUNT(S28:AB28)&lt;10,"",(S28*W_FEMININE+T28*W_TREND+U28*W_AESTHETIC+V28*W_STYLE+W28*W_LIGHT+X28*W_REELS+Y28*W_GIFT+Z28*W_PRICEFIT+AA28*W_DEMAND+AB28*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD28" s="14">
+      <c r="AD28" s="20">
         <f>IF(P28="","",IF(P28&gt;HARD_REJECT_PRICE,"Reject",IF(P28&gt;MAX_PRICE,"Price Review",IF(AC28="","",IF(AND(AC28&gt;=BUY_THRESHOLD,OR(AB28&lt;=2,U28&lt;=2)),"Maybe",IF(AC28&gt;=BUY_THRESHOLD,"Buy",IF(AC28&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE28" s="14" t="n"/>
-      <c r="AF28" s="14" t="n"/>
-      <c r="AG28" s="14" t="n"/>
-      <c r="AH28" s="14" t="n"/>
-      <c r="AI28" s="15" t="n"/>
+      <c r="AE28" s="20" t="n"/>
+      <c r="AF28" s="20" t="n"/>
+      <c r="AG28" s="20" t="n"/>
+      <c r="AH28" s="20" t="n"/>
+      <c r="AI28" s="21" t="n"/>
       <c r="AJ28">
         <f>IF(AC28="",-9999-ROW()*0.0000001,AC28-ROW()*0.0000001)</f>
         <v/>
@@ -3416,67 +4695,100 @@
         <f>IF(AND(OR(AD28="Maybe",AD28="Price Review"),AG28&lt;&gt;"Approved",AG28&lt;&gt;"Rejected"),IF(AC28="",0,AC28)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO28" s="25" t="n"/>
+      <c r="AP28" s="25" t="n"/>
+      <c r="AQ28" s="26" t="n"/>
+      <c r="AR28" s="26" t="n"/>
+      <c r="AS28" s="20" t="n"/>
+      <c r="AT28" s="26" t="n"/>
+      <c r="AU28" s="26" t="n"/>
+      <c r="AV28" s="26" t="n"/>
+      <c r="AW28" s="22">
+        <f>IF(OR(O28="",AV28=""),"",O28*AV28)</f>
+        <v/>
+      </c>
+      <c r="AX28" s="20" t="n"/>
+      <c r="AY28" s="20" t="n"/>
+      <c r="AZ28" s="20" t="n"/>
+      <c r="BA28" s="20" t="n"/>
+      <c r="BB28" s="20" t="n"/>
+      <c r="BC28" s="22" t="n"/>
+      <c r="BD28" s="20" t="n"/>
+      <c r="BE28" s="20">
+        <f>IF(C28="","",IF(AND(ISNUMBER(P28),P28&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB28),AB28&lt;=2),"Quality risk",IF(AND(ISNUMBER(U28),U28&lt;=2),"Aesthetic mismatch",IF(AY28="High","Too fragile",IF(AND(ISNUMBER(R28),R28&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT28),AT28&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD28="Maybe",AD28="Price Review"),"Needs partner review",IF(AD28="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF28" s="20" t="n"/>
+      <c r="BG28" s="20" t="n"/>
+      <c r="BH28" s="20" t="n"/>
+      <c r="BI28" s="20" t="n"/>
+      <c r="BJ28" s="20" t="n"/>
+      <c r="BK28" s="20" t="n"/>
+      <c r="BL28" s="20">
+        <f>IF(C28="","",IF(AND(BG28="Yes",BH28="Yes",BI28="Yes",BJ28="Yes",BK28="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="13">
         <f>IF(C29="","","AYN-"&amp;UPPER(LEFT(E29,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="11">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="n"/>
+      <c r="K29" s="15">
         <f>IF(I29="","",IF(J29="BDT",I29,IF(J29="USD",I29*USD_BDT,IF(J29="RMB",I29*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11">
+      <c r="L29" s="15" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="15" t="n"/>
+      <c r="O29" s="15">
         <f>IF(K29="","",K29+IFERROR(L29,0)+(K29*IF(M29="",CUSTOMS_PCT,M29))+IF(N29="",MISC_FEE,N29))</f>
         <v/>
       </c>
-      <c r="P29" s="11">
+      <c r="P29" s="15">
         <f>IF(O29="","",ROUND(O29*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="15">
         <f>IF(P29="","",P29-O29)</f>
         <v/>
       </c>
-      <c r="R29" s="12">
+      <c r="R29" s="16">
         <f>IF(OR(P29="",P29=0),"",Q29/P29)</f>
         <v/>
       </c>
-      <c r="S29" s="9" t="n"/>
-      <c r="T29" s="9" t="n"/>
-      <c r="U29" s="9" t="n"/>
-      <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
-      <c r="X29" s="9" t="n"/>
-      <c r="Y29" s="9" t="n"/>
-      <c r="Z29" s="9" t="n"/>
-      <c r="AA29" s="9" t="n"/>
-      <c r="AB29" s="9" t="n"/>
-      <c r="AC29" s="13">
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="13" t="n"/>
+      <c r="U29" s="13" t="n"/>
+      <c r="V29" s="13" t="n"/>
+      <c r="W29" s="13" t="n"/>
+      <c r="X29" s="13" t="n"/>
+      <c r="Y29" s="13" t="n"/>
+      <c r="Z29" s="13" t="n"/>
+      <c r="AA29" s="13" t="n"/>
+      <c r="AB29" s="13" t="n"/>
+      <c r="AC29" s="17">
         <f>IF(COUNT(S29:AB29)&lt;10,"",(S29*W_FEMININE+T29*W_TREND+U29*W_AESTHETIC+V29*W_STYLE+W29*W_LIGHT+X29*W_REELS+Y29*W_GIFT+Z29*W_PRICEFIT+AA29*W_DEMAND+AB29*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD29" s="9">
+      <c r="AD29" s="13">
         <f>IF(P29="","",IF(P29&gt;HARD_REJECT_PRICE,"Reject",IF(P29&gt;MAX_PRICE,"Price Review",IF(AC29="","",IF(AND(AC29&gt;=BUY_THRESHOLD,OR(AB29&lt;=2,U29&lt;=2)),"Maybe",IF(AC29&gt;=BUY_THRESHOLD,"Buy",IF(AC29&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE29" s="9" t="n"/>
-      <c r="AF29" s="9" t="n"/>
-      <c r="AG29" s="9" t="n"/>
-      <c r="AH29" s="9" t="n"/>
-      <c r="AI29" s="10" t="n"/>
+      <c r="AE29" s="13" t="n"/>
+      <c r="AF29" s="13" t="n"/>
+      <c r="AG29" s="13" t="n"/>
+      <c r="AH29" s="13" t="n"/>
+      <c r="AI29" s="14" t="n"/>
       <c r="AJ29">
         <f>IF(AC29="",-9999-ROW()*0.0000001,AC29-ROW()*0.0000001)</f>
         <v/>
@@ -3497,67 +4809,100 @@
         <f>IF(AND(OR(AD29="Maybe",AD29="Price Review"),AG29&lt;&gt;"Approved",AG29&lt;&gt;"Rejected"),IF(AC29="",0,AC29)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO29" s="18" t="n"/>
+      <c r="AP29" s="18" t="n"/>
+      <c r="AQ29" s="19" t="n"/>
+      <c r="AR29" s="19" t="n"/>
+      <c r="AS29" s="13" t="n"/>
+      <c r="AT29" s="19" t="n"/>
+      <c r="AU29" s="19" t="n"/>
+      <c r="AV29" s="19" t="n"/>
+      <c r="AW29" s="15">
+        <f>IF(OR(O29="",AV29=""),"",O29*AV29)</f>
+        <v/>
+      </c>
+      <c r="AX29" s="13" t="n"/>
+      <c r="AY29" s="13" t="n"/>
+      <c r="AZ29" s="13" t="n"/>
+      <c r="BA29" s="13" t="n"/>
+      <c r="BB29" s="13" t="n"/>
+      <c r="BC29" s="15" t="n"/>
+      <c r="BD29" s="13" t="n"/>
+      <c r="BE29" s="13">
+        <f>IF(C29="","",IF(AND(ISNUMBER(P29),P29&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB29),AB29&lt;=2),"Quality risk",IF(AND(ISNUMBER(U29),U29&lt;=2),"Aesthetic mismatch",IF(AY29="High","Too fragile",IF(AND(ISNUMBER(R29),R29&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT29),AT29&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD29="Maybe",AD29="Price Review"),"Needs partner review",IF(AD29="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF29" s="13" t="n"/>
+      <c r="BG29" s="13" t="n"/>
+      <c r="BH29" s="13" t="n"/>
+      <c r="BI29" s="13" t="n"/>
+      <c r="BJ29" s="13" t="n"/>
+      <c r="BK29" s="13" t="n"/>
+      <c r="BL29" s="13">
+        <f>IF(C29="","",IF(AND(BG29="Yes",BH29="Yes",BI29="Yes",BJ29="Yes",BK29="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="14">
+      <c r="A30" s="20">
         <f>IF(C30="","","AYN-"&amp;UPPER(LEFT(E30,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="16">
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="20" t="n"/>
+      <c r="K30" s="22">
         <f>IF(I30="","",IF(J30="BDT",I30,IF(J30="USD",I30*USD_BDT,IF(J30="RMB",I30*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L30" s="16" t="n"/>
-      <c r="M30" s="17" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16">
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22">
         <f>IF(K30="","",K30+IFERROR(L30,0)+(K30*IF(M30="",CUSTOMS_PCT,M30))+IF(N30="",MISC_FEE,N30))</f>
         <v/>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="22">
         <f>IF(O30="","",ROUND(O30*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="22">
         <f>IF(P30="","",P30-O30)</f>
         <v/>
       </c>
-      <c r="R30" s="17">
+      <c r="R30" s="23">
         <f>IF(OR(P30="",P30=0),"",Q30/P30)</f>
         <v/>
       </c>
-      <c r="S30" s="14" t="n"/>
-      <c r="T30" s="14" t="n"/>
-      <c r="U30" s="14" t="n"/>
-      <c r="V30" s="14" t="n"/>
-      <c r="W30" s="14" t="n"/>
-      <c r="X30" s="14" t="n"/>
-      <c r="Y30" s="14" t="n"/>
-      <c r="Z30" s="14" t="n"/>
-      <c r="AA30" s="14" t="n"/>
-      <c r="AB30" s="14" t="n"/>
-      <c r="AC30" s="18">
+      <c r="S30" s="20" t="n"/>
+      <c r="T30" s="20" t="n"/>
+      <c r="U30" s="20" t="n"/>
+      <c r="V30" s="20" t="n"/>
+      <c r="W30" s="20" t="n"/>
+      <c r="X30" s="20" t="n"/>
+      <c r="Y30" s="20" t="n"/>
+      <c r="Z30" s="20" t="n"/>
+      <c r="AA30" s="20" t="n"/>
+      <c r="AB30" s="20" t="n"/>
+      <c r="AC30" s="24">
         <f>IF(COUNT(S30:AB30)&lt;10,"",(S30*W_FEMININE+T30*W_TREND+U30*W_AESTHETIC+V30*W_STYLE+W30*W_LIGHT+X30*W_REELS+Y30*W_GIFT+Z30*W_PRICEFIT+AA30*W_DEMAND+AB30*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD30" s="14">
+      <c r="AD30" s="20">
         <f>IF(P30="","",IF(P30&gt;HARD_REJECT_PRICE,"Reject",IF(P30&gt;MAX_PRICE,"Price Review",IF(AC30="","",IF(AND(AC30&gt;=BUY_THRESHOLD,OR(AB30&lt;=2,U30&lt;=2)),"Maybe",IF(AC30&gt;=BUY_THRESHOLD,"Buy",IF(AC30&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE30" s="14" t="n"/>
-      <c r="AF30" s="14" t="n"/>
-      <c r="AG30" s="14" t="n"/>
-      <c r="AH30" s="14" t="n"/>
-      <c r="AI30" s="15" t="n"/>
+      <c r="AE30" s="20" t="n"/>
+      <c r="AF30" s="20" t="n"/>
+      <c r="AG30" s="20" t="n"/>
+      <c r="AH30" s="20" t="n"/>
+      <c r="AI30" s="21" t="n"/>
       <c r="AJ30">
         <f>IF(AC30="",-9999-ROW()*0.0000001,AC30-ROW()*0.0000001)</f>
         <v/>
@@ -3578,67 +4923,100 @@
         <f>IF(AND(OR(AD30="Maybe",AD30="Price Review"),AG30&lt;&gt;"Approved",AG30&lt;&gt;"Rejected"),IF(AC30="",0,AC30)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO30" s="25" t="n"/>
+      <c r="AP30" s="25" t="n"/>
+      <c r="AQ30" s="26" t="n"/>
+      <c r="AR30" s="26" t="n"/>
+      <c r="AS30" s="20" t="n"/>
+      <c r="AT30" s="26" t="n"/>
+      <c r="AU30" s="26" t="n"/>
+      <c r="AV30" s="26" t="n"/>
+      <c r="AW30" s="22">
+        <f>IF(OR(O30="",AV30=""),"",O30*AV30)</f>
+        <v/>
+      </c>
+      <c r="AX30" s="20" t="n"/>
+      <c r="AY30" s="20" t="n"/>
+      <c r="AZ30" s="20" t="n"/>
+      <c r="BA30" s="20" t="n"/>
+      <c r="BB30" s="20" t="n"/>
+      <c r="BC30" s="22" t="n"/>
+      <c r="BD30" s="20" t="n"/>
+      <c r="BE30" s="20">
+        <f>IF(C30="","",IF(AND(ISNUMBER(P30),P30&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB30),AB30&lt;=2),"Quality risk",IF(AND(ISNUMBER(U30),U30&lt;=2),"Aesthetic mismatch",IF(AY30="High","Too fragile",IF(AND(ISNUMBER(R30),R30&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT30),AT30&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD30="Maybe",AD30="Price Review"),"Needs partner review",IF(AD30="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF30" s="20" t="n"/>
+      <c r="BG30" s="20" t="n"/>
+      <c r="BH30" s="20" t="n"/>
+      <c r="BI30" s="20" t="n"/>
+      <c r="BJ30" s="20" t="n"/>
+      <c r="BK30" s="20" t="n"/>
+      <c r="BL30" s="20">
+        <f>IF(C30="","",IF(AND(BG30="Yes",BH30="Yes",BI30="Yes",BJ30="Yes",BK30="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="13">
         <f>IF(C31="","","AYN-"&amp;UPPER(LEFT(E31,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="11">
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="15">
         <f>IF(I31="","",IF(J31="BDT",I31,IF(J31="USD",I31*USD_BDT,IF(J31="RMB",I31*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11">
+      <c r="L31" s="15" t="n"/>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="15" t="n"/>
+      <c r="O31" s="15">
         <f>IF(K31="","",K31+IFERROR(L31,0)+(K31*IF(M31="",CUSTOMS_PCT,M31))+IF(N31="",MISC_FEE,N31))</f>
         <v/>
       </c>
-      <c r="P31" s="11">
+      <c r="P31" s="15">
         <f>IF(O31="","",ROUND(O31*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q31" s="11">
+      <c r="Q31" s="15">
         <f>IF(P31="","",P31-O31)</f>
         <v/>
       </c>
-      <c r="R31" s="12">
+      <c r="R31" s="16">
         <f>IF(OR(P31="",P31=0),"",Q31/P31)</f>
         <v/>
       </c>
-      <c r="S31" s="9" t="n"/>
-      <c r="T31" s="9" t="n"/>
-      <c r="U31" s="9" t="n"/>
-      <c r="V31" s="9" t="n"/>
-      <c r="W31" s="9" t="n"/>
-      <c r="X31" s="9" t="n"/>
-      <c r="Y31" s="9" t="n"/>
-      <c r="Z31" s="9" t="n"/>
-      <c r="AA31" s="9" t="n"/>
-      <c r="AB31" s="9" t="n"/>
-      <c r="AC31" s="13">
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="13" t="n"/>
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="13" t="n"/>
+      <c r="Y31" s="13" t="n"/>
+      <c r="Z31" s="13" t="n"/>
+      <c r="AA31" s="13" t="n"/>
+      <c r="AB31" s="13" t="n"/>
+      <c r="AC31" s="17">
         <f>IF(COUNT(S31:AB31)&lt;10,"",(S31*W_FEMININE+T31*W_TREND+U31*W_AESTHETIC+V31*W_STYLE+W31*W_LIGHT+X31*W_REELS+Y31*W_GIFT+Z31*W_PRICEFIT+AA31*W_DEMAND+AB31*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD31" s="9">
+      <c r="AD31" s="13">
         <f>IF(P31="","",IF(P31&gt;HARD_REJECT_PRICE,"Reject",IF(P31&gt;MAX_PRICE,"Price Review",IF(AC31="","",IF(AND(AC31&gt;=BUY_THRESHOLD,OR(AB31&lt;=2,U31&lt;=2)),"Maybe",IF(AC31&gt;=BUY_THRESHOLD,"Buy",IF(AC31&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE31" s="9" t="n"/>
-      <c r="AF31" s="9" t="n"/>
-      <c r="AG31" s="9" t="n"/>
-      <c r="AH31" s="9" t="n"/>
-      <c r="AI31" s="10" t="n"/>
+      <c r="AE31" s="13" t="n"/>
+      <c r="AF31" s="13" t="n"/>
+      <c r="AG31" s="13" t="n"/>
+      <c r="AH31" s="13" t="n"/>
+      <c r="AI31" s="14" t="n"/>
       <c r="AJ31">
         <f>IF(AC31="",-9999-ROW()*0.0000001,AC31-ROW()*0.0000001)</f>
         <v/>
@@ -3659,67 +5037,100 @@
         <f>IF(AND(OR(AD31="Maybe",AD31="Price Review"),AG31&lt;&gt;"Approved",AG31&lt;&gt;"Rejected"),IF(AC31="",0,AC31)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO31" s="18" t="n"/>
+      <c r="AP31" s="18" t="n"/>
+      <c r="AQ31" s="19" t="n"/>
+      <c r="AR31" s="19" t="n"/>
+      <c r="AS31" s="13" t="n"/>
+      <c r="AT31" s="19" t="n"/>
+      <c r="AU31" s="19" t="n"/>
+      <c r="AV31" s="19" t="n"/>
+      <c r="AW31" s="15">
+        <f>IF(OR(O31="",AV31=""),"",O31*AV31)</f>
+        <v/>
+      </c>
+      <c r="AX31" s="13" t="n"/>
+      <c r="AY31" s="13" t="n"/>
+      <c r="AZ31" s="13" t="n"/>
+      <c r="BA31" s="13" t="n"/>
+      <c r="BB31" s="13" t="n"/>
+      <c r="BC31" s="15" t="n"/>
+      <c r="BD31" s="13" t="n"/>
+      <c r="BE31" s="13">
+        <f>IF(C31="","",IF(AND(ISNUMBER(P31),P31&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB31),AB31&lt;=2),"Quality risk",IF(AND(ISNUMBER(U31),U31&lt;=2),"Aesthetic mismatch",IF(AY31="High","Too fragile",IF(AND(ISNUMBER(R31),R31&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT31),AT31&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD31="Maybe",AD31="Price Review"),"Needs partner review",IF(AD31="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF31" s="13" t="n"/>
+      <c r="BG31" s="13" t="n"/>
+      <c r="BH31" s="13" t="n"/>
+      <c r="BI31" s="13" t="n"/>
+      <c r="BJ31" s="13" t="n"/>
+      <c r="BK31" s="13" t="n"/>
+      <c r="BL31" s="13">
+        <f>IF(C31="","",IF(AND(BG31="Yes",BH31="Yes",BI31="Yes",BJ31="Yes",BK31="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="14">
+      <c r="A32" s="20">
         <f>IF(C32="","","AYN-"&amp;UPPER(LEFT(E32,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="16">
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="20" t="n"/>
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="20" t="n"/>
+      <c r="I32" s="20" t="n"/>
+      <c r="J32" s="20" t="n"/>
+      <c r="K32" s="22">
         <f>IF(I32="","",IF(J32="BDT",I32,IF(J32="USD",I32*USD_BDT,IF(J32="RMB",I32*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L32" s="16" t="n"/>
-      <c r="M32" s="17" t="n"/>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="16">
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="23" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22">
         <f>IF(K32="","",K32+IFERROR(L32,0)+(K32*IF(M32="",CUSTOMS_PCT,M32))+IF(N32="",MISC_FEE,N32))</f>
         <v/>
       </c>
-      <c r="P32" s="16">
+      <c r="P32" s="22">
         <f>IF(O32="","",ROUND(O32*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q32" s="16">
+      <c r="Q32" s="22">
         <f>IF(P32="","",P32-O32)</f>
         <v/>
       </c>
-      <c r="R32" s="17">
+      <c r="R32" s="23">
         <f>IF(OR(P32="",P32=0),"",Q32/P32)</f>
         <v/>
       </c>
-      <c r="S32" s="14" t="n"/>
-      <c r="T32" s="14" t="n"/>
-      <c r="U32" s="14" t="n"/>
-      <c r="V32" s="14" t="n"/>
-      <c r="W32" s="14" t="n"/>
-      <c r="X32" s="14" t="n"/>
-      <c r="Y32" s="14" t="n"/>
-      <c r="Z32" s="14" t="n"/>
-      <c r="AA32" s="14" t="n"/>
-      <c r="AB32" s="14" t="n"/>
-      <c r="AC32" s="18">
+      <c r="S32" s="20" t="n"/>
+      <c r="T32" s="20" t="n"/>
+      <c r="U32" s="20" t="n"/>
+      <c r="V32" s="20" t="n"/>
+      <c r="W32" s="20" t="n"/>
+      <c r="X32" s="20" t="n"/>
+      <c r="Y32" s="20" t="n"/>
+      <c r="Z32" s="20" t="n"/>
+      <c r="AA32" s="20" t="n"/>
+      <c r="AB32" s="20" t="n"/>
+      <c r="AC32" s="24">
         <f>IF(COUNT(S32:AB32)&lt;10,"",(S32*W_FEMININE+T32*W_TREND+U32*W_AESTHETIC+V32*W_STYLE+W32*W_LIGHT+X32*W_REELS+Y32*W_GIFT+Z32*W_PRICEFIT+AA32*W_DEMAND+AB32*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD32" s="14">
+      <c r="AD32" s="20">
         <f>IF(P32="","",IF(P32&gt;HARD_REJECT_PRICE,"Reject",IF(P32&gt;MAX_PRICE,"Price Review",IF(AC32="","",IF(AND(AC32&gt;=BUY_THRESHOLD,OR(AB32&lt;=2,U32&lt;=2)),"Maybe",IF(AC32&gt;=BUY_THRESHOLD,"Buy",IF(AC32&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE32" s="14" t="n"/>
-      <c r="AF32" s="14" t="n"/>
-      <c r="AG32" s="14" t="n"/>
-      <c r="AH32" s="14" t="n"/>
-      <c r="AI32" s="15" t="n"/>
+      <c r="AE32" s="20" t="n"/>
+      <c r="AF32" s="20" t="n"/>
+      <c r="AG32" s="20" t="n"/>
+      <c r="AH32" s="20" t="n"/>
+      <c r="AI32" s="21" t="n"/>
       <c r="AJ32">
         <f>IF(AC32="",-9999-ROW()*0.0000001,AC32-ROW()*0.0000001)</f>
         <v/>
@@ -3740,67 +5151,100 @@
         <f>IF(AND(OR(AD32="Maybe",AD32="Price Review"),AG32&lt;&gt;"Approved",AG32&lt;&gt;"Rejected"),IF(AC32="",0,AC32)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO32" s="25" t="n"/>
+      <c r="AP32" s="25" t="n"/>
+      <c r="AQ32" s="26" t="n"/>
+      <c r="AR32" s="26" t="n"/>
+      <c r="AS32" s="20" t="n"/>
+      <c r="AT32" s="26" t="n"/>
+      <c r="AU32" s="26" t="n"/>
+      <c r="AV32" s="26" t="n"/>
+      <c r="AW32" s="22">
+        <f>IF(OR(O32="",AV32=""),"",O32*AV32)</f>
+        <v/>
+      </c>
+      <c r="AX32" s="20" t="n"/>
+      <c r="AY32" s="20" t="n"/>
+      <c r="AZ32" s="20" t="n"/>
+      <c r="BA32" s="20" t="n"/>
+      <c r="BB32" s="20" t="n"/>
+      <c r="BC32" s="22" t="n"/>
+      <c r="BD32" s="20" t="n"/>
+      <c r="BE32" s="20">
+        <f>IF(C32="","",IF(AND(ISNUMBER(P32),P32&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB32),AB32&lt;=2),"Quality risk",IF(AND(ISNUMBER(U32),U32&lt;=2),"Aesthetic mismatch",IF(AY32="High","Too fragile",IF(AND(ISNUMBER(R32),R32&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT32),AT32&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD32="Maybe",AD32="Price Review"),"Needs partner review",IF(AD32="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF32" s="20" t="n"/>
+      <c r="BG32" s="20" t="n"/>
+      <c r="BH32" s="20" t="n"/>
+      <c r="BI32" s="20" t="n"/>
+      <c r="BJ32" s="20" t="n"/>
+      <c r="BK32" s="20" t="n"/>
+      <c r="BL32" s="20">
+        <f>IF(C32="","",IF(AND(BG32="Yes",BH32="Yes",BI32="Yes",BJ32="Yes",BK32="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="13">
         <f>IF(C33="","","AYN-"&amp;UPPER(LEFT(E33,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="11">
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="13" t="n"/>
+      <c r="K33" s="15">
         <f>IF(I33="","",IF(J33="BDT",I33,IF(J33="USD",I33*USD_BDT,IF(J33="RMB",I33*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11">
+      <c r="L33" s="15" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="15" t="n"/>
+      <c r="O33" s="15">
         <f>IF(K33="","",K33+IFERROR(L33,0)+(K33*IF(M33="",CUSTOMS_PCT,M33))+IF(N33="",MISC_FEE,N33))</f>
         <v/>
       </c>
-      <c r="P33" s="11">
+      <c r="P33" s="15">
         <f>IF(O33="","",ROUND(O33*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q33" s="11">
+      <c r="Q33" s="15">
         <f>IF(P33="","",P33-O33)</f>
         <v/>
       </c>
-      <c r="R33" s="12">
+      <c r="R33" s="16">
         <f>IF(OR(P33="",P33=0),"",Q33/P33)</f>
         <v/>
       </c>
-      <c r="S33" s="9" t="n"/>
-      <c r="T33" s="9" t="n"/>
-      <c r="U33" s="9" t="n"/>
-      <c r="V33" s="9" t="n"/>
-      <c r="W33" s="9" t="n"/>
-      <c r="X33" s="9" t="n"/>
-      <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="9" t="n"/>
-      <c r="AB33" s="9" t="n"/>
-      <c r="AC33" s="13">
+      <c r="S33" s="13" t="n"/>
+      <c r="T33" s="13" t="n"/>
+      <c r="U33" s="13" t="n"/>
+      <c r="V33" s="13" t="n"/>
+      <c r="W33" s="13" t="n"/>
+      <c r="X33" s="13" t="n"/>
+      <c r="Y33" s="13" t="n"/>
+      <c r="Z33" s="13" t="n"/>
+      <c r="AA33" s="13" t="n"/>
+      <c r="AB33" s="13" t="n"/>
+      <c r="AC33" s="17">
         <f>IF(COUNT(S33:AB33)&lt;10,"",(S33*W_FEMININE+T33*W_TREND+U33*W_AESTHETIC+V33*W_STYLE+W33*W_LIGHT+X33*W_REELS+Y33*W_GIFT+Z33*W_PRICEFIT+AA33*W_DEMAND+AB33*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD33" s="9">
+      <c r="AD33" s="13">
         <f>IF(P33="","",IF(P33&gt;HARD_REJECT_PRICE,"Reject",IF(P33&gt;MAX_PRICE,"Price Review",IF(AC33="","",IF(AND(AC33&gt;=BUY_THRESHOLD,OR(AB33&lt;=2,U33&lt;=2)),"Maybe",IF(AC33&gt;=BUY_THRESHOLD,"Buy",IF(AC33&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE33" s="9" t="n"/>
-      <c r="AF33" s="9" t="n"/>
-      <c r="AG33" s="9" t="n"/>
-      <c r="AH33" s="9" t="n"/>
-      <c r="AI33" s="10" t="n"/>
+      <c r="AE33" s="13" t="n"/>
+      <c r="AF33" s="13" t="n"/>
+      <c r="AG33" s="13" t="n"/>
+      <c r="AH33" s="13" t="n"/>
+      <c r="AI33" s="14" t="n"/>
       <c r="AJ33">
         <f>IF(AC33="",-9999-ROW()*0.0000001,AC33-ROW()*0.0000001)</f>
         <v/>
@@ -3821,67 +5265,100 @@
         <f>IF(AND(OR(AD33="Maybe",AD33="Price Review"),AG33&lt;&gt;"Approved",AG33&lt;&gt;"Rejected"),IF(AC33="",0,AC33)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO33" s="18" t="n"/>
+      <c r="AP33" s="18" t="n"/>
+      <c r="AQ33" s="19" t="n"/>
+      <c r="AR33" s="19" t="n"/>
+      <c r="AS33" s="13" t="n"/>
+      <c r="AT33" s="19" t="n"/>
+      <c r="AU33" s="19" t="n"/>
+      <c r="AV33" s="19" t="n"/>
+      <c r="AW33" s="15">
+        <f>IF(OR(O33="",AV33=""),"",O33*AV33)</f>
+        <v/>
+      </c>
+      <c r="AX33" s="13" t="n"/>
+      <c r="AY33" s="13" t="n"/>
+      <c r="AZ33" s="13" t="n"/>
+      <c r="BA33" s="13" t="n"/>
+      <c r="BB33" s="13" t="n"/>
+      <c r="BC33" s="15" t="n"/>
+      <c r="BD33" s="13" t="n"/>
+      <c r="BE33" s="13">
+        <f>IF(C33="","",IF(AND(ISNUMBER(P33),P33&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB33),AB33&lt;=2),"Quality risk",IF(AND(ISNUMBER(U33),U33&lt;=2),"Aesthetic mismatch",IF(AY33="High","Too fragile",IF(AND(ISNUMBER(R33),R33&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT33),AT33&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD33="Maybe",AD33="Price Review"),"Needs partner review",IF(AD33="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF33" s="13" t="n"/>
+      <c r="BG33" s="13" t="n"/>
+      <c r="BH33" s="13" t="n"/>
+      <c r="BI33" s="13" t="n"/>
+      <c r="BJ33" s="13" t="n"/>
+      <c r="BK33" s="13" t="n"/>
+      <c r="BL33" s="13">
+        <f>IF(C33="","",IF(AND(BG33="Yes",BH33="Yes",BI33="Yes",BJ33="Yes",BK33="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="14">
+      <c r="A34" s="20">
         <f>IF(C34="","","AYN-"&amp;UPPER(LEFT(E34,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="16">
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="22">
         <f>IF(I34="","",IF(J34="BDT",I34,IF(J34="USD",I34*USD_BDT,IF(J34="RMB",I34*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L34" s="16" t="n"/>
-      <c r="M34" s="17" t="n"/>
-      <c r="N34" s="16" t="n"/>
-      <c r="O34" s="16">
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="23" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22">
         <f>IF(K34="","",K34+IFERROR(L34,0)+(K34*IF(M34="",CUSTOMS_PCT,M34))+IF(N34="",MISC_FEE,N34))</f>
         <v/>
       </c>
-      <c r="P34" s="16">
+      <c r="P34" s="22">
         <f>IF(O34="","",ROUND(O34*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q34" s="16">
+      <c r="Q34" s="22">
         <f>IF(P34="","",P34-O34)</f>
         <v/>
       </c>
-      <c r="R34" s="17">
+      <c r="R34" s="23">
         <f>IF(OR(P34="",P34=0),"",Q34/P34)</f>
         <v/>
       </c>
-      <c r="S34" s="14" t="n"/>
-      <c r="T34" s="14" t="n"/>
-      <c r="U34" s="14" t="n"/>
-      <c r="V34" s="14" t="n"/>
-      <c r="W34" s="14" t="n"/>
-      <c r="X34" s="14" t="n"/>
-      <c r="Y34" s="14" t="n"/>
-      <c r="Z34" s="14" t="n"/>
-      <c r="AA34" s="14" t="n"/>
-      <c r="AB34" s="14" t="n"/>
-      <c r="AC34" s="18">
+      <c r="S34" s="20" t="n"/>
+      <c r="T34" s="20" t="n"/>
+      <c r="U34" s="20" t="n"/>
+      <c r="V34" s="20" t="n"/>
+      <c r="W34" s="20" t="n"/>
+      <c r="X34" s="20" t="n"/>
+      <c r="Y34" s="20" t="n"/>
+      <c r="Z34" s="20" t="n"/>
+      <c r="AA34" s="20" t="n"/>
+      <c r="AB34" s="20" t="n"/>
+      <c r="AC34" s="24">
         <f>IF(COUNT(S34:AB34)&lt;10,"",(S34*W_FEMININE+T34*W_TREND+U34*W_AESTHETIC+V34*W_STYLE+W34*W_LIGHT+X34*W_REELS+Y34*W_GIFT+Z34*W_PRICEFIT+AA34*W_DEMAND+AB34*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD34" s="14">
+      <c r="AD34" s="20">
         <f>IF(P34="","",IF(P34&gt;HARD_REJECT_PRICE,"Reject",IF(P34&gt;MAX_PRICE,"Price Review",IF(AC34="","",IF(AND(AC34&gt;=BUY_THRESHOLD,OR(AB34&lt;=2,U34&lt;=2)),"Maybe",IF(AC34&gt;=BUY_THRESHOLD,"Buy",IF(AC34&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE34" s="14" t="n"/>
-      <c r="AF34" s="14" t="n"/>
-      <c r="AG34" s="14" t="n"/>
-      <c r="AH34" s="14" t="n"/>
-      <c r="AI34" s="15" t="n"/>
+      <c r="AE34" s="20" t="n"/>
+      <c r="AF34" s="20" t="n"/>
+      <c r="AG34" s="20" t="n"/>
+      <c r="AH34" s="20" t="n"/>
+      <c r="AI34" s="21" t="n"/>
       <c r="AJ34">
         <f>IF(AC34="",-9999-ROW()*0.0000001,AC34-ROW()*0.0000001)</f>
         <v/>
@@ -3902,67 +5379,100 @@
         <f>IF(AND(OR(AD34="Maybe",AD34="Price Review"),AG34&lt;&gt;"Approved",AG34&lt;&gt;"Rejected"),IF(AC34="",0,AC34)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO34" s="25" t="n"/>
+      <c r="AP34" s="25" t="n"/>
+      <c r="AQ34" s="26" t="n"/>
+      <c r="AR34" s="26" t="n"/>
+      <c r="AS34" s="20" t="n"/>
+      <c r="AT34" s="26" t="n"/>
+      <c r="AU34" s="26" t="n"/>
+      <c r="AV34" s="26" t="n"/>
+      <c r="AW34" s="22">
+        <f>IF(OR(O34="",AV34=""),"",O34*AV34)</f>
+        <v/>
+      </c>
+      <c r="AX34" s="20" t="n"/>
+      <c r="AY34" s="20" t="n"/>
+      <c r="AZ34" s="20" t="n"/>
+      <c r="BA34" s="20" t="n"/>
+      <c r="BB34" s="20" t="n"/>
+      <c r="BC34" s="22" t="n"/>
+      <c r="BD34" s="20" t="n"/>
+      <c r="BE34" s="20">
+        <f>IF(C34="","",IF(AND(ISNUMBER(P34),P34&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB34),AB34&lt;=2),"Quality risk",IF(AND(ISNUMBER(U34),U34&lt;=2),"Aesthetic mismatch",IF(AY34="High","Too fragile",IF(AND(ISNUMBER(R34),R34&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT34),AT34&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD34="Maybe",AD34="Price Review"),"Needs partner review",IF(AD34="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF34" s="20" t="n"/>
+      <c r="BG34" s="20" t="n"/>
+      <c r="BH34" s="20" t="n"/>
+      <c r="BI34" s="20" t="n"/>
+      <c r="BJ34" s="20" t="n"/>
+      <c r="BK34" s="20" t="n"/>
+      <c r="BL34" s="20">
+        <f>IF(C34="","",IF(AND(BG34="Yes",BH34="Yes",BI34="Yes",BJ34="Yes",BK34="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9">
+      <c r="A35" s="13">
         <f>IF(C35="","","AYN-"&amp;UPPER(LEFT(E35,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="11">
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="13" t="n"/>
+      <c r="J35" s="13" t="n"/>
+      <c r="K35" s="15">
         <f>IF(I35="","",IF(J35="BDT",I35,IF(J35="USD",I35*USD_BDT,IF(J35="RMB",I35*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="11" t="n"/>
-      <c r="O35" s="11">
+      <c r="L35" s="15" t="n"/>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="15" t="n"/>
+      <c r="O35" s="15">
         <f>IF(K35="","",K35+IFERROR(L35,0)+(K35*IF(M35="",CUSTOMS_PCT,M35))+IF(N35="",MISC_FEE,N35))</f>
         <v/>
       </c>
-      <c r="P35" s="11">
+      <c r="P35" s="15">
         <f>IF(O35="","",ROUND(O35*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q35" s="11">
+      <c r="Q35" s="15">
         <f>IF(P35="","",P35-O35)</f>
         <v/>
       </c>
-      <c r="R35" s="12">
+      <c r="R35" s="16">
         <f>IF(OR(P35="",P35=0),"",Q35/P35)</f>
         <v/>
       </c>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="9" t="n"/>
-      <c r="U35" s="9" t="n"/>
-      <c r="V35" s="9" t="n"/>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
-      <c r="Z35" s="9" t="n"/>
-      <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
-      <c r="AC35" s="13">
+      <c r="S35" s="13" t="n"/>
+      <c r="T35" s="13" t="n"/>
+      <c r="U35" s="13" t="n"/>
+      <c r="V35" s="13" t="n"/>
+      <c r="W35" s="13" t="n"/>
+      <c r="X35" s="13" t="n"/>
+      <c r="Y35" s="13" t="n"/>
+      <c r="Z35" s="13" t="n"/>
+      <c r="AA35" s="13" t="n"/>
+      <c r="AB35" s="13" t="n"/>
+      <c r="AC35" s="17">
         <f>IF(COUNT(S35:AB35)&lt;10,"",(S35*W_FEMININE+T35*W_TREND+U35*W_AESTHETIC+V35*W_STYLE+W35*W_LIGHT+X35*W_REELS+Y35*W_GIFT+Z35*W_PRICEFIT+AA35*W_DEMAND+AB35*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD35" s="9">
+      <c r="AD35" s="13">
         <f>IF(P35="","",IF(P35&gt;HARD_REJECT_PRICE,"Reject",IF(P35&gt;MAX_PRICE,"Price Review",IF(AC35="","",IF(AND(AC35&gt;=BUY_THRESHOLD,OR(AB35&lt;=2,U35&lt;=2)),"Maybe",IF(AC35&gt;=BUY_THRESHOLD,"Buy",IF(AC35&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE35" s="9" t="n"/>
-      <c r="AF35" s="9" t="n"/>
-      <c r="AG35" s="9" t="n"/>
-      <c r="AH35" s="9" t="n"/>
-      <c r="AI35" s="10" t="n"/>
+      <c r="AE35" s="13" t="n"/>
+      <c r="AF35" s="13" t="n"/>
+      <c r="AG35" s="13" t="n"/>
+      <c r="AH35" s="13" t="n"/>
+      <c r="AI35" s="14" t="n"/>
       <c r="AJ35">
         <f>IF(AC35="",-9999-ROW()*0.0000001,AC35-ROW()*0.0000001)</f>
         <v/>
@@ -3983,67 +5493,100 @@
         <f>IF(AND(OR(AD35="Maybe",AD35="Price Review"),AG35&lt;&gt;"Approved",AG35&lt;&gt;"Rejected"),IF(AC35="",0,AC35)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO35" s="18" t="n"/>
+      <c r="AP35" s="18" t="n"/>
+      <c r="AQ35" s="19" t="n"/>
+      <c r="AR35" s="19" t="n"/>
+      <c r="AS35" s="13" t="n"/>
+      <c r="AT35" s="19" t="n"/>
+      <c r="AU35" s="19" t="n"/>
+      <c r="AV35" s="19" t="n"/>
+      <c r="AW35" s="15">
+        <f>IF(OR(O35="",AV35=""),"",O35*AV35)</f>
+        <v/>
+      </c>
+      <c r="AX35" s="13" t="n"/>
+      <c r="AY35" s="13" t="n"/>
+      <c r="AZ35" s="13" t="n"/>
+      <c r="BA35" s="13" t="n"/>
+      <c r="BB35" s="13" t="n"/>
+      <c r="BC35" s="15" t="n"/>
+      <c r="BD35" s="13" t="n"/>
+      <c r="BE35" s="13">
+        <f>IF(C35="","",IF(AND(ISNUMBER(P35),P35&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB35),AB35&lt;=2),"Quality risk",IF(AND(ISNUMBER(U35),U35&lt;=2),"Aesthetic mismatch",IF(AY35="High","Too fragile",IF(AND(ISNUMBER(R35),R35&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT35),AT35&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD35="Maybe",AD35="Price Review"),"Needs partner review",IF(AD35="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF35" s="13" t="n"/>
+      <c r="BG35" s="13" t="n"/>
+      <c r="BH35" s="13" t="n"/>
+      <c r="BI35" s="13" t="n"/>
+      <c r="BJ35" s="13" t="n"/>
+      <c r="BK35" s="13" t="n"/>
+      <c r="BL35" s="13">
+        <f>IF(C35="","",IF(AND(BG35="Yes",BH35="Yes",BI35="Yes",BJ35="Yes",BK35="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="14">
+      <c r="A36" s="20">
         <f>IF(C36="","","AYN-"&amp;UPPER(LEFT(E36,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="14" t="n"/>
-      <c r="I36" s="14" t="n"/>
-      <c r="J36" s="14" t="n"/>
-      <c r="K36" s="16">
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="22">
         <f>IF(I36="","",IF(J36="BDT",I36,IF(J36="USD",I36*USD_BDT,IF(J36="RMB",I36*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L36" s="16" t="n"/>
-      <c r="M36" s="17" t="n"/>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="16">
+      <c r="L36" s="22" t="n"/>
+      <c r="M36" s="23" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22">
         <f>IF(K36="","",K36+IFERROR(L36,0)+(K36*IF(M36="",CUSTOMS_PCT,M36))+IF(N36="",MISC_FEE,N36))</f>
         <v/>
       </c>
-      <c r="P36" s="16">
+      <c r="P36" s="22">
         <f>IF(O36="","",ROUND(O36*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q36" s="16">
+      <c r="Q36" s="22">
         <f>IF(P36="","",P36-O36)</f>
         <v/>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="23">
         <f>IF(OR(P36="",P36=0),"",Q36/P36)</f>
         <v/>
       </c>
-      <c r="S36" s="14" t="n"/>
-      <c r="T36" s="14" t="n"/>
-      <c r="U36" s="14" t="n"/>
-      <c r="V36" s="14" t="n"/>
-      <c r="W36" s="14" t="n"/>
-      <c r="X36" s="14" t="n"/>
-      <c r="Y36" s="14" t="n"/>
-      <c r="Z36" s="14" t="n"/>
-      <c r="AA36" s="14" t="n"/>
-      <c r="AB36" s="14" t="n"/>
-      <c r="AC36" s="18">
+      <c r="S36" s="20" t="n"/>
+      <c r="T36" s="20" t="n"/>
+      <c r="U36" s="20" t="n"/>
+      <c r="V36" s="20" t="n"/>
+      <c r="W36" s="20" t="n"/>
+      <c r="X36" s="20" t="n"/>
+      <c r="Y36" s="20" t="n"/>
+      <c r="Z36" s="20" t="n"/>
+      <c r="AA36" s="20" t="n"/>
+      <c r="AB36" s="20" t="n"/>
+      <c r="AC36" s="24">
         <f>IF(COUNT(S36:AB36)&lt;10,"",(S36*W_FEMININE+T36*W_TREND+U36*W_AESTHETIC+V36*W_STYLE+W36*W_LIGHT+X36*W_REELS+Y36*W_GIFT+Z36*W_PRICEFIT+AA36*W_DEMAND+AB36*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD36" s="14">
+      <c r="AD36" s="20">
         <f>IF(P36="","",IF(P36&gt;HARD_REJECT_PRICE,"Reject",IF(P36&gt;MAX_PRICE,"Price Review",IF(AC36="","",IF(AND(AC36&gt;=BUY_THRESHOLD,OR(AB36&lt;=2,U36&lt;=2)),"Maybe",IF(AC36&gt;=BUY_THRESHOLD,"Buy",IF(AC36&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE36" s="14" t="n"/>
-      <c r="AF36" s="14" t="n"/>
-      <c r="AG36" s="14" t="n"/>
-      <c r="AH36" s="14" t="n"/>
-      <c r="AI36" s="15" t="n"/>
+      <c r="AE36" s="20" t="n"/>
+      <c r="AF36" s="20" t="n"/>
+      <c r="AG36" s="20" t="n"/>
+      <c r="AH36" s="20" t="n"/>
+      <c r="AI36" s="21" t="n"/>
       <c r="AJ36">
         <f>IF(AC36="",-9999-ROW()*0.0000001,AC36-ROW()*0.0000001)</f>
         <v/>
@@ -4064,67 +5607,100 @@
         <f>IF(AND(OR(AD36="Maybe",AD36="Price Review"),AG36&lt;&gt;"Approved",AG36&lt;&gt;"Rejected"),IF(AC36="",0,AC36)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO36" s="25" t="n"/>
+      <c r="AP36" s="25" t="n"/>
+      <c r="AQ36" s="26" t="n"/>
+      <c r="AR36" s="26" t="n"/>
+      <c r="AS36" s="20" t="n"/>
+      <c r="AT36" s="26" t="n"/>
+      <c r="AU36" s="26" t="n"/>
+      <c r="AV36" s="26" t="n"/>
+      <c r="AW36" s="22">
+        <f>IF(OR(O36="",AV36=""),"",O36*AV36)</f>
+        <v/>
+      </c>
+      <c r="AX36" s="20" t="n"/>
+      <c r="AY36" s="20" t="n"/>
+      <c r="AZ36" s="20" t="n"/>
+      <c r="BA36" s="20" t="n"/>
+      <c r="BB36" s="20" t="n"/>
+      <c r="BC36" s="22" t="n"/>
+      <c r="BD36" s="20" t="n"/>
+      <c r="BE36" s="20">
+        <f>IF(C36="","",IF(AND(ISNUMBER(P36),P36&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB36),AB36&lt;=2),"Quality risk",IF(AND(ISNUMBER(U36),U36&lt;=2),"Aesthetic mismatch",IF(AY36="High","Too fragile",IF(AND(ISNUMBER(R36),R36&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT36),AT36&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD36="Maybe",AD36="Price Review"),"Needs partner review",IF(AD36="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF36" s="20" t="n"/>
+      <c r="BG36" s="20" t="n"/>
+      <c r="BH36" s="20" t="n"/>
+      <c r="BI36" s="20" t="n"/>
+      <c r="BJ36" s="20" t="n"/>
+      <c r="BK36" s="20" t="n"/>
+      <c r="BL36" s="20">
+        <f>IF(C36="","",IF(AND(BG36="Yes",BH36="Yes",BI36="Yes",BJ36="Yes",BK36="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9">
+      <c r="A37" s="13">
         <f>IF(C37="","","AYN-"&amp;UPPER(LEFT(E37,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="11">
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="13" t="n"/>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="13" t="n"/>
+      <c r="K37" s="15">
         <f>IF(I37="","",IF(J37="BDT",I37,IF(J37="USD",I37*USD_BDT,IF(J37="RMB",I37*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="11">
+      <c r="L37" s="15" t="n"/>
+      <c r="M37" s="16" t="n"/>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15">
         <f>IF(K37="","",K37+IFERROR(L37,0)+(K37*IF(M37="",CUSTOMS_PCT,M37))+IF(N37="",MISC_FEE,N37))</f>
         <v/>
       </c>
-      <c r="P37" s="11">
+      <c r="P37" s="15">
         <f>IF(O37="","",ROUND(O37*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q37" s="11">
+      <c r="Q37" s="15">
         <f>IF(P37="","",P37-O37)</f>
         <v/>
       </c>
-      <c r="R37" s="12">
+      <c r="R37" s="16">
         <f>IF(OR(P37="",P37=0),"",Q37/P37)</f>
         <v/>
       </c>
-      <c r="S37" s="9" t="n"/>
-      <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n"/>
-      <c r="V37" s="9" t="n"/>
-      <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
-      <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="9" t="n"/>
-      <c r="AA37" s="9" t="n"/>
-      <c r="AB37" s="9" t="n"/>
-      <c r="AC37" s="13">
+      <c r="S37" s="13" t="n"/>
+      <c r="T37" s="13" t="n"/>
+      <c r="U37" s="13" t="n"/>
+      <c r="V37" s="13" t="n"/>
+      <c r="W37" s="13" t="n"/>
+      <c r="X37" s="13" t="n"/>
+      <c r="Y37" s="13" t="n"/>
+      <c r="Z37" s="13" t="n"/>
+      <c r="AA37" s="13" t="n"/>
+      <c r="AB37" s="13" t="n"/>
+      <c r="AC37" s="17">
         <f>IF(COUNT(S37:AB37)&lt;10,"",(S37*W_FEMININE+T37*W_TREND+U37*W_AESTHETIC+V37*W_STYLE+W37*W_LIGHT+X37*W_REELS+Y37*W_GIFT+Z37*W_PRICEFIT+AA37*W_DEMAND+AB37*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD37" s="9">
+      <c r="AD37" s="13">
         <f>IF(P37="","",IF(P37&gt;HARD_REJECT_PRICE,"Reject",IF(P37&gt;MAX_PRICE,"Price Review",IF(AC37="","",IF(AND(AC37&gt;=BUY_THRESHOLD,OR(AB37&lt;=2,U37&lt;=2)),"Maybe",IF(AC37&gt;=BUY_THRESHOLD,"Buy",IF(AC37&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE37" s="9" t="n"/>
-      <c r="AF37" s="9" t="n"/>
-      <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
-      <c r="AI37" s="10" t="n"/>
+      <c r="AE37" s="13" t="n"/>
+      <c r="AF37" s="13" t="n"/>
+      <c r="AG37" s="13" t="n"/>
+      <c r="AH37" s="13" t="n"/>
+      <c r="AI37" s="14" t="n"/>
       <c r="AJ37">
         <f>IF(AC37="",-9999-ROW()*0.0000001,AC37-ROW()*0.0000001)</f>
         <v/>
@@ -4145,67 +5721,100 @@
         <f>IF(AND(OR(AD37="Maybe",AD37="Price Review"),AG37&lt;&gt;"Approved",AG37&lt;&gt;"Rejected"),IF(AC37="",0,AC37)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO37" s="18" t="n"/>
+      <c r="AP37" s="18" t="n"/>
+      <c r="AQ37" s="19" t="n"/>
+      <c r="AR37" s="19" t="n"/>
+      <c r="AS37" s="13" t="n"/>
+      <c r="AT37" s="19" t="n"/>
+      <c r="AU37" s="19" t="n"/>
+      <c r="AV37" s="19" t="n"/>
+      <c r="AW37" s="15">
+        <f>IF(OR(O37="",AV37=""),"",O37*AV37)</f>
+        <v/>
+      </c>
+      <c r="AX37" s="13" t="n"/>
+      <c r="AY37" s="13" t="n"/>
+      <c r="AZ37" s="13" t="n"/>
+      <c r="BA37" s="13" t="n"/>
+      <c r="BB37" s="13" t="n"/>
+      <c r="BC37" s="15" t="n"/>
+      <c r="BD37" s="13" t="n"/>
+      <c r="BE37" s="13">
+        <f>IF(C37="","",IF(AND(ISNUMBER(P37),P37&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB37),AB37&lt;=2),"Quality risk",IF(AND(ISNUMBER(U37),U37&lt;=2),"Aesthetic mismatch",IF(AY37="High","Too fragile",IF(AND(ISNUMBER(R37),R37&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT37),AT37&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD37="Maybe",AD37="Price Review"),"Needs partner review",IF(AD37="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF37" s="13" t="n"/>
+      <c r="BG37" s="13" t="n"/>
+      <c r="BH37" s="13" t="n"/>
+      <c r="BI37" s="13" t="n"/>
+      <c r="BJ37" s="13" t="n"/>
+      <c r="BK37" s="13" t="n"/>
+      <c r="BL37" s="13">
+        <f>IF(C37="","",IF(AND(BG37="Yes",BH37="Yes",BI37="Yes",BJ37="Yes",BK37="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="14">
+      <c r="A38" s="20">
         <f>IF(C38="","","AYN-"&amp;UPPER(LEFT(E38,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="16">
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="20" t="n"/>
+      <c r="J38" s="20" t="n"/>
+      <c r="K38" s="22">
         <f>IF(I38="","",IF(J38="BDT",I38,IF(J38="USD",I38*USD_BDT,IF(J38="RMB",I38*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L38" s="16" t="n"/>
-      <c r="M38" s="17" t="n"/>
-      <c r="N38" s="16" t="n"/>
-      <c r="O38" s="16">
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="23" t="n"/>
+      <c r="N38" s="22" t="n"/>
+      <c r="O38" s="22">
         <f>IF(K38="","",K38+IFERROR(L38,0)+(K38*IF(M38="",CUSTOMS_PCT,M38))+IF(N38="",MISC_FEE,N38))</f>
         <v/>
       </c>
-      <c r="P38" s="16">
+      <c r="P38" s="22">
         <f>IF(O38="","",ROUND(O38*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q38" s="16">
+      <c r="Q38" s="22">
         <f>IF(P38="","",P38-O38)</f>
         <v/>
       </c>
-      <c r="R38" s="17">
+      <c r="R38" s="23">
         <f>IF(OR(P38="",P38=0),"",Q38/P38)</f>
         <v/>
       </c>
-      <c r="S38" s="14" t="n"/>
-      <c r="T38" s="14" t="n"/>
-      <c r="U38" s="14" t="n"/>
-      <c r="V38" s="14" t="n"/>
-      <c r="W38" s="14" t="n"/>
-      <c r="X38" s="14" t="n"/>
-      <c r="Y38" s="14" t="n"/>
-      <c r="Z38" s="14" t="n"/>
-      <c r="AA38" s="14" t="n"/>
-      <c r="AB38" s="14" t="n"/>
-      <c r="AC38" s="18">
+      <c r="S38" s="20" t="n"/>
+      <c r="T38" s="20" t="n"/>
+      <c r="U38" s="20" t="n"/>
+      <c r="V38" s="20" t="n"/>
+      <c r="W38" s="20" t="n"/>
+      <c r="X38" s="20" t="n"/>
+      <c r="Y38" s="20" t="n"/>
+      <c r="Z38" s="20" t="n"/>
+      <c r="AA38" s="20" t="n"/>
+      <c r="AB38" s="20" t="n"/>
+      <c r="AC38" s="24">
         <f>IF(COUNT(S38:AB38)&lt;10,"",(S38*W_FEMININE+T38*W_TREND+U38*W_AESTHETIC+V38*W_STYLE+W38*W_LIGHT+X38*W_REELS+Y38*W_GIFT+Z38*W_PRICEFIT+AA38*W_DEMAND+AB38*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD38" s="14">
+      <c r="AD38" s="20">
         <f>IF(P38="","",IF(P38&gt;HARD_REJECT_PRICE,"Reject",IF(P38&gt;MAX_PRICE,"Price Review",IF(AC38="","",IF(AND(AC38&gt;=BUY_THRESHOLD,OR(AB38&lt;=2,U38&lt;=2)),"Maybe",IF(AC38&gt;=BUY_THRESHOLD,"Buy",IF(AC38&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE38" s="14" t="n"/>
-      <c r="AF38" s="14" t="n"/>
-      <c r="AG38" s="14" t="n"/>
-      <c r="AH38" s="14" t="n"/>
-      <c r="AI38" s="15" t="n"/>
+      <c r="AE38" s="20" t="n"/>
+      <c r="AF38" s="20" t="n"/>
+      <c r="AG38" s="20" t="n"/>
+      <c r="AH38" s="20" t="n"/>
+      <c r="AI38" s="21" t="n"/>
       <c r="AJ38">
         <f>IF(AC38="",-9999-ROW()*0.0000001,AC38-ROW()*0.0000001)</f>
         <v/>
@@ -4226,67 +5835,100 @@
         <f>IF(AND(OR(AD38="Maybe",AD38="Price Review"),AG38&lt;&gt;"Approved",AG38&lt;&gt;"Rejected"),IF(AC38="",0,AC38)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO38" s="25" t="n"/>
+      <c r="AP38" s="25" t="n"/>
+      <c r="AQ38" s="26" t="n"/>
+      <c r="AR38" s="26" t="n"/>
+      <c r="AS38" s="20" t="n"/>
+      <c r="AT38" s="26" t="n"/>
+      <c r="AU38" s="26" t="n"/>
+      <c r="AV38" s="26" t="n"/>
+      <c r="AW38" s="22">
+        <f>IF(OR(O38="",AV38=""),"",O38*AV38)</f>
+        <v/>
+      </c>
+      <c r="AX38" s="20" t="n"/>
+      <c r="AY38" s="20" t="n"/>
+      <c r="AZ38" s="20" t="n"/>
+      <c r="BA38" s="20" t="n"/>
+      <c r="BB38" s="20" t="n"/>
+      <c r="BC38" s="22" t="n"/>
+      <c r="BD38" s="20" t="n"/>
+      <c r="BE38" s="20">
+        <f>IF(C38="","",IF(AND(ISNUMBER(P38),P38&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB38),AB38&lt;=2),"Quality risk",IF(AND(ISNUMBER(U38),U38&lt;=2),"Aesthetic mismatch",IF(AY38="High","Too fragile",IF(AND(ISNUMBER(R38),R38&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT38),AT38&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD38="Maybe",AD38="Price Review"),"Needs partner review",IF(AD38="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF38" s="20" t="n"/>
+      <c r="BG38" s="20" t="n"/>
+      <c r="BH38" s="20" t="n"/>
+      <c r="BI38" s="20" t="n"/>
+      <c r="BJ38" s="20" t="n"/>
+      <c r="BK38" s="20" t="n"/>
+      <c r="BL38" s="20">
+        <f>IF(C38="","",IF(AND(BG38="Yes",BH38="Yes",BI38="Yes",BJ38="Yes",BK38="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9">
+      <c r="A39" s="13">
         <f>IF(C39="","","AYN-"&amp;UPPER(LEFT(E39,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="11">
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="13" t="n"/>
+      <c r="K39" s="15">
         <f>IF(I39="","",IF(J39="BDT",I39,IF(J39="USD",I39*USD_BDT,IF(J39="RMB",I39*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="11" t="n"/>
-      <c r="O39" s="11">
+      <c r="L39" s="15" t="n"/>
+      <c r="M39" s="16" t="n"/>
+      <c r="N39" s="15" t="n"/>
+      <c r="O39" s="15">
         <f>IF(K39="","",K39+IFERROR(L39,0)+(K39*IF(M39="",CUSTOMS_PCT,M39))+IF(N39="",MISC_FEE,N39))</f>
         <v/>
       </c>
-      <c r="P39" s="11">
+      <c r="P39" s="15">
         <f>IF(O39="","",ROUND(O39*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q39" s="11">
+      <c r="Q39" s="15">
         <f>IF(P39="","",P39-O39)</f>
         <v/>
       </c>
-      <c r="R39" s="12">
+      <c r="R39" s="16">
         <f>IF(OR(P39="",P39=0),"",Q39/P39)</f>
         <v/>
       </c>
-      <c r="S39" s="9" t="n"/>
-      <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n"/>
-      <c r="V39" s="9" t="n"/>
-      <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n"/>
-      <c r="Y39" s="9" t="n"/>
-      <c r="Z39" s="9" t="n"/>
-      <c r="AA39" s="9" t="n"/>
-      <c r="AB39" s="9" t="n"/>
-      <c r="AC39" s="13">
+      <c r="S39" s="13" t="n"/>
+      <c r="T39" s="13" t="n"/>
+      <c r="U39" s="13" t="n"/>
+      <c r="V39" s="13" t="n"/>
+      <c r="W39" s="13" t="n"/>
+      <c r="X39" s="13" t="n"/>
+      <c r="Y39" s="13" t="n"/>
+      <c r="Z39" s="13" t="n"/>
+      <c r="AA39" s="13" t="n"/>
+      <c r="AB39" s="13" t="n"/>
+      <c r="AC39" s="17">
         <f>IF(COUNT(S39:AB39)&lt;10,"",(S39*W_FEMININE+T39*W_TREND+U39*W_AESTHETIC+V39*W_STYLE+W39*W_LIGHT+X39*W_REELS+Y39*W_GIFT+Z39*W_PRICEFIT+AA39*W_DEMAND+AB39*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD39" s="9">
+      <c r="AD39" s="13">
         <f>IF(P39="","",IF(P39&gt;HARD_REJECT_PRICE,"Reject",IF(P39&gt;MAX_PRICE,"Price Review",IF(AC39="","",IF(AND(AC39&gt;=BUY_THRESHOLD,OR(AB39&lt;=2,U39&lt;=2)),"Maybe",IF(AC39&gt;=BUY_THRESHOLD,"Buy",IF(AC39&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE39" s="9" t="n"/>
-      <c r="AF39" s="9" t="n"/>
-      <c r="AG39" s="9" t="n"/>
-      <c r="AH39" s="9" t="n"/>
-      <c r="AI39" s="10" t="n"/>
+      <c r="AE39" s="13" t="n"/>
+      <c r="AF39" s="13" t="n"/>
+      <c r="AG39" s="13" t="n"/>
+      <c r="AH39" s="13" t="n"/>
+      <c r="AI39" s="14" t="n"/>
       <c r="AJ39">
         <f>IF(AC39="",-9999-ROW()*0.0000001,AC39-ROW()*0.0000001)</f>
         <v/>
@@ -4307,67 +5949,100 @@
         <f>IF(AND(OR(AD39="Maybe",AD39="Price Review"),AG39&lt;&gt;"Approved",AG39&lt;&gt;"Rejected"),IF(AC39="",0,AC39)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO39" s="18" t="n"/>
+      <c r="AP39" s="18" t="n"/>
+      <c r="AQ39" s="19" t="n"/>
+      <c r="AR39" s="19" t="n"/>
+      <c r="AS39" s="13" t="n"/>
+      <c r="AT39" s="19" t="n"/>
+      <c r="AU39" s="19" t="n"/>
+      <c r="AV39" s="19" t="n"/>
+      <c r="AW39" s="15">
+        <f>IF(OR(O39="",AV39=""),"",O39*AV39)</f>
+        <v/>
+      </c>
+      <c r="AX39" s="13" t="n"/>
+      <c r="AY39" s="13" t="n"/>
+      <c r="AZ39" s="13" t="n"/>
+      <c r="BA39" s="13" t="n"/>
+      <c r="BB39" s="13" t="n"/>
+      <c r="BC39" s="15" t="n"/>
+      <c r="BD39" s="13" t="n"/>
+      <c r="BE39" s="13">
+        <f>IF(C39="","",IF(AND(ISNUMBER(P39),P39&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB39),AB39&lt;=2),"Quality risk",IF(AND(ISNUMBER(U39),U39&lt;=2),"Aesthetic mismatch",IF(AY39="High","Too fragile",IF(AND(ISNUMBER(R39),R39&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT39),AT39&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD39="Maybe",AD39="Price Review"),"Needs partner review",IF(AD39="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF39" s="13" t="n"/>
+      <c r="BG39" s="13" t="n"/>
+      <c r="BH39" s="13" t="n"/>
+      <c r="BI39" s="13" t="n"/>
+      <c r="BJ39" s="13" t="n"/>
+      <c r="BK39" s="13" t="n"/>
+      <c r="BL39" s="13">
+        <f>IF(C39="","",IF(AND(BG39="Yes",BH39="Yes",BI39="Yes",BJ39="Yes",BK39="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="14">
+      <c r="A40" s="20">
         <f>IF(C40="","","AYN-"&amp;UPPER(LEFT(E40,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="14" t="n"/>
-      <c r="I40" s="14" t="n"/>
-      <c r="J40" s="14" t="n"/>
-      <c r="K40" s="16">
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="22">
         <f>IF(I40="","",IF(J40="BDT",I40,IF(J40="USD",I40*USD_BDT,IF(J40="RMB",I40*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L40" s="16" t="n"/>
-      <c r="M40" s="17" t="n"/>
-      <c r="N40" s="16" t="n"/>
-      <c r="O40" s="16">
+      <c r="L40" s="22" t="n"/>
+      <c r="M40" s="23" t="n"/>
+      <c r="N40" s="22" t="n"/>
+      <c r="O40" s="22">
         <f>IF(K40="","",K40+IFERROR(L40,0)+(K40*IF(M40="",CUSTOMS_PCT,M40))+IF(N40="",MISC_FEE,N40))</f>
         <v/>
       </c>
-      <c r="P40" s="16">
+      <c r="P40" s="22">
         <f>IF(O40="","",ROUND(O40*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q40" s="16">
+      <c r="Q40" s="22">
         <f>IF(P40="","",P40-O40)</f>
         <v/>
       </c>
-      <c r="R40" s="17">
+      <c r="R40" s="23">
         <f>IF(OR(P40="",P40=0),"",Q40/P40)</f>
         <v/>
       </c>
-      <c r="S40" s="14" t="n"/>
-      <c r="T40" s="14" t="n"/>
-      <c r="U40" s="14" t="n"/>
-      <c r="V40" s="14" t="n"/>
-      <c r="W40" s="14" t="n"/>
-      <c r="X40" s="14" t="n"/>
-      <c r="Y40" s="14" t="n"/>
-      <c r="Z40" s="14" t="n"/>
-      <c r="AA40" s="14" t="n"/>
-      <c r="AB40" s="14" t="n"/>
-      <c r="AC40" s="18">
+      <c r="S40" s="20" t="n"/>
+      <c r="T40" s="20" t="n"/>
+      <c r="U40" s="20" t="n"/>
+      <c r="V40" s="20" t="n"/>
+      <c r="W40" s="20" t="n"/>
+      <c r="X40" s="20" t="n"/>
+      <c r="Y40" s="20" t="n"/>
+      <c r="Z40" s="20" t="n"/>
+      <c r="AA40" s="20" t="n"/>
+      <c r="AB40" s="20" t="n"/>
+      <c r="AC40" s="24">
         <f>IF(COUNT(S40:AB40)&lt;10,"",(S40*W_FEMININE+T40*W_TREND+U40*W_AESTHETIC+V40*W_STYLE+W40*W_LIGHT+X40*W_REELS+Y40*W_GIFT+Z40*W_PRICEFIT+AA40*W_DEMAND+AB40*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD40" s="14">
+      <c r="AD40" s="20">
         <f>IF(P40="","",IF(P40&gt;HARD_REJECT_PRICE,"Reject",IF(P40&gt;MAX_PRICE,"Price Review",IF(AC40="","",IF(AND(AC40&gt;=BUY_THRESHOLD,OR(AB40&lt;=2,U40&lt;=2)),"Maybe",IF(AC40&gt;=BUY_THRESHOLD,"Buy",IF(AC40&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE40" s="14" t="n"/>
-      <c r="AF40" s="14" t="n"/>
-      <c r="AG40" s="14" t="n"/>
-      <c r="AH40" s="14" t="n"/>
-      <c r="AI40" s="15" t="n"/>
+      <c r="AE40" s="20" t="n"/>
+      <c r="AF40" s="20" t="n"/>
+      <c r="AG40" s="20" t="n"/>
+      <c r="AH40" s="20" t="n"/>
+      <c r="AI40" s="21" t="n"/>
       <c r="AJ40">
         <f>IF(AC40="",-9999-ROW()*0.0000001,AC40-ROW()*0.0000001)</f>
         <v/>
@@ -4388,67 +6063,100 @@
         <f>IF(AND(OR(AD40="Maybe",AD40="Price Review"),AG40&lt;&gt;"Approved",AG40&lt;&gt;"Rejected"),IF(AC40="",0,AC40)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO40" s="25" t="n"/>
+      <c r="AP40" s="25" t="n"/>
+      <c r="AQ40" s="26" t="n"/>
+      <c r="AR40" s="26" t="n"/>
+      <c r="AS40" s="20" t="n"/>
+      <c r="AT40" s="26" t="n"/>
+      <c r="AU40" s="26" t="n"/>
+      <c r="AV40" s="26" t="n"/>
+      <c r="AW40" s="22">
+        <f>IF(OR(O40="",AV40=""),"",O40*AV40)</f>
+        <v/>
+      </c>
+      <c r="AX40" s="20" t="n"/>
+      <c r="AY40" s="20" t="n"/>
+      <c r="AZ40" s="20" t="n"/>
+      <c r="BA40" s="20" t="n"/>
+      <c r="BB40" s="20" t="n"/>
+      <c r="BC40" s="22" t="n"/>
+      <c r="BD40" s="20" t="n"/>
+      <c r="BE40" s="20">
+        <f>IF(C40="","",IF(AND(ISNUMBER(P40),P40&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB40),AB40&lt;=2),"Quality risk",IF(AND(ISNUMBER(U40),U40&lt;=2),"Aesthetic mismatch",IF(AY40="High","Too fragile",IF(AND(ISNUMBER(R40),R40&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT40),AT40&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD40="Maybe",AD40="Price Review"),"Needs partner review",IF(AD40="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF40" s="20" t="n"/>
+      <c r="BG40" s="20" t="n"/>
+      <c r="BH40" s="20" t="n"/>
+      <c r="BI40" s="20" t="n"/>
+      <c r="BJ40" s="20" t="n"/>
+      <c r="BK40" s="20" t="n"/>
+      <c r="BL40" s="20">
+        <f>IF(C40="","",IF(AND(BG40="Yes",BH40="Yes",BI40="Yes",BJ40="Yes",BK40="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9">
+      <c r="A41" s="13">
         <f>IF(C41="","","AYN-"&amp;UPPER(LEFT(E41,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="11">
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="15">
         <f>IF(I41="","",IF(J41="BDT",I41,IF(J41="USD",I41*USD_BDT,IF(J41="RMB",I41*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="11" t="n"/>
-      <c r="O41" s="11">
+      <c r="L41" s="15" t="n"/>
+      <c r="M41" s="16" t="n"/>
+      <c r="N41" s="15" t="n"/>
+      <c r="O41" s="15">
         <f>IF(K41="","",K41+IFERROR(L41,0)+(K41*IF(M41="",CUSTOMS_PCT,M41))+IF(N41="",MISC_FEE,N41))</f>
         <v/>
       </c>
-      <c r="P41" s="11">
+      <c r="P41" s="15">
         <f>IF(O41="","",ROUND(O41*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q41" s="11">
+      <c r="Q41" s="15">
         <f>IF(P41="","",P41-O41)</f>
         <v/>
       </c>
-      <c r="R41" s="12">
+      <c r="R41" s="16">
         <f>IF(OR(P41="",P41=0),"",Q41/P41)</f>
         <v/>
       </c>
-      <c r="S41" s="9" t="n"/>
-      <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n"/>
-      <c r="V41" s="9" t="n"/>
-      <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
-      <c r="Y41" s="9" t="n"/>
-      <c r="Z41" s="9" t="n"/>
-      <c r="AA41" s="9" t="n"/>
-      <c r="AB41" s="9" t="n"/>
-      <c r="AC41" s="13">
+      <c r="S41" s="13" t="n"/>
+      <c r="T41" s="13" t="n"/>
+      <c r="U41" s="13" t="n"/>
+      <c r="V41" s="13" t="n"/>
+      <c r="W41" s="13" t="n"/>
+      <c r="X41" s="13" t="n"/>
+      <c r="Y41" s="13" t="n"/>
+      <c r="Z41" s="13" t="n"/>
+      <c r="AA41" s="13" t="n"/>
+      <c r="AB41" s="13" t="n"/>
+      <c r="AC41" s="17">
         <f>IF(COUNT(S41:AB41)&lt;10,"",(S41*W_FEMININE+T41*W_TREND+U41*W_AESTHETIC+V41*W_STYLE+W41*W_LIGHT+X41*W_REELS+Y41*W_GIFT+Z41*W_PRICEFIT+AA41*W_DEMAND+AB41*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD41" s="9">
+      <c r="AD41" s="13">
         <f>IF(P41="","",IF(P41&gt;HARD_REJECT_PRICE,"Reject",IF(P41&gt;MAX_PRICE,"Price Review",IF(AC41="","",IF(AND(AC41&gt;=BUY_THRESHOLD,OR(AB41&lt;=2,U41&lt;=2)),"Maybe",IF(AC41&gt;=BUY_THRESHOLD,"Buy",IF(AC41&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE41" s="9" t="n"/>
-      <c r="AF41" s="9" t="n"/>
-      <c r="AG41" s="9" t="n"/>
-      <c r="AH41" s="9" t="n"/>
-      <c r="AI41" s="10" t="n"/>
+      <c r="AE41" s="13" t="n"/>
+      <c r="AF41" s="13" t="n"/>
+      <c r="AG41" s="13" t="n"/>
+      <c r="AH41" s="13" t="n"/>
+      <c r="AI41" s="14" t="n"/>
       <c r="AJ41">
         <f>IF(AC41="",-9999-ROW()*0.0000001,AC41-ROW()*0.0000001)</f>
         <v/>
@@ -4469,67 +6177,100 @@
         <f>IF(AND(OR(AD41="Maybe",AD41="Price Review"),AG41&lt;&gt;"Approved",AG41&lt;&gt;"Rejected"),IF(AC41="",0,AC41)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
         <v/>
       </c>
+      <c r="AO41" s="18" t="n"/>
+      <c r="AP41" s="18" t="n"/>
+      <c r="AQ41" s="19" t="n"/>
+      <c r="AR41" s="19" t="n"/>
+      <c r="AS41" s="13" t="n"/>
+      <c r="AT41" s="19" t="n"/>
+      <c r="AU41" s="19" t="n"/>
+      <c r="AV41" s="19" t="n"/>
+      <c r="AW41" s="15">
+        <f>IF(OR(O41="",AV41=""),"",O41*AV41)</f>
+        <v/>
+      </c>
+      <c r="AX41" s="13" t="n"/>
+      <c r="AY41" s="13" t="n"/>
+      <c r="AZ41" s="13" t="n"/>
+      <c r="BA41" s="13" t="n"/>
+      <c r="BB41" s="13" t="n"/>
+      <c r="BC41" s="15" t="n"/>
+      <c r="BD41" s="13" t="n"/>
+      <c r="BE41" s="13">
+        <f>IF(C41="","",IF(AND(ISNUMBER(P41),P41&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB41),AB41&lt;=2),"Quality risk",IF(AND(ISNUMBER(U41),U41&lt;=2),"Aesthetic mismatch",IF(AY41="High","Too fragile",IF(AND(ISNUMBER(R41),R41&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT41),AT41&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD41="Maybe",AD41="Price Review"),"Needs partner review",IF(AD41="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF41" s="13" t="n"/>
+      <c r="BG41" s="13" t="n"/>
+      <c r="BH41" s="13" t="n"/>
+      <c r="BI41" s="13" t="n"/>
+      <c r="BJ41" s="13" t="n"/>
+      <c r="BK41" s="13" t="n"/>
+      <c r="BL41" s="13">
+        <f>IF(C41="","",IF(AND(BG41="Yes",BH41="Yes",BI41="Yes",BJ41="Yes",BK41="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="14">
+      <c r="A42" s="20">
         <f>IF(C42="","","AYN-"&amp;UPPER(LEFT(E42,3))&amp;"-"&amp;TEXT(ROW()-2,"000"))</f>
         <v/>
       </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="14" t="n"/>
-      <c r="K42" s="16">
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="22">
         <f>IF(I42="","",IF(J42="BDT",I42,IF(J42="USD",I42*USD_BDT,IF(J42="RMB",I42*RMB_BDT,""))))</f>
         <v/>
       </c>
-      <c r="L42" s="16" t="n"/>
-      <c r="M42" s="17" t="n"/>
-      <c r="N42" s="16" t="n"/>
-      <c r="O42" s="16">
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="23" t="n"/>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22">
         <f>IF(K42="","",K42+IFERROR(L42,0)+(K42*IF(M42="",CUSTOMS_PCT,M42))+IF(N42="",MISC_FEE,N42))</f>
         <v/>
       </c>
-      <c r="P42" s="16">
+      <c r="P42" s="22">
         <f>IF(O42="","",ROUND(O42*(1+MARKUP_PCT),-1)-1)</f>
         <v/>
       </c>
-      <c r="Q42" s="16">
+      <c r="Q42" s="22">
         <f>IF(P42="","",P42-O42)</f>
         <v/>
       </c>
-      <c r="R42" s="17">
+      <c r="R42" s="23">
         <f>IF(OR(P42="",P42=0),"",Q42/P42)</f>
         <v/>
       </c>
-      <c r="S42" s="14" t="n"/>
-      <c r="T42" s="14" t="n"/>
-      <c r="U42" s="14" t="n"/>
-      <c r="V42" s="14" t="n"/>
-      <c r="W42" s="14" t="n"/>
-      <c r="X42" s="14" t="n"/>
-      <c r="Y42" s="14" t="n"/>
-      <c r="Z42" s="14" t="n"/>
-      <c r="AA42" s="14" t="n"/>
-      <c r="AB42" s="14" t="n"/>
-      <c r="AC42" s="18">
+      <c r="S42" s="20" t="n"/>
+      <c r="T42" s="20" t="n"/>
+      <c r="U42" s="20" t="n"/>
+      <c r="V42" s="20" t="n"/>
+      <c r="W42" s="20" t="n"/>
+      <c r="X42" s="20" t="n"/>
+      <c r="Y42" s="20" t="n"/>
+      <c r="Z42" s="20" t="n"/>
+      <c r="AA42" s="20" t="n"/>
+      <c r="AB42" s="20" t="n"/>
+      <c r="AC42" s="24">
         <f>IF(COUNT(S42:AB42)&lt;10,"",(S42*W_FEMININE+T42*W_TREND+U42*W_AESTHETIC+V42*W_STYLE+W42*W_LIGHT+X42*W_REELS+Y42*W_GIFT+Z42*W_PRICEFIT+AA42*W_DEMAND+AB42*W_QUALITY)/5*100)</f>
         <v/>
       </c>
-      <c r="AD42" s="14">
+      <c r="AD42" s="20">
         <f>IF(P42="","",IF(P42&gt;HARD_REJECT_PRICE,"Reject",IF(P42&gt;MAX_PRICE,"Price Review",IF(AC42="","",IF(AND(AC42&gt;=BUY_THRESHOLD,OR(AB42&lt;=2,U42&lt;=2)),"Maybe",IF(AC42&gt;=BUY_THRESHOLD,"Buy",IF(AC42&gt;=MAYBE_THRESHOLD,"Maybe","Reject")))))))</f>
         <v/>
       </c>
-      <c r="AE42" s="14" t="n"/>
-      <c r="AF42" s="14" t="n"/>
-      <c r="AG42" s="14" t="n"/>
-      <c r="AH42" s="14" t="n"/>
-      <c r="AI42" s="15" t="n"/>
+      <c r="AE42" s="20" t="n"/>
+      <c r="AF42" s="20" t="n"/>
+      <c r="AG42" s="20" t="n"/>
+      <c r="AH42" s="20" t="n"/>
+      <c r="AI42" s="21" t="n"/>
       <c r="AJ42">
         <f>IF(AC42="",-9999-ROW()*0.0000001,AC42-ROW()*0.0000001)</f>
         <v/>
@@ -4548,6 +6289,39 @@
       </c>
       <c r="AN42">
         <f>IF(AND(OR(AD42="Maybe",AD42="Price Review"),AG42&lt;&gt;"Approved",AG42&lt;&gt;"Rejected"),IF(AC42="",0,AC42)-ROW()*0.0000001,-9999-ROW()*0.0000001)</f>
+        <v/>
+      </c>
+      <c r="AO42" s="25" t="n"/>
+      <c r="AP42" s="25" t="n"/>
+      <c r="AQ42" s="26" t="n"/>
+      <c r="AR42" s="26" t="n"/>
+      <c r="AS42" s="20" t="n"/>
+      <c r="AT42" s="26" t="n"/>
+      <c r="AU42" s="26" t="n"/>
+      <c r="AV42" s="26" t="n"/>
+      <c r="AW42" s="22">
+        <f>IF(OR(O42="",AV42=""),"",O42*AV42)</f>
+        <v/>
+      </c>
+      <c r="AX42" s="20" t="n"/>
+      <c r="AY42" s="20" t="n"/>
+      <c r="AZ42" s="20" t="n"/>
+      <c r="BA42" s="20" t="n"/>
+      <c r="BB42" s="20" t="n"/>
+      <c r="BC42" s="22" t="n"/>
+      <c r="BD42" s="20" t="n"/>
+      <c r="BE42" s="20">
+        <f>IF(C42="","",IF(AND(ISNUMBER(P42),P42&gt;MAX_PRICE),"Price too high",IF(AND(ISNUMBER(AB42),AB42&lt;=2),"Quality risk",IF(AND(ISNUMBER(U42),U42&lt;=2),"Aesthetic mismatch",IF(AY42="High","Too fragile",IF(AND(ISNUMBER(R42),R42&lt;LOW_PROFIT_PCT),"Low profit",IF(AND(ISNUMBER(AT42),AT42&gt;MOQ_WARNING),"MOQ too high",IF(OR(AD42="Maybe",AD42="Price Review"),"Needs partner review",IF(AD42="Buy","Good candidate","")))))))))</f>
+        <v/>
+      </c>
+      <c r="BF42" s="20" t="n"/>
+      <c r="BG42" s="20" t="n"/>
+      <c r="BH42" s="20" t="n"/>
+      <c r="BI42" s="20" t="n"/>
+      <c r="BJ42" s="20" t="n"/>
+      <c r="BK42" s="20" t="n"/>
+      <c r="BL42" s="20">
+        <f>IF(C42="","",IF(AND(BG42="Yes",BH42="Yes",BI42="Yes",BJ42="Yes",BK42="Yes"),"Yes","No"))</f>
         <v/>
       </c>
     </row>
@@ -4599,7 +6373,59 @@
       <formula>"Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="14">
+  <conditionalFormatting sqref="BE3:BE42">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="0">
+      <formula>"Good candidate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
+      <formula>"Needs partner review"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="3">
+      <formula>AND(BE3&lt;&gt;"",BE3&lt;&gt;"Good candidate",BE3&lt;&gt;"Needs partner review")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BL3:BL42">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="8">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY3:AY42">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="8">
+      <formula>"Medium"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="6">
+      <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BA3:BA42">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="3">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="8">
+      <formula>"Medium"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="6">
+      <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BD3:BD42">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="3">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="8">
+      <formula>"Medium"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="6">
+      <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="26">
     <dataValidation sqref="F3:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Where this product is sourced from" type="list">
       <formula1>LIST_PLATFORM</formula1>
     </dataValidation>
@@ -4642,6 +6468,42 @@
     <dataValidation sqref="AB3:AB42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Score 1 (worst) to 5 (best)" type="list">
       <formula1>LIST_SCORE</formula1>
     </dataValidation>
+    <dataValidation sqref="AS3:AS42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="BB3:BB42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="BG3:BG42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="BH3:BH42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="BI3:BI42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="BJ3:BJ42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="BK3:BK42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Yes or No" type="list">
+      <formula1>LIST_YESNO</formula1>
+    </dataValidation>
+    <dataValidation sqref="AY3:AY42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Low, Medium, or High" type="list">
+      <formula1>LIST_LEVEL</formula1>
+    </dataValidation>
+    <dataValidation sqref="BA3:BA42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Low, Medium, or High" type="list">
+      <formula1>LIST_LEVEL</formula1>
+    </dataValidation>
+    <dataValidation sqref="BD3:BD42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Low, Medium, or High" type="list">
+      <formula1>LIST_LEVEL</formula1>
+    </dataValidation>
+    <dataValidation sqref="AZ3:AZ42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Easy, Medium, or Hard" type="list">
+      <formula1>LIST_PACKAGING</formula1>
+    </dataValidation>
+    <dataValidation sqref="BF3:BF42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." promptTitle="Choose from list" prompt="Where this product is in the sourcing pipeline" type="list">
+      <formula1>LIST_SOURCING_STATUS</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4654,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4673,1279 +6535,1353 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Live view of the Product Tracker tab. Nothing here is editable — everything updates automatically.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Total products scouted</t>
         </is>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="30">
         <f>COUNTA('Product Tracker'!C3:C42)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="30">
         <f>COUNTIF('Product Tracker'!AD3:AD42,"Buy")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="30">
         <f>COUNTIF('Product Tracker'!AD3:AD42,"Maybe")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Price Review</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="30">
         <f>COUNTIF('Product Tracker'!AD3:AD42,"Price Review")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="30">
         <f>COUNTIF('Product Tracker'!AD3:AD42,"Reject")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Sourcing &amp; Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Total estimated purchase cost for approved products</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>SUMIF('Product Tracker'!AG3:AG42,"Approved",'Product Tracker'!AW3:AW42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Products ready for website upload</t>
+        </is>
+      </c>
+      <c r="B14" s="30">
+        <f>COUNTIF('Product Tracker'!BL3:BL42,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>High-risk products</t>
+        </is>
+      </c>
+      <c r="B15" s="30">
+        <f>SUMPRODUCT(--(('Product Tracker'!AY3:AY42="High")+('Product Tracker'!BA3:BA42="High")+(('Product Tracker'!AB3:AB42&lt;&gt;"")*('Product Tracker'!AB3:AB42&lt;=2))&gt;0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Products with high reel/photo potential</t>
+        </is>
+      </c>
+      <c r="B16" s="30">
+        <f>COUNTIF('Product Tracker'!X3:X42,"&gt;=4")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Products approved but not ordered yet</t>
+        </is>
+      </c>
+      <c r="B17" s="30">
+        <f>COUNTIFS('Product Tracker'!AG3:AG42,"Approved",'Product Tracker'!BF3:BF42,"Approved - Not Ordered")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Products ordered but not arrived yet</t>
+        </is>
+      </c>
+      <c r="B18" s="30">
+        <f>COUNTIF('Product Tracker'!BF3:BF42,"Ordered")+COUNTIF('Product Tracker'!BF3:BF42,"In Transit")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Top 10 Highest Scoring Products</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>Suggested Price</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
+    <row r="23">
+      <c r="A23" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B23" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C23" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D23" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E23" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F23" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,1),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
+    <row r="24">
+      <c r="A24" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B24" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C24" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D24" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E24" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F24" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,2),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
+    <row r="25">
+      <c r="A25" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B25" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C25" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D25" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E25" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F25" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,3),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
+    <row r="26">
+      <c r="A26" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B26" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C26" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D26" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E26" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F26" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,4),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
+    <row r="27">
+      <c r="A27" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B27" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C18" s="25">
+      <c r="C27" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D27" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E27" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F27" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,5),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
+    <row r="28">
+      <c r="A28" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B28" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C19" s="25">
+      <c r="C28" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D28" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E28" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F19" s="27">
+      <c r="F28" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,6),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
+    <row r="29">
+      <c r="A29" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B29" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C29" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D29" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E29" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F20" s="27">
+      <c r="F29" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,7),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="24" t="n">
+    <row r="30">
+      <c r="A30" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B30" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C21" s="25">
+      <c r="C30" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D30" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E30" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F21" s="27">
+      <c r="F30" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,8),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="24" t="n">
+    <row r="31">
+      <c r="A31" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B31" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C22" s="25">
+      <c r="C31" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D31" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E31" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F22" s="27">
+      <c r="F31" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,9),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="24" t="n">
+    <row r="32">
+      <c r="A32" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B32" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C23" s="25">
+      <c r="C32" s="34">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D32" s="35">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E32" s="33">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F23" s="27">
+      <c r="F32" s="36">
         <f>IF(LARGE('Product Tracker'!$AJ$3:$AJ$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AJ$3:$AJ$42,10),'Product Tracker'!$AJ$3:$AJ$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Best Products Under BDT 700</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C34" s="32" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>Suggested Price</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="24" t="n">
+    <row r="35">
+      <c r="A35" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B35" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C26" s="25">
+      <c r="C35" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D35" s="35">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E35" s="33">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F26" s="27">
+      <c r="F35" s="36">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,1),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="24" t="n">
+    <row r="36">
+      <c r="A36" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B36" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C27" s="25">
+      <c r="C36" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D36" s="35">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E36" s="33">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F27" s="27">
+      <c r="F36" s="36">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,2),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="24" t="n">
+    <row r="37">
+      <c r="A37" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B37" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C28" s="25">
+      <c r="C37" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D28" s="26">
+      <c r="D37" s="35">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E28" s="24">
+      <c r="E37" s="33">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F28" s="27">
+      <c r="F37" s="36">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,3),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="24" t="n">
+    <row r="38">
+      <c r="A38" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B38" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C29" s="25">
+      <c r="C38" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D29" s="26">
+      <c r="D38" s="35">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E38" s="33">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F29" s="27">
+      <c r="F38" s="36">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,4),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="24" t="n">
+    <row r="39">
+      <c r="A39" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B39" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C30" s="25">
+      <c r="C39" s="34">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D30" s="26">
+      <c r="D39" s="35">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E39" s="33">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F30" s="27">
+      <c r="F39" s="36">
         <f>IF(LARGE('Product Tracker'!$AK$3:$AK$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AK$3:$AK$42,5),'Product Tracker'!$AK$3:$AK$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Best Products for Reels/Photos</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C41" s="32" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D41" s="32" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F41" s="32" t="inlineStr">
         <is>
           <t>Suggested Price</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="24" t="n">
+    <row r="42">
+      <c r="A42" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B42" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C33" s="25">
+      <c r="C42" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D33" s="26">
+      <c r="D42" s="35">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E33" s="24">
+      <c r="E42" s="33">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F33" s="27">
+      <c r="F42" s="36">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,1),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="24" t="n">
+    <row r="43">
+      <c r="A43" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B43" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C34" s="25">
+      <c r="C43" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D34" s="26">
+      <c r="D43" s="35">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E43" s="33">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F34" s="27">
+      <c r="F43" s="36">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,2),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="24" t="n">
+    <row r="44">
+      <c r="A44" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B44" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C35" s="25">
+      <c r="C44" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D35" s="26">
+      <c r="D44" s="35">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E35" s="24">
+      <c r="E44" s="33">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F35" s="27">
+      <c r="F44" s="36">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,3),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="24" t="n">
+    <row r="45">
+      <c r="A45" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B45" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C36" s="25">
+      <c r="C45" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D36" s="26">
+      <c r="D45" s="35">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E36" s="24">
+      <c r="E45" s="33">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F36" s="27">
+      <c r="F45" s="36">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,4),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="24" t="n">
+    <row r="46">
+      <c r="A46" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B46" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C37" s="25">
+      <c r="C46" s="34">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D37" s="26">
+      <c r="D46" s="35">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E37" s="24">
+      <c r="E46" s="33">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F37" s="27">
+      <c r="F46" s="36">
         <f>IF(LARGE('Product Tracker'!$AL$3:$AL$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AL$3:$AL$42,5),'Product Tracker'!$AL$3:$AL$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="28" t="inlineStr">
         <is>
           <t>Best Giftable Products</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B48" s="32" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C48" s="32" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F48" s="32" t="inlineStr">
         <is>
           <t>Suggested Price</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="24" t="n">
+    <row r="49">
+      <c r="A49" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B49" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C40" s="25">
+      <c r="C49" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D40" s="26">
+      <c r="D49" s="35">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E40" s="24">
+      <c r="E49" s="33">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F40" s="27">
+      <c r="F49" s="36">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,1),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="24" t="n">
+    <row r="50">
+      <c r="A50" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B50" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C41" s="25">
+      <c r="C50" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D41" s="26">
+      <c r="D50" s="35">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E41" s="24">
+      <c r="E50" s="33">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F41" s="27">
+      <c r="F50" s="36">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,2),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="24" t="n">
+    <row r="51">
+      <c r="A51" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B51" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C42" s="25">
+      <c r="C51" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D42" s="26">
+      <c r="D51" s="35">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E42" s="24">
+      <c r="E51" s="33">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F42" s="27">
+      <c r="F51" s="36">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,3),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="24" t="n">
+    <row r="52">
+      <c r="A52" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B52" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C43" s="25">
+      <c r="C52" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D43" s="26">
+      <c r="D52" s="35">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E43" s="24">
+      <c r="E52" s="33">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F43" s="27">
+      <c r="F52" s="36">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,4),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="24" t="n">
+    <row r="53">
+      <c r="A53" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B44" s="25">
+      <c r="B53" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C44" s="25">
+      <c r="C53" s="34">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D44" s="26">
+      <c r="D53" s="35">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E44" s="24">
+      <c r="E53" s="33">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F44" s="27">
+      <c r="F53" s="36">
         <f>IF(LARGE('Product Tracker'!$AM$3:$AM$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AM$3:$AM$42,5),'Product Tracker'!$AM$3:$AM$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>Products Needing Partner Review (Maybe / Price Review, not yet decided)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C55" s="32" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E55" s="32" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F55" s="32" t="inlineStr">
         <is>
           <t>Suggested Price</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="24" t="n">
+    <row r="56">
+      <c r="A56" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B56" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C47" s="25">
+      <c r="C56" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D47" s="26">
+      <c r="D56" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E47" s="24">
+      <c r="E56" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F47" s="27">
+      <c r="F56" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,1)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,1),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="24" t="n">
+    <row r="57">
+      <c r="A57" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B57" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C48" s="25">
+      <c r="C57" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D48" s="26">
+      <c r="D57" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E48" s="24">
+      <c r="E57" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F48" s="27">
+      <c r="F57" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,2)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,2),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="24" t="n">
+    <row r="58">
+      <c r="A58" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B58" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C49" s="25">
+      <c r="C58" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D49" s="26">
+      <c r="D58" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E49" s="24">
+      <c r="E58" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F49" s="27">
+      <c r="F58" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,3)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,3),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="24" t="n">
+    <row r="59">
+      <c r="A59" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B59" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C50" s="25">
+      <c r="C59" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D50" s="26">
+      <c r="D59" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E50" s="24">
+      <c r="E59" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F50" s="27">
+      <c r="F59" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,4)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,4),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="24" t="n">
+    <row r="60">
+      <c r="A60" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B60" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C51" s="25">
+      <c r="C60" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D51" s="26">
+      <c r="D60" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E51" s="24">
+      <c r="E60" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F51" s="27">
+      <c r="F60" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,5)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,5),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="24" t="n">
+    <row r="61">
+      <c r="A61" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B61" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C52" s="25">
+      <c r="C61" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D52" s="26">
+      <c r="D61" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E52" s="24">
+      <c r="E61" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F52" s="27">
+      <c r="F61" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,6)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,6),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="24" t="n">
+    <row r="62">
+      <c r="A62" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B53" s="25">
+      <c r="B62" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C53" s="25">
+      <c r="C62" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D53" s="26">
+      <c r="D62" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E53" s="24">
+      <c r="E62" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F53" s="27">
+      <c r="F62" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,7)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,7),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="24" t="n">
+    <row r="63">
+      <c r="A63" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B54" s="25">
+      <c r="B63" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C54" s="25">
+      <c r="C63" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D54" s="26">
+      <c r="D63" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E54" s="24">
+      <c r="E63" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F54" s="27">
+      <c r="F63" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,8)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,8),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="24" t="n">
+    <row r="64">
+      <c r="A64" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B64" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C55" s="25">
+      <c r="C64" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D55" s="26">
+      <c r="D64" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E55" s="24">
+      <c r="E64" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F55" s="27">
+      <c r="F64" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,9)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,9),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="24" t="n">
+    <row r="65">
+      <c r="A65" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B65" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C56" s="25">
+      <c r="C65" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D56" s="26">
+      <c r="D65" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E56" s="24">
+      <c r="E65" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F56" s="27">
+      <c r="F65" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,10)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,10),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="24" t="n">
+    <row r="66">
+      <c r="A66" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B66" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C57" s="25">
+      <c r="C66" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D57" s="26">
+      <c r="D66" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E57" s="24">
+      <c r="E66" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F57" s="27">
+      <c r="F66" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,11)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,11),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="24" t="n">
+    <row r="67">
+      <c r="A67" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B67" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C58" s="25">
+      <c r="C67" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D58" s="26">
+      <c r="D67" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E58" s="24">
+      <c r="E67" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F58" s="27">
+      <c r="F67" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,12)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,12),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="24" t="n">
+    <row r="68">
+      <c r="A68" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B68" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C59" s="25">
+      <c r="C68" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D59" s="26">
+      <c r="D68" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E59" s="24">
+      <c r="E68" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F59" s="27">
+      <c r="F68" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,13)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,13),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="24" t="n">
+    <row r="69">
+      <c r="A69" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B60" s="25">
+      <c r="B69" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C60" s="25">
+      <c r="C69" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D60" s="26">
+      <c r="D69" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E60" s="24">
+      <c r="E69" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F60" s="27">
+      <c r="F69" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,14)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,14),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="24" t="n">
+    <row r="70">
+      <c r="A70" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B70" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$C$3:$C$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="C61" s="25">
+      <c r="C70" s="34">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$A$3:$A$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="D61" s="26">
+      <c r="D70" s="35">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AC$3:$AC$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="E61" s="24">
+      <c r="E70" s="33">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$AD$3:$AD$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
-      <c r="F61" s="27">
+      <c r="F70" s="36">
         <f>IF(LARGE('Product Tracker'!$AN$3:$AN$42,15)&gt;-9000,IFERROR(INDEX('Product Tracker'!$P$3:$P$42,MATCH(LARGE('Product Tracker'!$AN$3:$AN$42,15),'Product Tracker'!$AN$3:$AN$42,0)),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5972,14 +7908,14 @@
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Copy everything in the box below into Claude (or another AI assistant), paste in the product photo/link/description where indicated, then copy Claude's reply back into the matching score columns on the Product Tracker tab.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="520" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>You are helping AAYNA, a Bangladesh-based women's accessories brand, evaluate a sourcing candidate product.
 AAYNA's brand identity: feminine, trendy, affordable, clean and modern, with a warm, social-media-friendly feel. Visual aesthetic: dusty rose, cream white, antique gold, and espresso charcoal. Most products sell under BDT 700.
@@ -6017,7 +7953,7 @@
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Tip: if you ever change the 10 scoring criteria, their order, or the price ceiling in the Settings tab, update this prompt to match so Claude's answers keep lining up with the Product Tracker columns.</t>
         </is>
@@ -6035,7 +7971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6051,31 +7987,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Tune these numbers once. Every formula in the Product Tracker tab reads from here.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>USD to BDT exchange rate</t>
         </is>
@@ -6083,14 +8019,14 @@
       <c r="B5" t="n">
         <v>122</v>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Update when BDT/USD rate changes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>RMB (CNY) to BDT exchange rate</t>
         </is>
@@ -6098,14 +8034,14 @@
       <c r="B6" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Update when BDT/CNY rate changes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Default customs/duty %</t>
         </is>
@@ -6113,14 +8049,14 @@
       <c r="B7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>As decimal, e.g. 0.07 = 7%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Default misc fee per unit (BDT)</t>
         </is>
@@ -6128,14 +8064,14 @@
       <c r="B8" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Packaging, handling, platform fees per piece</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Default markup % over landed cost</t>
         </is>
@@ -6143,14 +8079,14 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>1.0 = 100% markup (sell at 2x landed cost)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Target max selling price (BDT)</t>
         </is>
@@ -6158,14 +8094,14 @@
       <c r="B10" t="n">
         <v>700</v>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>AAYNA's 'mostly under' price ceiling</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Hard reject price ceiling (BDT)</t>
         </is>
@@ -6173,14 +8109,14 @@
       <c r="B11" t="n">
         <v>1000</v>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Above the target price but at/under this = 'Price Review' (negotiable). Above this = automatic 'Reject'.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Weight: Feminine Score</t>
         </is>
@@ -6188,14 +8124,14 @@
       <c r="B12" t="n">
         <v>0.1</v>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>All 10 weights below must add up to 1.00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Weight: Trend Score</t>
         </is>
@@ -6203,10 +8139,10 @@
       <c r="B13" t="n">
         <v>0.1</v>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
+      <c r="C13" s="27" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Weight: AAYNA Aesthetic Fit Score</t>
         </is>
@@ -6214,10 +8150,10 @@
       <c r="B14" t="n">
         <v>0.15</v>
       </c>
-      <c r="C14" s="19" t="inlineStr"/>
+      <c r="C14" s="27" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Weight: Easy to Style Score</t>
         </is>
@@ -6225,10 +8161,10 @@
       <c r="B15" t="n">
         <v>0.08</v>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
+      <c r="C15" s="27" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Weight: Lightweight Score</t>
         </is>
@@ -6236,10 +8172,10 @@
       <c r="B16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C16" s="19" t="inlineStr"/>
+      <c r="C16" s="27" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Weight: Reels/Photo Potential Score</t>
         </is>
@@ -6247,10 +8183,10 @@
       <c r="B17" t="n">
         <v>0.1</v>
       </c>
-      <c r="C17" s="19" t="inlineStr"/>
+      <c r="C17" s="27" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Weight: Giftability Score</t>
         </is>
@@ -6258,10 +8194,10 @@
       <c r="B18" t="n">
         <v>0.08</v>
       </c>
-      <c r="C18" s="19" t="inlineStr"/>
+      <c r="C18" s="27" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Weight: Price Fit Score</t>
         </is>
@@ -6269,10 +8205,10 @@
       <c r="B19" t="n">
         <v>0.12</v>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
+      <c r="C19" s="27" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Weight: Demand Score</t>
         </is>
@@ -6280,10 +8216,10 @@
       <c r="B20" t="n">
         <v>0.12</v>
       </c>
-      <c r="C20" s="19" t="inlineStr"/>
+      <c r="C20" s="27" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Weight: Quality/Risk Score</t>
         </is>
@@ -6291,10 +8227,10 @@
       <c r="B21" t="n">
         <v>0.08</v>
       </c>
-      <c r="C21" s="19" t="inlineStr"/>
+      <c r="C21" s="27" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>Buy threshold (score &gt;=)</t>
         </is>
@@ -6302,14 +8238,14 @@
       <c r="B22" t="n">
         <v>75</v>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Total Product Score is out of 100</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Maybe threshold (score &gt;=)</t>
         </is>
@@ -6317,9 +8253,39 @@
       <c r="B23" t="n">
         <v>50</v>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>Below this = Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Low profit margin warning threshold</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Auto Flag shows 'Low profit' below this margin, e.g. 0.30 = 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>MOQ warning threshold (units)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>50</v>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Auto Flag shows 'MOQ too high' above this quantity</t>
         </is>
       </c>
     </row>
@@ -6339,7 +8305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6348,37 +8314,61 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Source Platform</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Source Currency</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="28" t="inlineStr">
         <is>
           <t>Approval Status</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>Score (1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Risk Level</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Packaging Difficulty</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Sourcing Status</t>
         </is>
       </c>
     </row>
@@ -6411,6 +8401,26 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6441,6 +8451,26 @@
       <c r="F3" t="n">
         <v>2</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6471,6 +8501,21 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sample Ordered</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6496,6 +8541,11 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sample Received</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6511,6 +8561,11 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Approved - Not Ordered</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6523,6 +8578,11 @@
           <t>Bag</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ordered</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -6530,6 +8590,11 @@
           <t>Belt</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -6537,11 +8602,21 @@
           <t>Sunglasses</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
           <t>Watch</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Live on Website</t>
         </is>
       </c>
     </row>
@@ -6578,7 +8653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6593,12 +8668,12 @@
       </c>
     </row>
     <row r="2" ht="100" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>This sheet helps the 3 of us score and decide on products from SkyBuyBD, AliExpress, or other China sourcing platforms — fast, consistently, and without spreadsheets fights.
 Workflow: Whoever finds a product adds a new row and fills in the WHITE input columns only. The colored formula columns calculate themselves. Then each partner fills in the 10 score columns (or pastes in Claude's scores from the Claude Scoring Prompt tab), and the sheet tells you Buy / Maybe / Price Review / Reject automatically.</t>
@@ -6606,132 +8681,180 @@
       </c>
     </row>
     <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Step 1 — Add the product</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>SKU fills in automatically. Enter Date Added, Product Name, Image/Link, Category, Source Platform, Source URL, Supplier Name.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Step 2 — Enter cost info</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Enter Unit Cost in whatever currency the supplier quoted (USD/RMB/BDT), pick the currency, then enter Shipping Cost/Unit and Misc Fees if known. Customs % and Misc Fees auto-fill from Settings tab if left blank.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Step 3 — Let it calculate</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Unit Cost (BDT), Estimated Landed Cost, Suggested Selling Price, Expected Profit, and Profit Margin % fill in automatically.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Step 4 — Score it (1 = worst, 5 = best)</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Feminine: how feminine/delicate does it look? Trend: how hot is this right now (TikTok/IG/competitors)? AAYNA Aesthetic Fit: how well does it match our dusty rose / cream / antique gold look? Easy to Style: how easily can a customer style this with everyday outfits? Lightweight: how light/comfortable is it to wear or carry? Reels/Photo Potential: how good would this look in a Reel, photo, or unboxing video? Giftability: how good is this as a gift? Price Fit: how comfortably can we sell this under BDT 700 and still profit? Demand: how likely is our target customer to actually want and buy this? Quality/Risk: how low is the risk of poor quality, damage in transit, or returns? Tip: use the Claude Scoring Prompt tab to get an AI first opinion on all 10 scores at once.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Step 5 — Read the verdict</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Total Product Score (0-100) calculates automatically using the weights set in the Settings tab. Decision applies these hard rules on top of the score: if Suggested Selling Price is over BDT 700, Decision becomes 'Price Review' (and 'Reject' if it's far over, above the Hard Reject Price Ceiling in Settings); if Quality/Risk or AAYNA Aesthetic Fit score is 1 or 2, Decision can never be 'Buy' (it caps at 'Maybe') even if the total score is high. Buy = green, Maybe = yellow, Price Review = orange, Reject = red.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="75" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Step 6 — Decide together</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Add a short Reason so the other partners know WHY. Add a Content/Reel Idea so marketing has a head start. Set Approval Status once all partners agree, note who Approved and the date.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="75" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>Step 7 — Sourcing &amp; operations columns</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Once a product looks promising, fill in the sourcing/operations columns (after the scoring columns): Supplier Rating, Product Rating, Sold Count/Order Count, Review Count, and Real Review Photos? help you judge if a supplier is trustworthy. MOQ, Recommended Test Quantity, and Final Approved Quantity track how many units to order; Total Purchase Cost calculates itself (Estimated Landed Cost x Final Approved Quantity) once both are filled in. Weight/Size, Fragility Level, Packaging Difficulty, and Courier Risk flag shipping problems before you commit. Duplicate Found on BD Market?, Competitor Price, and Market Saturation Level help you judge if it's already oversaturated locally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>Auto Flag / Warning</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Calculates itself and shows the single biggest problem with a product, in priority order: 'Price too high' (over the price ceiling), 'Quality risk' (Quality/Risk score 1-2), 'Aesthetic mismatch' (Aesthetic Fit score 1-2), 'Too fragile' (Fragility Level = High), 'Low profit' (margin below the Settings threshold), 'MOQ too high' (above the Settings threshold), 'Needs partner review' (still Maybe/Price Review), or 'Good candidate' (a clean Buy with no problems). Use it as a quick at-a-glance warning, not a replacement for reading the Reason column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>Website-readiness checklist</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Product Name Finalized?, SKU Finalized?, Photos Ready?, Description Ready?, and Price Approved? are simple Yes/No checkboxes for whoever preps the listing. Ready for Website Upload? calculates itself: it only shows 'Yes' once ALL FIVE of those checklist columns say 'Yes'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Sourcing Status</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Track where a product physically is in the pipeline: Not Started, Sourcing, Sample Ordered, Sample Received, Approved - Not Ordered, Ordered, In Transit, Arrived, or Live on Website. This is separate from Decision/Approval Status — a product can be Approved but still waiting on an order, or Ordered while the website checklist is still in progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Adjusting the formulas</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>Don't like the default markup, exchange rate, price ceilings, or scoring weights? Change them ONCE in the Settings tab — every row updates automatically. No need to touch the Product Tracker formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Don't like the default markup, exchange rate, price ceilings, scoring weights, low profit margin warning, or MOQ warning threshold? Change them ONCE in the Settings tab — every row updates automatically. No need to touch the Product Tracker formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>The Dashboard tab</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>A live, read-only overview: how many products are Buy/Maybe/Price Review/Reject, the Top 10 highest scoring products, the best products under BDT 700, the best products for reels/photos, the best giftable products, and everything still waiting on partner review. Nothing on this tab needs to be filled in by hand — it reads straight from the Product Tracker tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>A live, read-only overview: how many products are Buy/Maybe/Price Review/Reject; total estimated purchase cost for approved products, products ready for website upload, high-risk products, products with high reel/photo potential, products approved but not ordered yet, and products ordered but not arrived yet; the Top 10 highest scoring products, the best products under BDT 700, the best products for reels/photos, the best giftable products, and everything still waiting on partner review. Nothing on this tab needs to be filled in by hand — it reads straight from the Product Tracker tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>The Claude Scoring Prompt tab</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>A ready-to-copy prompt for getting an AI first opinion on a product's 10 scores, a recommended decision, and a content/reel idea, formatted so the reply is easy to paste back into the right columns.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="75" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Color key</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Green = Buy / Approved. Yellow = Maybe / Pending. Orange = Price Review (price is over our 700 BDT target but might still be worth negotiating). Red = Reject / Rejected, or a Quality/Risk or Aesthetic Fit score of 1-2.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Tips for 3-partner teams</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Assign one score block per partner if you want speed (e.g. Partner A scores Feminine + Trend + Aesthetic Fit, Partner B scores Easy to Style + Lightweight + Reels/Photo, Partner C scores Giftability + Price Fit + Demand + Quality/Risk) — or all 3 score independently and average manually before finalizing. Keep the Reason column honest; it's your shared memory.</t>
         </is>
